--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,18 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59107974-E74D-4149-B78C-E3DF132AD685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E38574-B74F-4B6E-B524-301EB285BE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
   <sheets>
-    <sheet name="table" sheetId="2" r:id="rId1"/>
-    <sheet name="data" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="table" sheetId="2" r:id="rId2"/>
+    <sheet name="data" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">table!$A$1:$H$41</definedName>
+    <definedName name="ExternalData_1" localSheetId="1" hidden="1">table!$A$1:$H$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="30">
   <si>
     <t>S No</t>
   </si>
@@ -130,6 +134,18 @@
   <si>
     <t>Keyboard</t>
   </si>
+  <si>
+    <t>TOTAL SALES</t>
+  </si>
+  <si>
+    <t>TOTAL ITEM</t>
+  </si>
+  <si>
+    <t>AVG SALES</t>
+  </si>
+  <si>
+    <t>KPIS</t>
+  </si>
 </sst>
 </file>
 
@@ -144,12 +160,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -164,16 +186,90 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -199,6 +295,737 @@
 </styleSheet>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="THINKPAD" refreshedDate="46309.977522453701" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{FFB1D962-FE14-49D9-BFDB-4943184A39C0}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="sales"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="S No" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="40"/>
+    </cacheField>
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-01-01T00:00:00" maxDate="2023-02-10T00:00:00"/>
+    </cacheField>
+    <cacheField name="Salesman" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Item" numFmtId="0">
+      <sharedItems count="8">
+        <s v="Mouse"/>
+        <s v="Scanner"/>
+        <s v="Printer"/>
+        <s v="Laptop"/>
+        <s v="Speaker"/>
+        <s v="Monitor"/>
+        <s v="Headset"/>
+        <s v="Keyboard"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Qty" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="8"/>
+    </cacheField>
+    <cacheField name="Price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="190" maxValue="8500"/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="190" maxValue="68000" count="28">
+        <n v="1050"/>
+        <n v="4500"/>
+        <n v="14700"/>
+        <n v="420"/>
+        <n v="1500"/>
+        <n v="34000"/>
+        <n v="300"/>
+        <n v="51000"/>
+        <n v="4800"/>
+        <n v="4200"/>
+        <n v="12600"/>
+        <n v="1800"/>
+        <n v="2100"/>
+        <n v="600"/>
+        <n v="2700"/>
+        <n v="1140"/>
+        <n v="42500"/>
+        <n v="190"/>
+        <n v="1260"/>
+        <n v="760"/>
+        <n v="68000"/>
+        <n v="900"/>
+        <n v="6300"/>
+        <n v="17000"/>
+        <n v="380"/>
+        <n v="25500"/>
+        <n v="10500"/>
+        <n v="7200"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+  <r>
+    <n v="1"/>
+    <d v="2023-01-01T00:00:00"/>
+    <s v="Ahmed Said"/>
+    <s v="Cairo"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="210"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <d v="2023-01-02T00:00:00"/>
+    <s v="Ali Ramadan"/>
+    <s v="Domietta"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="1500"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <d v="2023-01-03T00:00:00"/>
+    <s v="Ashraf Zaki"/>
+    <s v="Cairo"/>
+    <x v="2"/>
+    <n v="7"/>
+    <n v="2100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <d v="2023-01-04T00:00:00"/>
+    <s v="Fathy Ali"/>
+    <s v="Cairo"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="210"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <d v="2023-01-05T00:00:00"/>
+    <s v="Tamer Mohamed"/>
+    <s v="Domietta"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="1500"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <d v="2023-01-06T00:00:00"/>
+    <s v="Khaled Hassan"/>
+    <s v="Domietta"/>
+    <x v="3"/>
+    <n v="4"/>
+    <n v="8500"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <d v="2023-01-07T00:00:00"/>
+    <s v="Ahmed Said"/>
+    <s v="Giza"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="300"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <d v="2023-01-08T00:00:00"/>
+    <s v="Ali Ramadan"/>
+    <s v="Domietta"/>
+    <x v="3"/>
+    <n v="6"/>
+    <n v="8500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <d v="2023-01-09T00:00:00"/>
+    <s v="Ashraf Zaki"/>
+    <s v="Alexandria"/>
+    <x v="5"/>
+    <n v="4"/>
+    <n v="1200"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <d v="2023-01-10T00:00:00"/>
+    <s v="Fathy Ali"/>
+    <s v="Alexandria"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="2100"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <d v="2023-01-11T00:00:00"/>
+    <s v="Tamer Mohamed"/>
+    <s v="Giza"/>
+    <x v="2"/>
+    <n v="6"/>
+    <n v="2100"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <d v="2023-01-12T00:00:00"/>
+    <s v="Khaled Hassan"/>
+    <s v="Alexandria"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="300"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <d v="2023-01-13T00:00:00"/>
+    <s v="Ahmed Said"/>
+    <s v="Giza"/>
+    <x v="2"/>
+    <n v="7"/>
+    <n v="2100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <d v="2023-01-14T00:00:00"/>
+    <s v="Ali Ramadan"/>
+    <s v="Cairo"/>
+    <x v="4"/>
+    <n v="6"/>
+    <n v="300"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <d v="2023-01-15T00:00:00"/>
+    <s v="Ashraf Zaki"/>
+    <s v="Domietta"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="2100"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <d v="2023-01-16T00:00:00"/>
+    <s v="Fathy Ali"/>
+    <s v="Domietta"/>
+    <x v="4"/>
+    <n v="2"/>
+    <n v="300"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <d v="2023-01-17T00:00:00"/>
+    <s v="Tamer Mohamed"/>
+    <s v="Domietta"/>
+    <x v="2"/>
+    <n v="7"/>
+    <n v="2100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <d v="2023-01-18T00:00:00"/>
+    <s v="Khaled Hassan"/>
+    <s v="Alexandria"/>
+    <x v="6"/>
+    <n v="6"/>
+    <n v="450"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <d v="2023-01-19T00:00:00"/>
+    <s v="Ahmed Said"/>
+    <s v="Domietta"/>
+    <x v="7"/>
+    <n v="6"/>
+    <n v="190"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <d v="2023-01-20T00:00:00"/>
+    <s v="Ali Ramadan"/>
+    <s v="Domietta"/>
+    <x v="4"/>
+    <n v="2"/>
+    <n v="300"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <d v="2023-01-21T00:00:00"/>
+    <s v="Ashraf Zaki"/>
+    <s v="Domietta"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="1500"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <d v="2023-01-22T00:00:00"/>
+    <s v="Fathy Ali"/>
+    <s v="Giza"/>
+    <x v="3"/>
+    <n v="5"/>
+    <n v="8500"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <d v="2023-01-23T00:00:00"/>
+    <s v="Tamer Mohamed"/>
+    <s v="Domietta"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="190"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <d v="2023-01-24T00:00:00"/>
+    <s v="Khaled Hassan"/>
+    <s v="Domietta"/>
+    <x v="0"/>
+    <n v="6"/>
+    <n v="210"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <d v="2023-01-25T00:00:00"/>
+    <s v="Ahmed Said"/>
+    <s v="Giza"/>
+    <x v="4"/>
+    <n v="2"/>
+    <n v="300"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <d v="2023-01-26T00:00:00"/>
+    <s v="Ali Ramadan"/>
+    <s v="Domietta"/>
+    <x v="7"/>
+    <n v="4"/>
+    <n v="190"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <d v="2023-01-27T00:00:00"/>
+    <s v="Ashraf Zaki"/>
+    <s v="Giza"/>
+    <x v="3"/>
+    <n v="8"/>
+    <n v="8500"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <d v="2023-01-28T00:00:00"/>
+    <s v="Fathy Ali"/>
+    <s v="Domietta"/>
+    <x v="4"/>
+    <n v="3"/>
+    <n v="300"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <d v="2023-01-29T00:00:00"/>
+    <s v="Tamer Mohamed"/>
+    <s v="Domietta"/>
+    <x v="4"/>
+    <n v="7"/>
+    <n v="300"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <d v="2023-01-30T00:00:00"/>
+    <s v="Khaled Hassan"/>
+    <s v="Giza"/>
+    <x v="7"/>
+    <n v="4"/>
+    <n v="190"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <d v="2023-01-31T00:00:00"/>
+    <s v="Ahmed Said"/>
+    <s v="Domietta"/>
+    <x v="6"/>
+    <n v="2"/>
+    <n v="450"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <d v="2023-02-01T00:00:00"/>
+    <s v="Ali Ramadan"/>
+    <s v="Cairo"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="2100"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <d v="2023-02-02T00:00:00"/>
+    <s v="Ashraf Zaki"/>
+    <s v="Domietta"/>
+    <x v="3"/>
+    <n v="2"/>
+    <n v="8500"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <d v="2023-02-03T00:00:00"/>
+    <s v="Fathy Ali"/>
+    <s v="Giza"/>
+    <x v="3"/>
+    <n v="8"/>
+    <n v="8500"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <d v="2023-02-04T00:00:00"/>
+    <s v="Tamer Mohamed"/>
+    <s v="Alexandria"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="210"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <d v="2023-02-05T00:00:00"/>
+    <s v="Khaled Hassan"/>
+    <s v="Alexandria"/>
+    <x v="7"/>
+    <n v="2"/>
+    <n v="190"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <d v="2023-02-06T00:00:00"/>
+    <s v="Ahmed Said"/>
+    <s v="Alexandria"/>
+    <x v="3"/>
+    <n v="3"/>
+    <n v="8500"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <d v="2023-02-07T00:00:00"/>
+    <s v="Ali Ramadan"/>
+    <s v="Giza"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="210"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <d v="2023-02-08T00:00:00"/>
+    <s v="Ashraf Zaki"/>
+    <s v="Domietta"/>
+    <x v="2"/>
+    <n v="5"/>
+    <n v="2100"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <d v="2023-02-09T00:00:00"/>
+    <s v="Fathy Ali"/>
+    <s v="Domietta"/>
+    <x v="5"/>
+    <n v="6"/>
+    <n v="1200"/>
+    <x v="27"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="8">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{45FE5043-C852-44A5-BF97-16E323DBE1F5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9">
@@ -221,10 +1048,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="10"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -549,6 +1376,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1649C905-6944-4F98-B4AE-37BE068CDF30}">
+  <dimension ref="A2:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>426530</v>
+      </c>
+      <c r="C6" s="4">
+        <v>40</v>
+      </c>
+      <c r="E6" s="4">
+        <v>10663.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF8A719-9DE1-494C-AEC9-6B8400C82FA6}">
   <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1637,7 +2514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D1B5A55-B004-4FDC-90CE-889382A104E7}">
   <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E38574-B74F-4B6E-B524-301EB285BE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4E5FC3-6B2B-4A22-B5EE-17907C860EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
-    <sheet name="table" sheetId="2" r:id="rId2"/>
-    <sheet name="data" sheetId="1" r:id="rId3"/>
+    <sheet name="dashboard" sheetId="4" r:id="rId1"/>
+    <sheet name="data analysis" sheetId="3" r:id="rId2"/>
+    <sheet name="table" sheetId="2" r:id="rId3"/>
+    <sheet name="data" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">table!$A$1:$H$41</definedName>
+    <definedName name="ExternalData_1" localSheetId="2" hidden="1">table!$A$1:$H$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="5" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -151,7 +152,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,10 +195,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -195,11 +208,237 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -295,6 +534,256 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'data analysis'!A7">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{298D81AF-3522-AE4E-1E11-5B9B0E9C0C11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2385060" y="701040"/>
+          <a:ext cx="1866900" cy="739140"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:fld id="{E579ED93-EF0A-42B5-9B0D-24E1CFD28BCA}" type="TxLink">
+            <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:rPr>
+            <a:pPr algn="r"/>
+            <a:t> $426,530 </a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="2000" b="1">
+            <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>240030</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>278130</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'data analysis'!C7">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E128FE5D-66DC-2A53-2918-C5B556CBB598}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5116830" y="701040"/>
+          <a:ext cx="1866900" cy="739140"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:fld id="{CAE52DA5-E783-42D2-873D-9F631120CFC5}" type="TxLink">
+            <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+            </a:rPr>
+            <a:pPr algn="r"/>
+            <a:t>40</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="2000" b="1">
+            <a:latin typeface="+mj-lt"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="'data analysis'!E7">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CF5D85A-1B58-1E0F-6ECB-D976385F9B60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7848600" y="701040"/>
+          <a:ext cx="1866900" cy="739140"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:fld id="{5705C105-A208-49EE-830A-EA84537AE66E}" type="TxLink">
+            <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:rPr>
+            <a:t>10663.25</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="2000" b="1">
+            <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="THINKPAD" refreshedDate="46309.977522453701" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{FFB1D962-FE14-49D9-BFDB-4943184A39C0}">
   <cacheSource type="worksheet">
@@ -305,7 +794,48 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="40"/>
     </cacheField>
     <cacheField name="Date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-01-01T00:00:00" maxDate="2023-02-10T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-01-01T00:00:00" maxDate="2023-02-10T00:00:00" count="40">
+        <d v="2023-01-01T00:00:00"/>
+        <d v="2023-01-02T00:00:00"/>
+        <d v="2023-01-03T00:00:00"/>
+        <d v="2023-01-04T00:00:00"/>
+        <d v="2023-01-05T00:00:00"/>
+        <d v="2023-01-06T00:00:00"/>
+        <d v="2023-01-07T00:00:00"/>
+        <d v="2023-01-08T00:00:00"/>
+        <d v="2023-01-09T00:00:00"/>
+        <d v="2023-01-10T00:00:00"/>
+        <d v="2023-01-11T00:00:00"/>
+        <d v="2023-01-12T00:00:00"/>
+        <d v="2023-01-13T00:00:00"/>
+        <d v="2023-01-14T00:00:00"/>
+        <d v="2023-01-15T00:00:00"/>
+        <d v="2023-01-16T00:00:00"/>
+        <d v="2023-01-17T00:00:00"/>
+        <d v="2023-01-18T00:00:00"/>
+        <d v="2023-01-19T00:00:00"/>
+        <d v="2023-01-20T00:00:00"/>
+        <d v="2023-01-21T00:00:00"/>
+        <d v="2023-01-22T00:00:00"/>
+        <d v="2023-01-23T00:00:00"/>
+        <d v="2023-01-24T00:00:00"/>
+        <d v="2023-01-25T00:00:00"/>
+        <d v="2023-01-26T00:00:00"/>
+        <d v="2023-01-27T00:00:00"/>
+        <d v="2023-01-28T00:00:00"/>
+        <d v="2023-01-29T00:00:00"/>
+        <d v="2023-01-30T00:00:00"/>
+        <d v="2023-01-31T00:00:00"/>
+        <d v="2023-02-01T00:00:00"/>
+        <d v="2023-02-02T00:00:00"/>
+        <d v="2023-02-03T00:00:00"/>
+        <d v="2023-02-04T00:00:00"/>
+        <d v="2023-02-05T00:00:00"/>
+        <d v="2023-02-06T00:00:00"/>
+        <d v="2023-02-07T00:00:00"/>
+        <d v="2023-02-08T00:00:00"/>
+        <d v="2023-02-09T00:00:00"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Salesman" numFmtId="0">
       <sharedItems/>
@@ -366,7 +896,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="548194542"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -376,7 +906,7 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
   <r>
     <n v="1"/>
-    <d v="2023-01-01T00:00:00"/>
+    <x v="0"/>
     <s v="Ahmed Said"/>
     <s v="Cairo"/>
     <x v="0"/>
@@ -386,7 +916,7 @@
   </r>
   <r>
     <n v="2"/>
-    <d v="2023-01-02T00:00:00"/>
+    <x v="1"/>
     <s v="Ali Ramadan"/>
     <s v="Domietta"/>
     <x v="1"/>
@@ -396,7 +926,7 @@
   </r>
   <r>
     <n v="3"/>
-    <d v="2023-01-03T00:00:00"/>
+    <x v="2"/>
     <s v="Ashraf Zaki"/>
     <s v="Cairo"/>
     <x v="2"/>
@@ -406,7 +936,7 @@
   </r>
   <r>
     <n v="4"/>
-    <d v="2023-01-04T00:00:00"/>
+    <x v="3"/>
     <s v="Fathy Ali"/>
     <s v="Cairo"/>
     <x v="0"/>
@@ -416,7 +946,7 @@
   </r>
   <r>
     <n v="5"/>
-    <d v="2023-01-05T00:00:00"/>
+    <x v="4"/>
     <s v="Tamer Mohamed"/>
     <s v="Domietta"/>
     <x v="1"/>
@@ -426,7 +956,7 @@
   </r>
   <r>
     <n v="6"/>
-    <d v="2023-01-06T00:00:00"/>
+    <x v="5"/>
     <s v="Khaled Hassan"/>
     <s v="Domietta"/>
     <x v="3"/>
@@ -436,7 +966,7 @@
   </r>
   <r>
     <n v="7"/>
-    <d v="2023-01-07T00:00:00"/>
+    <x v="6"/>
     <s v="Ahmed Said"/>
     <s v="Giza"/>
     <x v="4"/>
@@ -446,7 +976,7 @@
   </r>
   <r>
     <n v="8"/>
-    <d v="2023-01-08T00:00:00"/>
+    <x v="7"/>
     <s v="Ali Ramadan"/>
     <s v="Domietta"/>
     <x v="3"/>
@@ -456,7 +986,7 @@
   </r>
   <r>
     <n v="9"/>
-    <d v="2023-01-09T00:00:00"/>
+    <x v="8"/>
     <s v="Ashraf Zaki"/>
     <s v="Alexandria"/>
     <x v="5"/>
@@ -466,7 +996,7 @@
   </r>
   <r>
     <n v="10"/>
-    <d v="2023-01-10T00:00:00"/>
+    <x v="9"/>
     <s v="Fathy Ali"/>
     <s v="Alexandria"/>
     <x v="2"/>
@@ -476,7 +1006,7 @@
   </r>
   <r>
     <n v="11"/>
-    <d v="2023-01-11T00:00:00"/>
+    <x v="10"/>
     <s v="Tamer Mohamed"/>
     <s v="Giza"/>
     <x v="2"/>
@@ -486,7 +1016,7 @@
   </r>
   <r>
     <n v="12"/>
-    <d v="2023-01-12T00:00:00"/>
+    <x v="11"/>
     <s v="Khaled Hassan"/>
     <s v="Alexandria"/>
     <x v="4"/>
@@ -496,7 +1026,7 @@
   </r>
   <r>
     <n v="13"/>
-    <d v="2023-01-13T00:00:00"/>
+    <x v="12"/>
     <s v="Ahmed Said"/>
     <s v="Giza"/>
     <x v="2"/>
@@ -506,7 +1036,7 @@
   </r>
   <r>
     <n v="14"/>
-    <d v="2023-01-14T00:00:00"/>
+    <x v="13"/>
     <s v="Ali Ramadan"/>
     <s v="Cairo"/>
     <x v="4"/>
@@ -516,7 +1046,7 @@
   </r>
   <r>
     <n v="15"/>
-    <d v="2023-01-15T00:00:00"/>
+    <x v="14"/>
     <s v="Ashraf Zaki"/>
     <s v="Domietta"/>
     <x v="2"/>
@@ -526,7 +1056,7 @@
   </r>
   <r>
     <n v="16"/>
-    <d v="2023-01-16T00:00:00"/>
+    <x v="15"/>
     <s v="Fathy Ali"/>
     <s v="Domietta"/>
     <x v="4"/>
@@ -536,7 +1066,7 @@
   </r>
   <r>
     <n v="17"/>
-    <d v="2023-01-17T00:00:00"/>
+    <x v="16"/>
     <s v="Tamer Mohamed"/>
     <s v="Domietta"/>
     <x v="2"/>
@@ -546,7 +1076,7 @@
   </r>
   <r>
     <n v="18"/>
-    <d v="2023-01-18T00:00:00"/>
+    <x v="17"/>
     <s v="Khaled Hassan"/>
     <s v="Alexandria"/>
     <x v="6"/>
@@ -556,7 +1086,7 @@
   </r>
   <r>
     <n v="19"/>
-    <d v="2023-01-19T00:00:00"/>
+    <x v="18"/>
     <s v="Ahmed Said"/>
     <s v="Domietta"/>
     <x v="7"/>
@@ -566,7 +1096,7 @@
   </r>
   <r>
     <n v="20"/>
-    <d v="2023-01-20T00:00:00"/>
+    <x v="19"/>
     <s v="Ali Ramadan"/>
     <s v="Domietta"/>
     <x v="4"/>
@@ -576,7 +1106,7 @@
   </r>
   <r>
     <n v="21"/>
-    <d v="2023-01-21T00:00:00"/>
+    <x v="20"/>
     <s v="Ashraf Zaki"/>
     <s v="Domietta"/>
     <x v="1"/>
@@ -586,7 +1116,7 @@
   </r>
   <r>
     <n v="22"/>
-    <d v="2023-01-22T00:00:00"/>
+    <x v="21"/>
     <s v="Fathy Ali"/>
     <s v="Giza"/>
     <x v="3"/>
@@ -596,7 +1126,7 @@
   </r>
   <r>
     <n v="23"/>
-    <d v="2023-01-23T00:00:00"/>
+    <x v="22"/>
     <s v="Tamer Mohamed"/>
     <s v="Domietta"/>
     <x v="7"/>
@@ -606,7 +1136,7 @@
   </r>
   <r>
     <n v="24"/>
-    <d v="2023-01-24T00:00:00"/>
+    <x v="23"/>
     <s v="Khaled Hassan"/>
     <s v="Domietta"/>
     <x v="0"/>
@@ -616,7 +1146,7 @@
   </r>
   <r>
     <n v="25"/>
-    <d v="2023-01-25T00:00:00"/>
+    <x v="24"/>
     <s v="Ahmed Said"/>
     <s v="Giza"/>
     <x v="4"/>
@@ -626,7 +1156,7 @@
   </r>
   <r>
     <n v="26"/>
-    <d v="2023-01-26T00:00:00"/>
+    <x v="25"/>
     <s v="Ali Ramadan"/>
     <s v="Domietta"/>
     <x v="7"/>
@@ -636,7 +1166,7 @@
   </r>
   <r>
     <n v="27"/>
-    <d v="2023-01-27T00:00:00"/>
+    <x v="26"/>
     <s v="Ashraf Zaki"/>
     <s v="Giza"/>
     <x v="3"/>
@@ -646,7 +1176,7 @@
   </r>
   <r>
     <n v="28"/>
-    <d v="2023-01-28T00:00:00"/>
+    <x v="27"/>
     <s v="Fathy Ali"/>
     <s v="Domietta"/>
     <x v="4"/>
@@ -656,7 +1186,7 @@
   </r>
   <r>
     <n v="29"/>
-    <d v="2023-01-29T00:00:00"/>
+    <x v="28"/>
     <s v="Tamer Mohamed"/>
     <s v="Domietta"/>
     <x v="4"/>
@@ -666,7 +1196,7 @@
   </r>
   <r>
     <n v="30"/>
-    <d v="2023-01-30T00:00:00"/>
+    <x v="29"/>
     <s v="Khaled Hassan"/>
     <s v="Giza"/>
     <x v="7"/>
@@ -676,7 +1206,7 @@
   </r>
   <r>
     <n v="31"/>
-    <d v="2023-01-31T00:00:00"/>
+    <x v="30"/>
     <s v="Ahmed Said"/>
     <s v="Domietta"/>
     <x v="6"/>
@@ -686,7 +1216,7 @@
   </r>
   <r>
     <n v="32"/>
-    <d v="2023-02-01T00:00:00"/>
+    <x v="31"/>
     <s v="Ali Ramadan"/>
     <s v="Cairo"/>
     <x v="2"/>
@@ -696,7 +1226,7 @@
   </r>
   <r>
     <n v="33"/>
-    <d v="2023-02-02T00:00:00"/>
+    <x v="32"/>
     <s v="Ashraf Zaki"/>
     <s v="Domietta"/>
     <x v="3"/>
@@ -706,7 +1236,7 @@
   </r>
   <r>
     <n v="34"/>
-    <d v="2023-02-03T00:00:00"/>
+    <x v="33"/>
     <s v="Fathy Ali"/>
     <s v="Giza"/>
     <x v="3"/>
@@ -716,7 +1246,7 @@
   </r>
   <r>
     <n v="35"/>
-    <d v="2023-02-04T00:00:00"/>
+    <x v="34"/>
     <s v="Tamer Mohamed"/>
     <s v="Alexandria"/>
     <x v="0"/>
@@ -726,7 +1256,7 @@
   </r>
   <r>
     <n v="36"/>
-    <d v="2023-02-05T00:00:00"/>
+    <x v="35"/>
     <s v="Khaled Hassan"/>
     <s v="Alexandria"/>
     <x v="7"/>
@@ -736,7 +1266,7 @@
   </r>
   <r>
     <n v="37"/>
-    <d v="2023-02-06T00:00:00"/>
+    <x v="36"/>
     <s v="Ahmed Said"/>
     <s v="Alexandria"/>
     <x v="3"/>
@@ -746,7 +1276,7 @@
   </r>
   <r>
     <n v="38"/>
-    <d v="2023-02-07T00:00:00"/>
+    <x v="37"/>
     <s v="Ali Ramadan"/>
     <s v="Giza"/>
     <x v="0"/>
@@ -756,7 +1286,7 @@
   </r>
   <r>
     <n v="39"/>
-    <d v="2023-02-08T00:00:00"/>
+    <x v="38"/>
     <s v="Ashraf Zaki"/>
     <s v="Domietta"/>
     <x v="2"/>
@@ -766,7 +1296,7 @@
   </r>
   <r>
     <n v="40"/>
-    <d v="2023-02-09T00:00:00"/>
+    <x v="39"/>
     <s v="Fathy Ali"/>
     <s v="Domietta"/>
     <x v="5"/>
@@ -778,11 +1308,55 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -844,11 +1418,28 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="40" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -861,11 +1452,55 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0">
@@ -927,11 +1562,28 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="8">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="33" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -944,11 +1596,55 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -1010,11 +1706,28 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="9">
+    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="33" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -1048,10 +1761,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="42"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -1376,14 +2089,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC7FC4E-8D9E-4A1E-BCC5-B9D37254EE36}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1649C905-6944-4F98-B4AE-37BE068CDF30}">
-  <dimension ref="A2:E6"/>
+  <dimension ref="A2:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1414,6 +2137,19 @@
         <v>40</v>
       </c>
       <c r="E6" s="4">
+        <v>10663.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>426530</v>
+      </c>
+      <c r="C7">
+        <f>GETPIVOTDATA("Item",$C$5)</f>
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <f>GETPIVOTDATA("Amount",$E$5)</f>
         <v>10663.25</v>
       </c>
     </row>
@@ -1425,7 +2161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF8A719-9DE1-494C-AEC9-6B8400C82FA6}">
   <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2514,7 +3250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D1B5A55-B004-4FDC-90CE-889382A104E7}">
   <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4E5FC3-6B2B-4A22-B5EE-17907C860EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335AA08A-0D72-4D1E-B270-56EB7B506255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
   <sheets>
     <sheet name="dashboard" sheetId="4" r:id="rId1"/>
@@ -779,6 +779,156 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Graphic 5" descr="Money with solid fill">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAD87EE3-6A2A-DAE4-1F6A-4CBB4C810A49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2522220" y="838200"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Graphic 7" descr="Bar chart with solid fill">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D3243E3-E0D5-78A8-0AF9-066946EF9BEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5242560" y="845820"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Graphic 9" descr="Coins with solid fill">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820BEEF1-CD67-BB33-C74D-0C2F9D4BEFEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7993380" y="838200"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335AA08A-0D72-4D1E-B270-56EB7B506255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B859417-3B23-43F2-8931-D4E9E3C95B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -20,12 +20,21 @@
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">table!$A$1:$H$41</definedName>
+    <definedName name="NativeTimeline_Date">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="5" r:id="rId5"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
+      <x15:timelineCacheRefs>
+        <x15:timelineCacheRef r:id="rId6"/>
+      </x15:timelineCacheRefs>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -199,7 +208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -209,12 +218,524 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="119">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -538,397 +1059,571 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>18358</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>594360</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>141663</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="'data analysis'!A7">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="12" name="Group 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{298D81AF-3522-AE4E-1E11-5B9B0E9C0C11}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F77C03-3584-0089-DE88-7E7005622D0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2385060" y="701040"/>
-          <a:ext cx="1866900" cy="739140"/>
+          <a:off x="2438400" y="1664278"/>
+          <a:ext cx="1866900" cy="671945"/>
+          <a:chOff x="2385060" y="701040"/>
+          <a:chExt cx="1866900" cy="739140"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="'data analysis'!A7">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="TextBox 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{298D81AF-3522-AE4E-1E11-5B9B0E9C0C11}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2385060" y="701040"/>
+            <a:ext cx="1866900" cy="739140"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="95000"/>
             </a:schemeClr>
           </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:fld id="{E579ED93-EF0A-42B5-9B0D-24E1CFD28BCA}" type="TxLink">
-            <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr algn="r"/>
-            <a:t> $426,530 </a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2000" b="1">
-            <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+            <a:fld id="{E579ED93-EF0A-42B5-9B0D-24E1CFD28BCA}" type="TxLink">
+              <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:pPr algn="r"/>
+              <a:t> $290,180 </a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2000" b="1">
+              <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="6" name="Graphic 5" descr="Money with solid fill">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAD87EE3-6A2A-DAE4-1F6A-4CBB4C810A49}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2522220" y="838200"/>
+            <a:ext cx="457200" cy="457200"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>240030</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>293370</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>18358</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>278130</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:colOff>331470</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>141663</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="'data analysis'!C7">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="13" name="Group 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E128FE5D-66DC-2A53-2918-C5B556CBB598}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C648A276-A127-552E-5911-9F55C081F05D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5116830" y="701040"/>
-          <a:ext cx="1866900" cy="739140"/>
+          <a:off x="5170170" y="1664278"/>
+          <a:ext cx="1866900" cy="671945"/>
+          <a:chOff x="5116830" y="701040"/>
+          <a:chExt cx="1866900" cy="739140"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="'data analysis'!C7">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="3" name="TextBox 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E128FE5D-66DC-2A53-2918-C5B556CBB598}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5116830" y="701040"/>
+            <a:ext cx="1866900" cy="739140"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="95000"/>
             </a:schemeClr>
           </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:fld id="{CAE52DA5-E783-42D2-873D-9F631120CFC5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="r"/>
+            <a:fld id="{CAE52DA5-E783-42D2-873D-9F631120CFC5}" type="TxLink">
+              <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+              </a:rPr>
+              <a:pPr algn="r"/>
+              <a:t>31</a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="+mj-lt"/>
-            </a:rPr>
-            <a:pPr algn="r"/>
-            <a:t>40</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2000" b="1">
-            <a:latin typeface="+mj-lt"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="8" name="Graphic 7" descr="Bar chart with solid fill">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D3243E3-E0D5-78A8-0AF9-066946EF9BEF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5242560" y="845820"/>
+            <a:ext cx="457200" cy="457200"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>18358</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>141663</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="'data analysis'!E7">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="14" name="Group 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CF5D85A-1B58-1E0F-6ECB-D976385F9B60}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3285620-29D6-1D96-4D9D-BAAF38A9912E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7848600" y="701040"/>
-          <a:ext cx="1866900" cy="739140"/>
+          <a:off x="7901940" y="1664278"/>
+          <a:ext cx="1866900" cy="671945"/>
+          <a:chOff x="7848600" y="734638"/>
+          <a:chExt cx="1866900" cy="671945"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="'data analysis'!E7">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="TextBox 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CF5D85A-1B58-1E0F-6ECB-D976385F9B60}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7848600" y="734638"/>
+            <a:ext cx="1866900" cy="671945"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
           <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="95000"/>
             </a:schemeClr>
           </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:fld id="{5705C105-A208-49EE-830A-EA84537AE66E}" type="TxLink">
-            <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>10663.25</a:t>
-          </a:fld>
-          <a:endParaRPr lang="en-US" sz="2000" b="1">
-            <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="r"/>
+            <a:fld id="{5705C105-A208-49EE-830A-EA84537AE66E}" type="TxLink">
+              <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>9361</a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2000" b="1">
+              <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="10" name="Graphic 9" descr="Coins with solid fill">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820BEEF1-CD67-BB33-C74D-0C2F9D4BEFEB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7947660" y="838200"/>
+            <a:ext cx="457200" cy="457200"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>541020</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Graphic 5" descr="Money with solid fill">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAD87EE3-6A2A-DAE4-1F6A-4CBB4C810A49}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2522220" y="838200"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="11" name="Date 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48BEA061-2CC9-40DD-9566-8F872D9BD8FD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2430780" y="144780"/>
+              <a:ext cx="7322820" cy="1196340"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Graphic 7" descr="Bar chart with solid fill">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D3243E3-E0D5-78A8-0AF9-066946EF9BEF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5242560" y="845820"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Graphic 9" descr="Coins with solid fill">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820BEEF1-CD67-BB33-C74D-0C2F9D4BEFEB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7993380" y="838200"/>
-          <a:ext cx="457200" cy="457200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Date">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{712F1F2D-AA36-429E-889B-E6B299DD56A9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4663440" y="937260"/>
+              <a:ext cx="3337560" cy="1181100"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>Timeline: Works in Excel 2013 or higher. Do not move or resize.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1568,13 +2263,13 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="36">
+    <format dxfId="112">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="40" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="188" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -1712,13 +2407,13 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="40">
+    <format dxfId="113">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="33" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="181" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -1856,13 +2551,13 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="41">
+    <format dxfId="114">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="33" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="181" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -1911,10 +2606,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="118"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="117"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="116"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="115"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -2238,6 +2933,32 @@
 </a:theme>
 </file>
 
+<file path=xl/timelineCaches/timelineCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="NativeTimeline_Date" xr10:uid="{1A08CDD6-FD3D-453E-AB64-7E0795993188}" sourceName="Date">
+  <pivotTables>
+    <pivotTable tabId="3" name="PivotTable2"/>
+    <pivotTable tabId="3" name="PivotTable1"/>
+    <pivotTable tabId="3" name="PivotTable3"/>
+  </pivotTables>
+  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="548194542" filterType="dateBetween">
+    <selection startDate="2023-01-01T00:00:00" endDate="2023-01-31T00:00:00"/>
+    <bounds startDate="2023-01-01T00:00:00" endDate="2024-01-01T00:00:00"/>
+  </state>
+</timelineCacheDefinition>
+</file>
+
+<file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
+<timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <timeline name="Date 1" xr10:uid="{4BAC2FE9-C0D7-4F7A-AA2C-A32B2D77E7A4}" cache="NativeTimeline_Date" caption="Date" showHorizontalScrollbar="0" level="2" selectionLevel="2" scrollPosition="2023-01-01T00:00:00" style="TimeSlicerStyleDark1"/>
+</timelines>
+</file>
+
+<file path=xl/timelines/timeline2.xml><?xml version="1.0" encoding="utf-8"?>
+<timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <timeline name="Date" xr10:uid="{8BE855AF-BCA8-4844-9C58-AD1748EA83F3}" cache="NativeTimeline_Date" caption="Date" showHorizontalScrollbar="0" level="2" selectionLevel="2" scrollPosition="2023-01-01T00:00:00"/>
+</timelines>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC7FC4E-8D9E-4A1E-BCC5-B9D37254EE36}">
   <dimension ref="A1"/>
@@ -2245,6 +2966,13 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
+      <x15:timelineRefs>
+        <x15:timelineRef r:id="rId2"/>
+      </x15:timelineRefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -2253,10 +2981,10 @@
   <dimension ref="A2:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2281,26 +3009,27 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
-        <v>426530</v>
+        <v>290180</v>
       </c>
       <c r="C6" s="4">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E6" s="4">
-        <v>10663.25</v>
+        <v>9360.645161290322</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
-        <v>426530</v>
+        <f>GETPIVOTDATA("Amount",$A$5)</f>
+        <v>290180</v>
       </c>
       <c r="C7">
         <f>GETPIVOTDATA("Item",$C$5)</f>
-        <v>40</v>
-      </c>
-      <c r="E7">
+        <v>31</v>
+      </c>
+      <c r="E7" s="7">
         <f>GETPIVOTDATA("Amount",$E$5)</f>
-        <v>10663.25</v>
+        <v>9360.645161290322</v>
       </c>
     </row>
   </sheetData>
@@ -2308,6 +3037,14 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
+      <x15:timelineRefs>
+        <x15:timelineRef r:id="rId5"/>
+      </x15:timelineRefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B859417-3B23-43F2-8931-D4E9E3C95B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84242AE8-80D1-469E-B6CB-B148ADC83800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="6" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="35">
   <si>
     <t>S No</t>
   </si>
@@ -145,6 +145,15 @@
     <t>Keyboard</t>
   </si>
   <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
+  <si>
     <t>TOTAL SALES</t>
   </si>
   <si>
@@ -155,6 +164,12 @@
   </si>
   <si>
     <t>KPIS</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
   </si>
 </sst>
 </file>
@@ -208,11 +223,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -224,7 +243,168 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="119">
+  <dxfs count="142">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1053,6 +1233,4675 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[0B5F9D00.xlsx]data analysis!PivotTable5</c:name>
+    <c:fmtId val="2"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>sales</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> by months</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data analysis'!$I$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data analysis'!$H$6:$H$8</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data analysis'!$I$6:$I$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>290180</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>136350</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-32D4-4D15-873C-9CE162229622}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1216137871"/>
+        <c:axId val="1216138351"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1216137871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1216138351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1216138351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1216137871"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[0B5F9D00.xlsx]data analysis!PivotTable6</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:dlblFieldTable/>
+              <c15:showDataLabelsRange val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="4.0774719673802244E-2"/>
+              <c:y val="-9.7222222222222238E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:fld id="{8F04FACA-BB3F-456F-978F-18AE092E4DB8}" type="CELLRANGE">
+                  <a:rPr lang="en-US"/>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:t>[CELLRANGE]</a:t>
+                </a:fld>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>, </a:t>
+                </a:r>
+                <a:fld id="{6C4A9361-0318-4687-8174-06F0597D5D29}" type="PERCENTAGE">
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:t>[PERCENTAGE]</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" baseline="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:dlblFieldTable/>
+              <c15:showDataLabelsRange val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0.12742099898063192"/>
+              <c:y val="-7.8703703703703748E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:fld id="{E8EA7B26-7E78-4AC7-BBF5-D1085E5A7553}" type="CELLRANGE">
+                  <a:rPr lang="en-US"/>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:t>[CELLRANGE]</a:t>
+                </a:fld>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>, </a:t>
+                </a:r>
+                <a:fld id="{5FFDEAF5-0A11-4A88-87D1-98907541AF9D}" type="PERCENTAGE">
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:t>[PERCENTAGE]</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" baseline="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:dlblFieldTable/>
+              <c15:showDataLabelsRange val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="8.1549439347604488E-2"/>
+              <c:y val="0.12037037037037028"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:fld id="{089C05EC-B45A-4671-B50E-34574E5C55A6}" type="CELLRANGE">
+                  <a:rPr lang="en-US"/>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:t>[CELLRANGE]</a:t>
+                </a:fld>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>, </a:t>
+                </a:r>
+                <a:fld id="{50D51559-626D-4A36-BB8E-3999BA1A592C}" type="PERCENTAGE">
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:t>[PERCENTAGE]</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" baseline="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:dlblFieldTable/>
+              <c15:showDataLabelsRange val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="-9.1743119266055051E-2"/>
+              <c:y val="9.722222222222214E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:fld id="{53B4288B-A224-48D5-A844-84B01B96274D}" type="CELLRANGE">
+                  <a:rPr lang="en-US"/>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:t>[CELLRANGE]</a:t>
+                </a:fld>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>, </a:t>
+                </a:r>
+                <a:fld id="{FBF05BD7-46BE-452E-B85F-5AA2B1D5BC3C}" type="PERCENTAGE">
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:pPr>
+                    <a:defRPr/>
+                  </a:pPr>
+                  <a:t>[PERCENTAGE]</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" baseline="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:dlblFieldTable/>
+              <c15:showDataLabelsRange val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data analysis'!$H$21:$H$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-176F-40FB-A8D7-950581BCD903}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-176F-40FB-A8D7-950581BCD903}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-176F-40FB-A8D7-950581BCD903}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-176F-40FB-A8D7-950581BCD903}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.0774719673802244E-2"/>
+                  <c:y val="-9.7222222222222238E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{8F04FACA-BB3F-456F-978F-18AE092E4DB8}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{6C4A9361-0318-4687-8174-06F0597D5D29}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[PERCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-176F-40FB-A8D7-950581BCD903}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.12742099898063192"/>
+                  <c:y val="-7.8703703703703748E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E8EA7B26-7E78-4AC7-BBF5-D1085E5A7553}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{5FFDEAF5-0A11-4A88-87D1-98907541AF9D}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[PERCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-176F-40FB-A8D7-950581BCD903}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.1549439347604488E-2"/>
+                  <c:y val="0.12037037037037028"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{089C05EC-B45A-4671-B50E-34574E5C55A6}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{50D51559-626D-4A36-BB8E-3999BA1A592C}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[PERCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-176F-40FB-A8D7-950581BCD903}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-9.1743119266055051E-2"/>
+                  <c:y val="9.722222222222214E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{53B4288B-A224-48D5-A844-84B01B96274D}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{FBF05BD7-46BE-452E-B85F-5AA2B1D5BC3C}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[PERCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-176F-40FB-A8D7-950581BCD903}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data analysis'!$H$21:$H$24</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alexandria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cairo</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Domietta</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Giza</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data analysis'!$H$21:$H$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>38300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24270</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>155450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>208510</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'data analysis'!$H$21:$H$24</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="4"/>
+                  <c:pt idx="0">
+                    <c:v>Alexandria</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Cairo</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Domietta</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Giza</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-176F-40FB-A8D7-950581BCD903}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[0B5F9D00.xlsx]data analysis!PivotTable5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data analysis'!$I$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data analysis'!$H$6:$H$8</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data analysis'!$I$6:$I$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>290180</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>136350</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CF70-42B1-9B26-8E6C39327083}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1216137871"/>
+        <c:axId val="1216138351"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1216137871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1216138351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1216138351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1216137871"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[0B5F9D00.xlsx]data analysis!PivotTable6</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data analysis'!$I$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data analysis'!$H$21:$H$25</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Alexandria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cairo</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Domietta</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Giza</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data analysis'!$I$21:$I$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>38300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24270</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>155450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>208510</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C1B3-46DC-BCB9-EEF66AC136DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1148,7 +5997,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t> $290,180 </a:t>
+              <a:t> $426,530 </a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -1285,7 +6134,7 @@
                 <a:latin typeface="+mj-lt"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>31</a:t>
+              <a:t>40</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="+mj-lt"/>
@@ -1421,7 +6270,7 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
-              <a:t>9361</a:t>
+              <a:t>10663</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -1544,6 +6393,82 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94815654-BF95-431E-9CD7-EFEB4F4A5D8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="16" name="Chart 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86A1A43B-B5D6-4312-8078-A26775AC0B97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1551,16 +6476,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
@@ -1596,7 +6521,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4663440" y="937260"/>
+              <a:off x="11376660" y="1333500"/>
               <a:ext cx="3337560" cy="1181100"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1626,6 +6551,78 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C5959A1-3B9A-CB8F-1D33-63BFD6A5D488}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16128143-2187-D852-FA66-B541680348E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1634,7 +6631,7 @@
   <cacheSource type="worksheet">
     <worksheetSource name="sales"/>
   </cacheSource>
-  <cacheFields count="8">
+  <cacheFields count="10">
     <cacheField name="S No" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="40"/>
     </cacheField>
@@ -1681,12 +6678,18 @@
         <d v="2023-02-08T00:00:00"/>
         <d v="2023-02-09T00:00:00"/>
       </sharedItems>
+      <fieldGroup par="9"/>
     </cacheField>
     <cacheField name="Salesman" numFmtId="0">
       <sharedItems/>
     </cacheField>
     <cacheField name="Region" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="4">
+        <s v="Cairo"/>
+        <s v="Domietta"/>
+        <s v="Giza"/>
+        <s v="Alexandria"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Item" numFmtId="0">
       <sharedItems count="8">
@@ -1738,6 +6741,402 @@
         <n v="7200"/>
       </sharedItems>
     </cacheField>
+    <cacheField name="Days (Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="days" startDate="2023-01-01T00:00:00" endDate="2023-02-10T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;1/1/2023"/>
+          <s v="1-Jan"/>
+          <s v="2-Jan"/>
+          <s v="3-Jan"/>
+          <s v="4-Jan"/>
+          <s v="5-Jan"/>
+          <s v="6-Jan"/>
+          <s v="7-Jan"/>
+          <s v="8-Jan"/>
+          <s v="9-Jan"/>
+          <s v="10-Jan"/>
+          <s v="11-Jan"/>
+          <s v="12-Jan"/>
+          <s v="13-Jan"/>
+          <s v="14-Jan"/>
+          <s v="15-Jan"/>
+          <s v="16-Jan"/>
+          <s v="17-Jan"/>
+          <s v="18-Jan"/>
+          <s v="19-Jan"/>
+          <s v="20-Jan"/>
+          <s v="21-Jan"/>
+          <s v="22-Jan"/>
+          <s v="23-Jan"/>
+          <s v="24-Jan"/>
+          <s v="25-Jan"/>
+          <s v="26-Jan"/>
+          <s v="27-Jan"/>
+          <s v="28-Jan"/>
+          <s v="29-Jan"/>
+          <s v="30-Jan"/>
+          <s v="31-Jan"/>
+          <s v="1-Feb"/>
+          <s v="2-Feb"/>
+          <s v="3-Feb"/>
+          <s v="4-Feb"/>
+          <s v="5-Feb"/>
+          <s v="6-Feb"/>
+          <s v="7-Feb"/>
+          <s v="8-Feb"/>
+          <s v="9-Feb"/>
+          <s v="10-Feb"/>
+          <s v="11-Feb"/>
+          <s v="12-Feb"/>
+          <s v="13-Feb"/>
+          <s v="14-Feb"/>
+          <s v="15-Feb"/>
+          <s v="16-Feb"/>
+          <s v="17-Feb"/>
+          <s v="18-Feb"/>
+          <s v="19-Feb"/>
+          <s v="20-Feb"/>
+          <s v="21-Feb"/>
+          <s v="22-Feb"/>
+          <s v="23-Feb"/>
+          <s v="24-Feb"/>
+          <s v="25-Feb"/>
+          <s v="26-Feb"/>
+          <s v="27-Feb"/>
+          <s v="28-Feb"/>
+          <s v="29-Feb"/>
+          <s v="1-Mar"/>
+          <s v="2-Mar"/>
+          <s v="3-Mar"/>
+          <s v="4-Mar"/>
+          <s v="5-Mar"/>
+          <s v="6-Mar"/>
+          <s v="7-Mar"/>
+          <s v="8-Mar"/>
+          <s v="9-Mar"/>
+          <s v="10-Mar"/>
+          <s v="11-Mar"/>
+          <s v="12-Mar"/>
+          <s v="13-Mar"/>
+          <s v="14-Mar"/>
+          <s v="15-Mar"/>
+          <s v="16-Mar"/>
+          <s v="17-Mar"/>
+          <s v="18-Mar"/>
+          <s v="19-Mar"/>
+          <s v="20-Mar"/>
+          <s v="21-Mar"/>
+          <s v="22-Mar"/>
+          <s v="23-Mar"/>
+          <s v="24-Mar"/>
+          <s v="25-Mar"/>
+          <s v="26-Mar"/>
+          <s v="27-Mar"/>
+          <s v="28-Mar"/>
+          <s v="29-Mar"/>
+          <s v="30-Mar"/>
+          <s v="31-Mar"/>
+          <s v="1-Apr"/>
+          <s v="2-Apr"/>
+          <s v="3-Apr"/>
+          <s v="4-Apr"/>
+          <s v="5-Apr"/>
+          <s v="6-Apr"/>
+          <s v="7-Apr"/>
+          <s v="8-Apr"/>
+          <s v="9-Apr"/>
+          <s v="10-Apr"/>
+          <s v="11-Apr"/>
+          <s v="12-Apr"/>
+          <s v="13-Apr"/>
+          <s v="14-Apr"/>
+          <s v="15-Apr"/>
+          <s v="16-Apr"/>
+          <s v="17-Apr"/>
+          <s v="18-Apr"/>
+          <s v="19-Apr"/>
+          <s v="20-Apr"/>
+          <s v="21-Apr"/>
+          <s v="22-Apr"/>
+          <s v="23-Apr"/>
+          <s v="24-Apr"/>
+          <s v="25-Apr"/>
+          <s v="26-Apr"/>
+          <s v="27-Apr"/>
+          <s v="28-Apr"/>
+          <s v="29-Apr"/>
+          <s v="30-Apr"/>
+          <s v="1-May"/>
+          <s v="2-May"/>
+          <s v="3-May"/>
+          <s v="4-May"/>
+          <s v="5-May"/>
+          <s v="6-May"/>
+          <s v="7-May"/>
+          <s v="8-May"/>
+          <s v="9-May"/>
+          <s v="10-May"/>
+          <s v="11-May"/>
+          <s v="12-May"/>
+          <s v="13-May"/>
+          <s v="14-May"/>
+          <s v="15-May"/>
+          <s v="16-May"/>
+          <s v="17-May"/>
+          <s v="18-May"/>
+          <s v="19-May"/>
+          <s v="20-May"/>
+          <s v="21-May"/>
+          <s v="22-May"/>
+          <s v="23-May"/>
+          <s v="24-May"/>
+          <s v="25-May"/>
+          <s v="26-May"/>
+          <s v="27-May"/>
+          <s v="28-May"/>
+          <s v="29-May"/>
+          <s v="30-May"/>
+          <s v="31-May"/>
+          <s v="1-Jun"/>
+          <s v="2-Jun"/>
+          <s v="3-Jun"/>
+          <s v="4-Jun"/>
+          <s v="5-Jun"/>
+          <s v="6-Jun"/>
+          <s v="7-Jun"/>
+          <s v="8-Jun"/>
+          <s v="9-Jun"/>
+          <s v="10-Jun"/>
+          <s v="11-Jun"/>
+          <s v="12-Jun"/>
+          <s v="13-Jun"/>
+          <s v="14-Jun"/>
+          <s v="15-Jun"/>
+          <s v="16-Jun"/>
+          <s v="17-Jun"/>
+          <s v="18-Jun"/>
+          <s v="19-Jun"/>
+          <s v="20-Jun"/>
+          <s v="21-Jun"/>
+          <s v="22-Jun"/>
+          <s v="23-Jun"/>
+          <s v="24-Jun"/>
+          <s v="25-Jun"/>
+          <s v="26-Jun"/>
+          <s v="27-Jun"/>
+          <s v="28-Jun"/>
+          <s v="29-Jun"/>
+          <s v="30-Jun"/>
+          <s v="1-Jul"/>
+          <s v="2-Jul"/>
+          <s v="3-Jul"/>
+          <s v="4-Jul"/>
+          <s v="5-Jul"/>
+          <s v="6-Jul"/>
+          <s v="7-Jul"/>
+          <s v="8-Jul"/>
+          <s v="9-Jul"/>
+          <s v="10-Jul"/>
+          <s v="11-Jul"/>
+          <s v="12-Jul"/>
+          <s v="13-Jul"/>
+          <s v="14-Jul"/>
+          <s v="15-Jul"/>
+          <s v="16-Jul"/>
+          <s v="17-Jul"/>
+          <s v="18-Jul"/>
+          <s v="19-Jul"/>
+          <s v="20-Jul"/>
+          <s v="21-Jul"/>
+          <s v="22-Jul"/>
+          <s v="23-Jul"/>
+          <s v="24-Jul"/>
+          <s v="25-Jul"/>
+          <s v="26-Jul"/>
+          <s v="27-Jul"/>
+          <s v="28-Jul"/>
+          <s v="29-Jul"/>
+          <s v="30-Jul"/>
+          <s v="31-Jul"/>
+          <s v="1-Aug"/>
+          <s v="2-Aug"/>
+          <s v="3-Aug"/>
+          <s v="4-Aug"/>
+          <s v="5-Aug"/>
+          <s v="6-Aug"/>
+          <s v="7-Aug"/>
+          <s v="8-Aug"/>
+          <s v="9-Aug"/>
+          <s v="10-Aug"/>
+          <s v="11-Aug"/>
+          <s v="12-Aug"/>
+          <s v="13-Aug"/>
+          <s v="14-Aug"/>
+          <s v="15-Aug"/>
+          <s v="16-Aug"/>
+          <s v="17-Aug"/>
+          <s v="18-Aug"/>
+          <s v="19-Aug"/>
+          <s v="20-Aug"/>
+          <s v="21-Aug"/>
+          <s v="22-Aug"/>
+          <s v="23-Aug"/>
+          <s v="24-Aug"/>
+          <s v="25-Aug"/>
+          <s v="26-Aug"/>
+          <s v="27-Aug"/>
+          <s v="28-Aug"/>
+          <s v="29-Aug"/>
+          <s v="30-Aug"/>
+          <s v="31-Aug"/>
+          <s v="1-Sep"/>
+          <s v="2-Sep"/>
+          <s v="3-Sep"/>
+          <s v="4-Sep"/>
+          <s v="5-Sep"/>
+          <s v="6-Sep"/>
+          <s v="7-Sep"/>
+          <s v="8-Sep"/>
+          <s v="9-Sep"/>
+          <s v="10-Sep"/>
+          <s v="11-Sep"/>
+          <s v="12-Sep"/>
+          <s v="13-Sep"/>
+          <s v="14-Sep"/>
+          <s v="15-Sep"/>
+          <s v="16-Sep"/>
+          <s v="17-Sep"/>
+          <s v="18-Sep"/>
+          <s v="19-Sep"/>
+          <s v="20-Sep"/>
+          <s v="21-Sep"/>
+          <s v="22-Sep"/>
+          <s v="23-Sep"/>
+          <s v="24-Sep"/>
+          <s v="25-Sep"/>
+          <s v="26-Sep"/>
+          <s v="27-Sep"/>
+          <s v="28-Sep"/>
+          <s v="29-Sep"/>
+          <s v="30-Sep"/>
+          <s v="1-Oct"/>
+          <s v="2-Oct"/>
+          <s v="3-Oct"/>
+          <s v="4-Oct"/>
+          <s v="5-Oct"/>
+          <s v="6-Oct"/>
+          <s v="7-Oct"/>
+          <s v="8-Oct"/>
+          <s v="9-Oct"/>
+          <s v="10-Oct"/>
+          <s v="11-Oct"/>
+          <s v="12-Oct"/>
+          <s v="13-Oct"/>
+          <s v="14-Oct"/>
+          <s v="15-Oct"/>
+          <s v="16-Oct"/>
+          <s v="17-Oct"/>
+          <s v="18-Oct"/>
+          <s v="19-Oct"/>
+          <s v="20-Oct"/>
+          <s v="21-Oct"/>
+          <s v="22-Oct"/>
+          <s v="23-Oct"/>
+          <s v="24-Oct"/>
+          <s v="25-Oct"/>
+          <s v="26-Oct"/>
+          <s v="27-Oct"/>
+          <s v="28-Oct"/>
+          <s v="29-Oct"/>
+          <s v="30-Oct"/>
+          <s v="31-Oct"/>
+          <s v="1-Nov"/>
+          <s v="2-Nov"/>
+          <s v="3-Nov"/>
+          <s v="4-Nov"/>
+          <s v="5-Nov"/>
+          <s v="6-Nov"/>
+          <s v="7-Nov"/>
+          <s v="8-Nov"/>
+          <s v="9-Nov"/>
+          <s v="10-Nov"/>
+          <s v="11-Nov"/>
+          <s v="12-Nov"/>
+          <s v="13-Nov"/>
+          <s v="14-Nov"/>
+          <s v="15-Nov"/>
+          <s v="16-Nov"/>
+          <s v="17-Nov"/>
+          <s v="18-Nov"/>
+          <s v="19-Nov"/>
+          <s v="20-Nov"/>
+          <s v="21-Nov"/>
+          <s v="22-Nov"/>
+          <s v="23-Nov"/>
+          <s v="24-Nov"/>
+          <s v="25-Nov"/>
+          <s v="26-Nov"/>
+          <s v="27-Nov"/>
+          <s v="28-Nov"/>
+          <s v="29-Nov"/>
+          <s v="30-Nov"/>
+          <s v="1-Dec"/>
+          <s v="2-Dec"/>
+          <s v="3-Dec"/>
+          <s v="4-Dec"/>
+          <s v="5-Dec"/>
+          <s v="6-Dec"/>
+          <s v="7-Dec"/>
+          <s v="8-Dec"/>
+          <s v="9-Dec"/>
+          <s v="10-Dec"/>
+          <s v="11-Dec"/>
+          <s v="12-Dec"/>
+          <s v="13-Dec"/>
+          <s v="14-Dec"/>
+          <s v="15-Dec"/>
+          <s v="16-Dec"/>
+          <s v="17-Dec"/>
+          <s v="18-Dec"/>
+          <s v="19-Dec"/>
+          <s v="20-Dec"/>
+          <s v="21-Dec"/>
+          <s v="22-Dec"/>
+          <s v="23-Dec"/>
+          <s v="24-Dec"/>
+          <s v="25-Dec"/>
+          <s v="26-Dec"/>
+          <s v="27-Dec"/>
+          <s v="28-Dec"/>
+          <s v="29-Dec"/>
+          <s v="30-Dec"/>
+          <s v="31-Dec"/>
+          <s v="&gt;2/10/2023"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Months (Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="months" startDate="2023-01-01T00:00:00" endDate="2023-02-10T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;1/1/2023"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;2/10/2023"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -1753,7 +7152,7 @@
     <n v="1"/>
     <x v="0"/>
     <s v="Ahmed Said"/>
-    <s v="Cairo"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="5"/>
     <n v="210"/>
@@ -1763,7 +7162,7 @@
     <n v="2"/>
     <x v="1"/>
     <s v="Ali Ramadan"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="3"/>
     <n v="1500"/>
@@ -1773,7 +7172,7 @@
     <n v="3"/>
     <x v="2"/>
     <s v="Ashraf Zaki"/>
-    <s v="Cairo"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="7"/>
     <n v="2100"/>
@@ -1783,7 +7182,7 @@
     <n v="4"/>
     <x v="3"/>
     <s v="Fathy Ali"/>
-    <s v="Cairo"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="2"/>
     <n v="210"/>
@@ -1793,7 +7192,7 @@
     <n v="5"/>
     <x v="4"/>
     <s v="Tamer Mohamed"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="1"/>
     <n v="1500"/>
@@ -1803,7 +7202,7 @@
     <n v="6"/>
     <x v="5"/>
     <s v="Khaled Hassan"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="4"/>
     <n v="8500"/>
@@ -1813,7 +7212,7 @@
     <n v="7"/>
     <x v="6"/>
     <s v="Ahmed Said"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="4"/>
     <n v="1"/>
     <n v="300"/>
@@ -1823,7 +7222,7 @@
     <n v="8"/>
     <x v="7"/>
     <s v="Ali Ramadan"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="6"/>
     <n v="8500"/>
@@ -1833,7 +7232,7 @@
     <n v="9"/>
     <x v="8"/>
     <s v="Ashraf Zaki"/>
-    <s v="Alexandria"/>
+    <x v="3"/>
     <x v="5"/>
     <n v="4"/>
     <n v="1200"/>
@@ -1843,7 +7242,7 @@
     <n v="10"/>
     <x v="9"/>
     <s v="Fathy Ali"/>
-    <s v="Alexandria"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="2"/>
     <n v="2100"/>
@@ -1853,7 +7252,7 @@
     <n v="11"/>
     <x v="10"/>
     <s v="Tamer Mohamed"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="6"/>
     <n v="2100"/>
@@ -1863,7 +7262,7 @@
     <n v="12"/>
     <x v="11"/>
     <s v="Khaled Hassan"/>
-    <s v="Alexandria"/>
+    <x v="3"/>
     <x v="4"/>
     <n v="1"/>
     <n v="300"/>
@@ -1873,7 +7272,7 @@
     <n v="13"/>
     <x v="12"/>
     <s v="Ahmed Said"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="7"/>
     <n v="2100"/>
@@ -1883,7 +7282,7 @@
     <n v="14"/>
     <x v="13"/>
     <s v="Ali Ramadan"/>
-    <s v="Cairo"/>
+    <x v="0"/>
     <x v="4"/>
     <n v="6"/>
     <n v="300"/>
@@ -1893,7 +7292,7 @@
     <n v="15"/>
     <x v="14"/>
     <s v="Ashraf Zaki"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="1"/>
     <n v="2100"/>
@@ -1903,7 +7302,7 @@
     <n v="16"/>
     <x v="15"/>
     <s v="Fathy Ali"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="2"/>
     <n v="300"/>
@@ -1913,7 +7312,7 @@
     <n v="17"/>
     <x v="16"/>
     <s v="Tamer Mohamed"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="7"/>
     <n v="2100"/>
@@ -1923,7 +7322,7 @@
     <n v="18"/>
     <x v="17"/>
     <s v="Khaled Hassan"/>
-    <s v="Alexandria"/>
+    <x v="3"/>
     <x v="6"/>
     <n v="6"/>
     <n v="450"/>
@@ -1933,7 +7332,7 @@
     <n v="19"/>
     <x v="18"/>
     <s v="Ahmed Said"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="6"/>
     <n v="190"/>
@@ -1943,7 +7342,7 @@
     <n v="20"/>
     <x v="19"/>
     <s v="Ali Ramadan"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="2"/>
     <n v="300"/>
@@ -1953,7 +7352,7 @@
     <n v="21"/>
     <x v="20"/>
     <s v="Ashraf Zaki"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="3"/>
     <n v="1500"/>
@@ -1963,7 +7362,7 @@
     <n v="22"/>
     <x v="21"/>
     <s v="Fathy Ali"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="5"/>
     <n v="8500"/>
@@ -1973,7 +7372,7 @@
     <n v="23"/>
     <x v="22"/>
     <s v="Tamer Mohamed"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="1"/>
     <n v="190"/>
@@ -1983,7 +7382,7 @@
     <n v="24"/>
     <x v="23"/>
     <s v="Khaled Hassan"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="6"/>
     <n v="210"/>
@@ -1993,7 +7392,7 @@
     <n v="25"/>
     <x v="24"/>
     <s v="Ahmed Said"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="4"/>
     <n v="2"/>
     <n v="300"/>
@@ -2003,7 +7402,7 @@
     <n v="26"/>
     <x v="25"/>
     <s v="Ali Ramadan"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="4"/>
     <n v="190"/>
@@ -2013,7 +7412,7 @@
     <n v="27"/>
     <x v="26"/>
     <s v="Ashraf Zaki"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="8"/>
     <n v="8500"/>
@@ -2023,7 +7422,7 @@
     <n v="28"/>
     <x v="27"/>
     <s v="Fathy Ali"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="3"/>
     <n v="300"/>
@@ -2033,7 +7432,7 @@
     <n v="29"/>
     <x v="28"/>
     <s v="Tamer Mohamed"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="7"/>
     <n v="300"/>
@@ -2043,7 +7442,7 @@
     <n v="30"/>
     <x v="29"/>
     <s v="Khaled Hassan"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="7"/>
     <n v="4"/>
     <n v="190"/>
@@ -2053,7 +7452,7 @@
     <n v="31"/>
     <x v="30"/>
     <s v="Ahmed Said"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="2"/>
     <n v="450"/>
@@ -2063,7 +7462,7 @@
     <n v="32"/>
     <x v="31"/>
     <s v="Ali Ramadan"/>
-    <s v="Cairo"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="3"/>
     <n v="2100"/>
@@ -2073,7 +7472,7 @@
     <n v="33"/>
     <x v="32"/>
     <s v="Ashraf Zaki"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="2"/>
     <n v="8500"/>
@@ -2083,7 +7482,7 @@
     <n v="34"/>
     <x v="33"/>
     <s v="Fathy Ali"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="8"/>
     <n v="8500"/>
@@ -2093,7 +7492,7 @@
     <n v="35"/>
     <x v="34"/>
     <s v="Tamer Mohamed"/>
-    <s v="Alexandria"/>
+    <x v="3"/>
     <x v="0"/>
     <n v="2"/>
     <n v="210"/>
@@ -2103,7 +7502,7 @@
     <n v="36"/>
     <x v="35"/>
     <s v="Khaled Hassan"/>
-    <s v="Alexandria"/>
+    <x v="3"/>
     <x v="7"/>
     <n v="2"/>
     <n v="190"/>
@@ -2113,7 +7512,7 @@
     <n v="37"/>
     <x v="36"/>
     <s v="Ahmed Said"/>
-    <s v="Alexandria"/>
+    <x v="3"/>
     <x v="3"/>
     <n v="3"/>
     <n v="8500"/>
@@ -2123,7 +7522,7 @@
     <n v="38"/>
     <x v="37"/>
     <s v="Ali Ramadan"/>
-    <s v="Giza"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="5"/>
     <n v="210"/>
@@ -2133,7 +7532,7 @@
     <n v="39"/>
     <x v="38"/>
     <s v="Ashraf Zaki"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="5"/>
     <n v="2100"/>
@@ -2143,7 +7542,7 @@
     <n v="40"/>
     <x v="39"/>
     <s v="Fathy Ali"/>
-    <s v="Domietta"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="6"/>
     <n v="1200"/>
@@ -2153,9 +7552,1264 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="H20:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="41">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="11">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="231" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="9"/>
+    <field x="8"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="53">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="231" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="8">
+  <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
       <items count="41">
@@ -2252,6 +8906,398 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowItems count="1">
     <i/>
@@ -2263,18 +9309,18 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="112">
+    <format dxfId="135">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="188" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="231" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -2296,10 +9342,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="8">
+  <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
       <items count="41">
@@ -2396,6 +9442,398 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowItems count="1">
     <i/>
@@ -2407,18 +9845,18 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="113">
+    <format dxfId="136">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="181" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="224" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -2440,10 +9878,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="8">
+  <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
       <items count="41">
@@ -2540,6 +9978,398 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowItems count="1">
     <i/>
@@ -2551,18 +10381,18 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="114">
+    <format dxfId="137">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="181" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="224" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -2606,10 +10436,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="118"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="117"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="116"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="141"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="140"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="139"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="138"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -2621,7 +10451,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Grayscale">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2629,34 +10459,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="F8F8F8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="DDDDDD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="B2B2B2"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="969696"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="808080"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5F5F5F"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4D4D4D"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="5F5F5F"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="919191"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -2939,10 +10769,12 @@
     <pivotTable tabId="3" name="PivotTable2"/>
     <pivotTable tabId="3" name="PivotTable1"/>
     <pivotTable tabId="3" name="PivotTable3"/>
+    <pivotTable tabId="3" name="PivotTable5"/>
+    <pivotTable tabId="3" name="PivotTable6"/>
   </pivotTables>
   <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="548194542" filterType="dateBetween">
-    <selection startDate="2023-01-01T00:00:00" endDate="2023-01-31T00:00:00"/>
-    <bounds startDate="2023-01-01T00:00:00" endDate="2024-01-01T00:00:00"/>
+    <selection startDate="2023-01-01T00:00:00" endDate="2023-02-28T00:00:00"/>
+    <bounds startDate="2023-01-01T00:00:00" endDate="2025-01-01T00:00:00"/>
   </state>
 </timelineCacheDefinition>
 </file>
@@ -2978,58 +10810,134 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1649C905-6944-4F98-B4AE-37BE068CDF30}">
-  <dimension ref="A2:E7"/>
+  <dimension ref="A2:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>426530</v>
+      </c>
+      <c r="C6" s="6">
+        <v>40</v>
+      </c>
+      <c r="E6" s="6">
+        <v>10663.25</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="6">
+        <v>290180</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>290180</v>
-      </c>
-      <c r="C6" s="4">
-        <v>31</v>
-      </c>
-      <c r="E6" s="4">
-        <v>9360.645161290322</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
         <f>GETPIVOTDATA("Amount",$A$5)</f>
-        <v>290180</v>
+        <v>426530</v>
       </c>
       <c r="C7">
         <f>GETPIVOTDATA("Item",$C$5)</f>
-        <v>31</v>
-      </c>
-      <c r="E7" s="7">
+        <v>40</v>
+      </c>
+      <c r="E7" s="9">
         <f>GETPIVOTDATA("Amount",$E$5)</f>
-        <v>9360.645161290322</v>
+        <v>10663.25</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="6">
+        <v>136350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="6">
+        <v>426530</v>
+      </c>
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="6">
+        <v>38300</v>
+      </c>
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="6">
+        <v>24270</v>
+      </c>
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="6">
+        <v>155450</v>
+      </c>
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="6">
+        <v>208510</v>
+      </c>
+    </row>
+    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="6">
+        <v>426530</v>
       </c>
     </row>
   </sheetData>
@@ -3037,11 +10945,11 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
       <x15:timelineRefs>
-        <x15:timelineRef r:id="rId5"/>
+        <x15:timelineRef r:id="rId7"/>
       </x15:timelineRefs>
     </ext>
   </extLst>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84242AE8-80D1-469E-B6CB-B148ADC83800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44081467-0A3B-4521-8BE0-3FBB810044A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -243,7 +243,77 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="142">
+  <dxfs count="152">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2065,7 +2135,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{8F04FACA-BB3F-456F-978F-18AE092E4DB8}" type="CELLRANGE">
+                <a:fld id="{D513CBE0-E094-4C26-96DA-DB434CB46CB4}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2076,7 +2146,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{6C4A9361-0318-4687-8174-06F0597D5D29}" type="PERCENTAGE">
+                <a:fld id="{72920183-DA88-4872-88F3-A9CECC31E244}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2171,7 +2241,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{E8EA7B26-7E78-4AC7-BBF5-D1085E5A7553}" type="CELLRANGE">
+                <a:fld id="{50B8A57B-9ECA-4A6B-9F76-D0604A308663}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2182,7 +2252,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{5FFDEAF5-0A11-4A88-87D1-98907541AF9D}" type="PERCENTAGE">
+                <a:fld id="{D0E6F6D9-C13A-437F-BE53-C2E24046A817}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2277,7 +2347,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{089C05EC-B45A-4671-B50E-34574E5C55A6}" type="CELLRANGE">
+                <a:fld id="{B3701F17-3C06-487F-9634-982686149457}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2288,7 +2358,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{50D51559-626D-4A36-BB8E-3999BA1A592C}" type="PERCENTAGE">
+                <a:fld id="{38602BB4-B684-45A1-A60C-0E81C4D44DB3}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2383,7 +2453,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{53B4288B-A224-48D5-A844-84B01B96274D}" type="CELLRANGE">
+                <a:fld id="{80DB1AD1-58C2-4FE5-A975-4AA7F66E591B}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2394,7 +2464,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{FBF05BD7-46BE-452E-B85F-5AA2B1D5BC3C}" type="PERCENTAGE">
+                <a:fld id="{5FC59D29-5B66-45B3-A6DC-0B54DECF4553}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2561,7 +2631,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8F04FACA-BB3F-456F-978F-18AE092E4DB8}" type="CELLRANGE">
+                    <a:fld id="{D513CBE0-E094-4C26-96DA-DB434CB46CB4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2570,7 +2640,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{6C4A9361-0318-4687-8174-06F0597D5D29}" type="PERCENTAGE">
+                    <a:fld id="{72920183-DA88-4872-88F3-A9CECC31E244}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2608,7 +2678,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E8EA7B26-7E78-4AC7-BBF5-D1085E5A7553}" type="CELLRANGE">
+                    <a:fld id="{50B8A57B-9ECA-4A6B-9F76-D0604A308663}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2617,7 +2687,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{5FFDEAF5-0A11-4A88-87D1-98907541AF9D}" type="PERCENTAGE">
+                    <a:fld id="{D0E6F6D9-C13A-437F-BE53-C2E24046A817}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2655,7 +2725,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{089C05EC-B45A-4671-B50E-34574E5C55A6}" type="CELLRANGE">
+                    <a:fld id="{B3701F17-3C06-487F-9634-982686149457}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2664,7 +2734,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{50D51559-626D-4A36-BB8E-3999BA1A592C}" type="PERCENTAGE">
+                    <a:fld id="{38602BB4-B684-45A1-A60C-0E81C4D44DB3}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2702,7 +2772,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{53B4288B-A224-48D5-A844-84B01B96274D}" type="CELLRANGE">
+                    <a:fld id="{80DB1AD1-58C2-4FE5-A975-4AA7F66E591B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2711,7 +2781,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{FBF05BD7-46BE-452E-B85F-5AA2B1D5BC3C}" type="PERCENTAGE">
+                    <a:fld id="{5FC59D29-5B66-45B3-A6DC-0B54DECF4553}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -8079,7 +8149,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="41">
+    <format dxfId="66">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -8210,7 +8280,7 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="231" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="261" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -8753,7 +8823,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="53">
+    <format dxfId="78">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -8779,7 +8849,7 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="231" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="261" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -9309,13 +9379,13 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="135">
+    <format dxfId="145">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="231" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="261" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -9845,13 +9915,13 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="136">
+    <format dxfId="146">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="224" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="254" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -10381,13 +10451,13 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="137">
+    <format dxfId="147">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="224" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="254" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -10436,10 +10506,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="141"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="140"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="139"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="138"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="151"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="150"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="149"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="148"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44081467-0A3B-4521-8BE0-3FBB810044A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B768F143-C0AC-4AB2-AE5C-E64546D44E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="35">
   <si>
     <t>S No</t>
   </si>
@@ -178,7 +178,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -233,668 +233,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="152">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="64">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1291,6 +640,41 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2088,7 +1472,6 @@
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:dlblFieldTable/>
               <c15:showDataLabelsRange val="1"/>
             </c:ext>
           </c:extLst>
@@ -2135,8 +1518,8 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{D513CBE0-E094-4C26-96DA-DB434CB46CB4}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
+                <a:fld id="{529C971A-3412-4BCB-8996-9C91C1B76611}" type="CELLRANGE">
+                  <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
                   </a:pPr>
@@ -2146,7 +1529,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{72920183-DA88-4872-88F3-A9CECC31E244}" type="PERCENTAGE">
+                <a:fld id="{C1D37818-9627-454B-BA10-55F0847C5CDE}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2241,8 +1624,8 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{50B8A57B-9ECA-4A6B-9F76-D0604A308663}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
+                <a:fld id="{D5B3FA10-BE4F-4834-8504-D5CA61B6170E}" type="CELLRANGE">
+                  <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
                   </a:pPr>
@@ -2252,7 +1635,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{D0E6F6D9-C13A-437F-BE53-C2E24046A817}" type="PERCENTAGE">
+                <a:fld id="{23CFFE3D-C9A7-4E9B-B8C0-9CC3B57E35B4}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2347,8 +1730,8 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{B3701F17-3C06-487F-9634-982686149457}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
+                <a:fld id="{83B8FA74-CA0B-4D65-947E-AA6C8835284C}" type="CELLRANGE">
+                  <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
                   </a:pPr>
@@ -2358,7 +1741,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{38602BB4-B684-45A1-A60C-0E81C4D44DB3}" type="PERCENTAGE">
+                <a:fld id="{2500C280-F941-4406-B72B-6110BF80652C}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2453,8 +1836,8 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{80DB1AD1-58C2-4FE5-A975-4AA7F66E591B}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
+                <a:fld id="{C7516DF8-1AD7-4764-BEF6-4506872175A2}" type="CELLRANGE">
+                  <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
                   </a:pPr>
@@ -2464,7 +1847,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{5FC59D29-5B66-45B3-A6DC-0B54DECF4553}" type="PERCENTAGE">
+                <a:fld id="{80C1E98A-6FD1-495D-A25F-F370996C88D8}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2631,8 +2014,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D513CBE0-E094-4C26-96DA-DB434CB46CB4}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{529C971A-3412-4BCB-8996-9C91C1B76611}" type="CELLRANGE">
+                      <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -2640,7 +2023,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{72920183-DA88-4872-88F3-A9CECC31E244}" type="PERCENTAGE">
+                    <a:fld id="{C1D37818-9627-454B-BA10-55F0847C5CDE}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2678,8 +2061,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{50B8A57B-9ECA-4A6B-9F76-D0604A308663}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{D5B3FA10-BE4F-4834-8504-D5CA61B6170E}" type="CELLRANGE">
+                      <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -2687,7 +2070,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{D0E6F6D9-C13A-437F-BE53-C2E24046A817}" type="PERCENTAGE">
+                    <a:fld id="{23CFFE3D-C9A7-4E9B-B8C0-9CC3B57E35B4}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2725,8 +2108,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B3701F17-3C06-487F-9634-982686149457}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{83B8FA74-CA0B-4D65-947E-AA6C8835284C}" type="CELLRANGE">
+                      <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -2734,7 +2117,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{38602BB4-B684-45A1-A60C-0E81C4D44DB3}" type="PERCENTAGE">
+                    <a:fld id="{2500C280-F941-4406-B72B-6110BF80652C}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2772,8 +2155,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{80DB1AD1-58C2-4FE5-A975-4AA7F66E591B}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{C7516DF8-1AD7-4764-BEF6-4506872175A2}" type="CELLRANGE">
+                      <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -2781,7 +2164,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{5FC59D29-5B66-45B3-A6DC-0B54DECF4553}" type="PERCENTAGE">
+                    <a:fld id="{80C1E98A-6FD1-495D-A25F-F370996C88D8}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -3008,6 +2391,560 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[0B5F9D00.xlsx]data analysis!PivotTable4</c:name>
+    <c:fmtId val="8"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>top</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> pruduct by amount</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data analysis'!$M$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data analysis'!$L$22:$L$25</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Printer</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data analysis'!$M$22:$M$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>306000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-37E2-4940-A47D-8ADBE66178CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="435650320"/>
+        <c:axId val="435662320"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="435650320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="435662320"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="435662320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="435650320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3399,7 +3336,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3507,6 +3444,62 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -3540,6 +3533,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5C7C-4FCC-B56E-32017B38C32B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3555,6 +3553,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5C7C-4FCC-B56E-32017B38C32B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -3570,6 +3573,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5C7C-4FCC-B56E-32017B38C32B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -3585,6 +3593,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-5C7C-4FCC-B56E-32017B38C32B}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -3645,6 +3658,403 @@
         <c:firstSliceAng val="0"/>
         <c:holeSize val="75"/>
       </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[0B5F9D00.xlsx]data analysis!PivotTable4</c:name>
+    <c:fmtId val="6"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data analysis'!$M$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data analysis'!$L$22:$L$25</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Printer</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data analysis'!$M$22:$M$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>306000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8019-4E31-B20D-98DCAA019A47}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="435650320"/>
+        <c:axId val="435662320"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="435650320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="435662320"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="435662320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="435650320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -3904,6 +4314,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -4940,7 +5430,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5048,11 +5538,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -5063,11 +5548,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -5099,9 +5579,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5456,7 +5933,7 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5513,7 +5990,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -5565,6 +6042,522 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="19050">
         <a:solidFill>
           <a:schemeClr val="lt1"/>
@@ -5942,6 +6935,509 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -6340,6 +7836,7 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
+              <a:pPr algn="r"/>
               <a:t>10663</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
@@ -6399,8 +7896,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+      <mc:Choice Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Date 1">
@@ -6418,12 +7915,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date 1"/>
+              <tsle:timeslicer name="Date 1"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6539,6 +8036,44 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AC612F3-0F36-4197-8A47-CD0219F7827B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6557,8 +8092,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+      <mc:Choice Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Date">
@@ -6576,12 +8111,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date"/>
+              <tsle:timeslicer name="Date"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6688,6 +8223,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAADD22A-C8F5-BBAA-D014-FD7AE6C57259}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7622,7 +9193,2814 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57377406-EF9D-40FA-8C1C-85593D1E9337}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="L21:M25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="54">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="6">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="2">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="319" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+    <filter fld="4" type="count" evalOrder="-1" id="263" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="3" filterVal="3"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="9"/>
+    <field x="8"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="59">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="317" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="60">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="317" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="61">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="310" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="62">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="310" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="H20:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -8149,11 +12527,11 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="66">
+    <format dxfId="63">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="11">
+  <chartFormats count="15">
     <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -8277,571 +12655,50 @@
         </references>
       </pivotArea>
     </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="261" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="369">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="3">
-    <field x="9"/>
-    <field x="8"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="78">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="3" format="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
+    <chartFormat chart="3" format="2">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="2">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -8849,1615 +12706,7 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="261" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="145">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="261" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="146">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="254" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="147">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="254" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="317" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -10506,10 +12755,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="151"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="150"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="149"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="148"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="55"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -10841,6 +13090,7 @@
     <pivotTable tabId="3" name="PivotTable3"/>
     <pivotTable tabId="3" name="PivotTable5"/>
     <pivotTable tabId="3" name="PivotTable6"/>
+    <pivotTable tabId="3" name="PivotTable4"/>
   </pivotTables>
   <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="548194542" filterType="dateBetween">
     <selection startDate="2023-01-01T00:00:00" endDate="2023-02-28T00:00:00"/>
@@ -10880,7 +13130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1649C905-6944-4F98-B4AE-37BE068CDF30}">
-  <dimension ref="A2:I25"/>
+  <dimension ref="A2:M25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -10889,16 +13139,18 @@
     <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -10935,7 +13187,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <f>GETPIVOTDATA("Amount",$A$5)</f>
         <v>426530</v>
       </c>
@@ -10943,7 +13195,7 @@
         <f>GETPIVOTDATA("Item",$C$5)</f>
         <v>40</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f>GETPIVOTDATA("Amount",$E$5)</f>
         <v>10663.25</v>
       </c>
@@ -10962,7 +13214,7 @@
         <v>426530</v>
       </c>
     </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H20" s="4" t="s">
         <v>26</v>
       </c>
@@ -10970,44 +13222,74 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H21" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
         <v>38300</v>
       </c>
+      <c r="L21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="I22" s="6">
         <v>24270</v>
       </c>
+      <c r="L22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="6">
+        <v>306000</v>
+      </c>
     </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I23" s="6">
         <v>155450</v>
       </c>
+      <c r="L23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M23" s="6">
+        <v>79800</v>
+      </c>
     </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H24" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="6">
         <v>208510</v>
       </c>
+      <c r="L24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="6">
+        <v>12000</v>
+      </c>
     </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="I25" s="6">
         <v>426530</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="6">
+        <v>397800</v>
       </c>
     </row>
   </sheetData>
@@ -11015,11 +13297,11 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId7"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
       <x15:timelineRefs>
-        <x15:timelineRef r:id="rId7"/>
+        <x15:timelineRef r:id="rId8"/>
       </x15:timelineRefs>
     </ext>
   </extLst>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B768F143-C0AC-4AB2-AE5C-E64546D44E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EFF462-CF66-4F30-B976-E06B4E1AC1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="34">
   <si>
     <t>S No</t>
   </si>
@@ -168,9 +168,6 @@
   <si>
     <t>Jan</t>
   </si>
-  <si>
-    <t>Feb</t>
-  </si>
 </sst>
 </file>
 
@@ -243,7 +240,623 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="152">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -977,29 +1590,23 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$6:$H$8</c:f>
+              <c:f>'data analysis'!$H$6:$H$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Feb</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$6:$I$8</c:f>
+              <c:f>'data analysis'!$I$6:$I$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>290180</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>136350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1214,6 +1821,36 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>amount</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> by region</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1518,7 +2155,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{529C971A-3412-4BCB-8996-9C91C1B76611}" type="CELLRANGE">
+                <a:fld id="{B8E61775-6FE6-4DB4-8216-0A143AA8DC32}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1529,7 +2166,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{C1D37818-9627-454B-BA10-55F0847C5CDE}" type="PERCENTAGE">
+                <a:fld id="{598386B9-0B5A-4026-99FC-91883A7E8F82}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1624,7 +2261,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{D5B3FA10-BE4F-4834-8504-D5CA61B6170E}" type="CELLRANGE">
+                <a:fld id="{3B880D56-BF59-4B89-B431-00E8A0D4AFDA}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1635,7 +2272,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{23CFFE3D-C9A7-4E9B-B8C0-9CC3B57E35B4}" type="PERCENTAGE">
+                <a:fld id="{69A2FAC1-F5E8-4A6F-B584-12383D03ECAD}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1730,7 +2367,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{83B8FA74-CA0B-4D65-947E-AA6C8835284C}" type="CELLRANGE">
+                <a:fld id="{6D6611F4-1C31-48F4-A0AA-1CEAB75005AD}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1741,7 +2378,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{2500C280-F941-4406-B72B-6110BF80652C}" type="PERCENTAGE">
+                <a:fld id="{97C1442A-06FF-4443-81AA-91E167B34498}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1836,7 +2473,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{C7516DF8-1AD7-4764-BEF6-4506872175A2}" type="CELLRANGE">
+                <a:fld id="{B70DAC1B-E684-40B1-83F3-541BEC3112ED}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1847,7 +2484,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{80C1E98A-6FD1-495D-A25F-F370996C88D8}" type="PERCENTAGE">
+                <a:fld id="{10521747-F48A-4BD6-98B1-CF2CB2237851}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2014,7 +2651,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{529C971A-3412-4BCB-8996-9C91C1B76611}" type="CELLRANGE">
+                    <a:fld id="{B8E61775-6FE6-4DB4-8216-0A143AA8DC32}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2023,7 +2660,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{C1D37818-9627-454B-BA10-55F0847C5CDE}" type="PERCENTAGE">
+                    <a:fld id="{598386B9-0B5A-4026-99FC-91883A7E8F82}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2061,7 +2698,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D5B3FA10-BE4F-4834-8504-D5CA61B6170E}" type="CELLRANGE">
+                    <a:fld id="{3B880D56-BF59-4B89-B431-00E8A0D4AFDA}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2070,7 +2707,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{23CFFE3D-C9A7-4E9B-B8C0-9CC3B57E35B4}" type="PERCENTAGE">
+                    <a:fld id="{69A2FAC1-F5E8-4A6F-B584-12383D03ECAD}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2108,7 +2745,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{83B8FA74-CA0B-4D65-947E-AA6C8835284C}" type="CELLRANGE">
+                    <a:fld id="{6D6611F4-1C31-48F4-A0AA-1CEAB75005AD}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2117,7 +2754,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{2500C280-F941-4406-B72B-6110BF80652C}" type="PERCENTAGE">
+                    <a:fld id="{97C1442A-06FF-4443-81AA-91E167B34498}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2155,7 +2792,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C7516DF8-1AD7-4764-BEF6-4506872175A2}" type="CELLRANGE">
+                    <a:fld id="{B70DAC1B-E684-40B1-83F3-541BEC3112ED}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2164,7 +2801,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{80C1E98A-6FD1-495D-A25F-F370996C88D8}" type="PERCENTAGE">
+                    <a:fld id="{10521747-F48A-4BD6-98B1-CF2CB2237851}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2272,16 +2909,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>38300</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24270</c:v>
+                  <c:v>17970</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>155450</c:v>
+                  <c:v>120750</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>208510</c:v>
+                  <c:v>139460</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2428,15 +3065,15 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>top</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> pruduct by amount</a:t>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> prouct by amount</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t> </a:t>
             </a:r>
           </a:p>
@@ -2743,7 +3380,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Monitor</c:v>
+                  <c:v>Scanner</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2755,13 +3392,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>306000</c:v>
+                  <c:v>195500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79800</c:v>
+                  <c:v>63000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12000</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2958,6 +3595,529 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
+    <c:name>[0B5F9D00.xlsx]data analysis!PivotTable7</c:name>
+    <c:fmtId val="8"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>top</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> salers</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data analysis'!$I$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data analysis'!$H$36:$H$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Ali Ramadan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ashraf Zaki</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Fathy Ali</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data analysis'!$I$36:$I$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>58660</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48620</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7577-4FC9-8CDC-48B8A48BD2E0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="497161696"/>
+        <c:axId val="497169856"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="497161696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="497169856"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="497169856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="497161696"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
     <c:name>[0B5F9D00.xlsx]data analysis!PivotTable5</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
@@ -3084,29 +4244,23 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$6:$H$8</c:f>
+              <c:f>'data analysis'!$H$6:$H$7</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Jan</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Feb</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$6:$I$8</c:f>
+              <c:f>'data analysis'!$I$6:$I$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>290180</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>136350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3336,7 +4490,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3626,16 +4780,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>38300</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24270</c:v>
+                  <c:v>17970</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>155450</c:v>
+                  <c:v>120750</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>208510</c:v>
+                  <c:v>139460</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3757,7 +4911,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3906,7 +5060,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Monitor</c:v>
+                  <c:v>Scanner</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3918,13 +5072,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>306000</c:v>
+                  <c:v>195500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79800</c:v>
+                  <c:v>63000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12000</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4052,6 +5206,402 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="435650320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[0B5F9D00.xlsx]data analysis!PivotTable7</c:name>
+    <c:fmtId val="6"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data analysis'!$I$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data analysis'!$H$36:$H$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Ali Ramadan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ashraf Zaki</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Fathy Ali</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data analysis'!$I$36:$I$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>58660</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48620</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FDFC-4C1D-9A65-4CF24BB3E542}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="497161696"/>
+        <c:axId val="497169856"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="497161696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="497169856"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="497169856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="497161696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4394,6 +5944,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -5933,7 +7563,7 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6041,11 +7671,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -6056,11 +7681,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -6092,9 +7712,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6150,22 +7767,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -6270,8 +7888,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6403,19 +8021,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -6449,7 +8068,7 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6506,7 +8125,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -6558,6 +8177,522 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="19050">
         <a:solidFill>
           <a:schemeClr val="lt1"/>
@@ -6967,7 +9102,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7438,6 +9573,511 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -7563,7 +10203,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t> $426,530 </a:t>
+              <a:t> $290,180 </a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -7700,7 +10340,7 @@
                 <a:latin typeface="+mj-lt"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>40</a:t>
+              <a:t>31</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="+mj-lt"/>
@@ -7837,7 +10477,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>10663</a:t>
+              <a:t>9361</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -7885,19 +10525,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-      <mc:Choice Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Date 1">
@@ -7915,12 +10555,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer name="Date 1"/>
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date 1"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7930,8 +10570,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2430780" y="144780"/>
-              <a:ext cx="7322820" cy="1196340"/>
+              <a:off x="769620" y="4594860"/>
+              <a:ext cx="1569720" cy="1371600"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8038,16 +10678,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>541020</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8069,6 +10709,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22EC6FF2-97BC-455F-8CC0-C269253454CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8230,16 +10908,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8259,6 +10937,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{549F7B4A-9521-5BE4-7582-2081B0F71C64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8322,7 +11036,14 @@
       <fieldGroup par="9"/>
     </cacheField>
     <cacheField name="Salesman" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="6">
+        <s v="Ahmed Said"/>
+        <s v="Ali Ramadan"/>
+        <s v="Ashraf Zaki"/>
+        <s v="Fathy Ali"/>
+        <s v="Tamer Mohamed"/>
+        <s v="Khaled Hassan"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Region" numFmtId="0">
       <sharedItems count="4">
@@ -8792,7 +11513,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="Ahmed Said"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <n v="5"/>
@@ -8802,7 +11523,7 @@
   <r>
     <n v="2"/>
     <x v="1"/>
-    <s v="Ali Ramadan"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="1"/>
     <n v="3"/>
@@ -8812,7 +11533,7 @@
   <r>
     <n v="3"/>
     <x v="2"/>
-    <s v="Ashraf Zaki"/>
+    <x v="2"/>
     <x v="0"/>
     <x v="2"/>
     <n v="7"/>
@@ -8822,7 +11543,7 @@
   <r>
     <n v="4"/>
     <x v="3"/>
-    <s v="Fathy Ali"/>
+    <x v="3"/>
     <x v="0"/>
     <x v="0"/>
     <n v="2"/>
@@ -8832,7 +11553,7 @@
   <r>
     <n v="5"/>
     <x v="4"/>
-    <s v="Tamer Mohamed"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="1"/>
     <n v="1"/>
@@ -8842,7 +11563,7 @@
   <r>
     <n v="6"/>
     <x v="5"/>
-    <s v="Khaled Hassan"/>
+    <x v="5"/>
     <x v="1"/>
     <x v="3"/>
     <n v="4"/>
@@ -8852,7 +11573,7 @@
   <r>
     <n v="7"/>
     <x v="6"/>
-    <s v="Ahmed Said"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="4"/>
     <n v="1"/>
@@ -8862,7 +11583,7 @@
   <r>
     <n v="8"/>
     <x v="7"/>
-    <s v="Ali Ramadan"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="3"/>
     <n v="6"/>
@@ -8872,7 +11593,7 @@
   <r>
     <n v="9"/>
     <x v="8"/>
-    <s v="Ashraf Zaki"/>
+    <x v="2"/>
     <x v="3"/>
     <x v="5"/>
     <n v="4"/>
@@ -8882,7 +11603,7 @@
   <r>
     <n v="10"/>
     <x v="9"/>
-    <s v="Fathy Ali"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="2"/>
     <n v="2"/>
@@ -8892,7 +11613,7 @@
   <r>
     <n v="11"/>
     <x v="10"/>
-    <s v="Tamer Mohamed"/>
+    <x v="4"/>
     <x v="2"/>
     <x v="2"/>
     <n v="6"/>
@@ -8902,7 +11623,7 @@
   <r>
     <n v="12"/>
     <x v="11"/>
-    <s v="Khaled Hassan"/>
+    <x v="5"/>
     <x v="3"/>
     <x v="4"/>
     <n v="1"/>
@@ -8912,7 +11633,7 @@
   <r>
     <n v="13"/>
     <x v="12"/>
-    <s v="Ahmed Said"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="2"/>
     <n v="7"/>
@@ -8922,7 +11643,7 @@
   <r>
     <n v="14"/>
     <x v="13"/>
-    <s v="Ali Ramadan"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="4"/>
     <n v="6"/>
@@ -8932,7 +11653,7 @@
   <r>
     <n v="15"/>
     <x v="14"/>
-    <s v="Ashraf Zaki"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="2"/>
     <n v="1"/>
@@ -8942,7 +11663,7 @@
   <r>
     <n v="16"/>
     <x v="15"/>
-    <s v="Fathy Ali"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="4"/>
     <n v="2"/>
@@ -8952,7 +11673,7 @@
   <r>
     <n v="17"/>
     <x v="16"/>
-    <s v="Tamer Mohamed"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="2"/>
     <n v="7"/>
@@ -8962,7 +11683,7 @@
   <r>
     <n v="18"/>
     <x v="17"/>
-    <s v="Khaled Hassan"/>
+    <x v="5"/>
     <x v="3"/>
     <x v="6"/>
     <n v="6"/>
@@ -8972,7 +11693,7 @@
   <r>
     <n v="19"/>
     <x v="18"/>
-    <s v="Ahmed Said"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="7"/>
     <n v="6"/>
@@ -8982,7 +11703,7 @@
   <r>
     <n v="20"/>
     <x v="19"/>
-    <s v="Ali Ramadan"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="4"/>
     <n v="2"/>
@@ -8992,7 +11713,7 @@
   <r>
     <n v="21"/>
     <x v="20"/>
-    <s v="Ashraf Zaki"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="1"/>
     <n v="3"/>
@@ -9002,7 +11723,7 @@
   <r>
     <n v="22"/>
     <x v="21"/>
-    <s v="Fathy Ali"/>
+    <x v="3"/>
     <x v="2"/>
     <x v="3"/>
     <n v="5"/>
@@ -9012,7 +11733,7 @@
   <r>
     <n v="23"/>
     <x v="22"/>
-    <s v="Tamer Mohamed"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="7"/>
     <n v="1"/>
@@ -9022,7 +11743,7 @@
   <r>
     <n v="24"/>
     <x v="23"/>
-    <s v="Khaled Hassan"/>
+    <x v="5"/>
     <x v="1"/>
     <x v="0"/>
     <n v="6"/>
@@ -9032,7 +11753,7 @@
   <r>
     <n v="25"/>
     <x v="24"/>
-    <s v="Ahmed Said"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="4"/>
     <n v="2"/>
@@ -9042,7 +11763,7 @@
   <r>
     <n v="26"/>
     <x v="25"/>
-    <s v="Ali Ramadan"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="7"/>
     <n v="4"/>
@@ -9052,7 +11773,7 @@
   <r>
     <n v="27"/>
     <x v="26"/>
-    <s v="Ashraf Zaki"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="3"/>
     <n v="8"/>
@@ -9062,7 +11783,7 @@
   <r>
     <n v="28"/>
     <x v="27"/>
-    <s v="Fathy Ali"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="4"/>
     <n v="3"/>
@@ -9072,7 +11793,7 @@
   <r>
     <n v="29"/>
     <x v="28"/>
-    <s v="Tamer Mohamed"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="4"/>
     <n v="7"/>
@@ -9082,7 +11803,7 @@
   <r>
     <n v="30"/>
     <x v="29"/>
-    <s v="Khaled Hassan"/>
+    <x v="5"/>
     <x v="2"/>
     <x v="7"/>
     <n v="4"/>
@@ -9092,7 +11813,7 @@
   <r>
     <n v="31"/>
     <x v="30"/>
-    <s v="Ahmed Said"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="6"/>
     <n v="2"/>
@@ -9102,7 +11823,7 @@
   <r>
     <n v="32"/>
     <x v="31"/>
-    <s v="Ali Ramadan"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="2"/>
     <n v="3"/>
@@ -9112,7 +11833,7 @@
   <r>
     <n v="33"/>
     <x v="32"/>
-    <s v="Ashraf Zaki"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="3"/>
     <n v="2"/>
@@ -9122,7 +11843,7 @@
   <r>
     <n v="34"/>
     <x v="33"/>
-    <s v="Fathy Ali"/>
+    <x v="3"/>
     <x v="2"/>
     <x v="3"/>
     <n v="8"/>
@@ -9132,7 +11853,7 @@
   <r>
     <n v="35"/>
     <x v="34"/>
-    <s v="Tamer Mohamed"/>
+    <x v="4"/>
     <x v="3"/>
     <x v="0"/>
     <n v="2"/>
@@ -9142,7 +11863,7 @@
   <r>
     <n v="36"/>
     <x v="35"/>
-    <s v="Khaled Hassan"/>
+    <x v="5"/>
     <x v="3"/>
     <x v="7"/>
     <n v="2"/>
@@ -9152,7 +11873,7 @@
   <r>
     <n v="37"/>
     <x v="36"/>
-    <s v="Ahmed Said"/>
+    <x v="0"/>
     <x v="3"/>
     <x v="3"/>
     <n v="3"/>
@@ -9162,7 +11883,7 @@
   <r>
     <n v="38"/>
     <x v="37"/>
-    <s v="Ali Ramadan"/>
+    <x v="1"/>
     <x v="2"/>
     <x v="0"/>
     <n v="5"/>
@@ -9172,7 +11893,7 @@
   <r>
     <n v="39"/>
     <x v="38"/>
-    <s v="Ashraf Zaki"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="2"/>
     <n v="5"/>
@@ -9182,7 +11903,7 @@
   <r>
     <n v="40"/>
     <x v="39"/>
-    <s v="Fathy Ali"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="5"/>
     <n v="6"/>
@@ -9193,7 +11914,638 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57377406-EF9D-40FA-8C1C-85593D1E9337}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4624B9DB-16A8-46B5-A956-2588C79515CB}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="H35:I39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="ascending">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="141">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="6">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="2">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+    <filter fld="2" type="count" evalOrder="-1" id="318" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="3" filterVal="3"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57377406-EF9D-40FA-8C1C-85593D1E9337}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="L21:M25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -9713,7 +13065,7 @@
       <x v="5"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="6"/>
     </i>
     <i t="grand">
       <x/>
@@ -9726,11 +13078,11 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="54">
+    <format dxfId="142">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="6">
+  <chartFormats count="5">
     <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -9767,15 +13119,6 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="7" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
     <chartFormat chart="8" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -9788,12 +13131,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="2">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="319" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="471" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -9822,9 +13165,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="H5:I7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -10320,12 +13663,9 @@
     <field x="8"/>
     <field x="1"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="2">
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -10338,7 +13678,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="59">
+    <format dxfId="147">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -10364,12 +13704,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="317" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="469" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -10391,8 +13731,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -10894,18 +14234,18 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="60">
+    <format dxfId="148">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="317" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="469" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -10927,8 +14267,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -11430,18 +14770,18 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="61">
+    <format dxfId="149">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="310" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="462" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -11463,8 +14803,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -11966,18 +15306,18 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="62">
+    <format dxfId="150">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="310" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="462" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -11999,8 +15339,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="H20:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -12527,7 +15867,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="63">
+    <format dxfId="151">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12706,12 +16046,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="317" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="469" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
+            <customFilter operator="lessThanOrEqual" val="44957"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -12755,10 +16095,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="146"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="145"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="144"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="143"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -13091,9 +16431,10 @@
     <pivotTable tabId="3" name="PivotTable5"/>
     <pivotTable tabId="3" name="PivotTable6"/>
     <pivotTable tabId="3" name="PivotTable4"/>
+    <pivotTable tabId="3" name="PivotTable7"/>
   </pivotTables>
   <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="548194542" filterType="dateBetween">
-    <selection startDate="2023-01-01T00:00:00" endDate="2023-02-28T00:00:00"/>
+    <selection startDate="2023-01-01T00:00:00" endDate="2023-01-31T00:00:00"/>
     <bounds startDate="2023-01-01T00:00:00" endDate="2025-01-01T00:00:00"/>
   </state>
 </timelineCacheDefinition>
@@ -13101,7 +16442,7 @@
 
 <file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
 <timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <timeline name="Date 1" xr10:uid="{4BAC2FE9-C0D7-4F7A-AA2C-A32B2D77E7A4}" cache="NativeTimeline_Date" caption="Date" showHorizontalScrollbar="0" level="2" selectionLevel="2" scrollPosition="2023-01-01T00:00:00" style="TimeSlicerStyleDark1"/>
+  <timeline name="Date 1" xr10:uid="{4BAC2FE9-C0D7-4F7A-AA2C-A32B2D77E7A4}" cache="NativeTimeline_Date" caption="Date" level="2" selectionLevel="2" scrollPosition="2023-01-01T00:00:00" style="TimeSlicerStyleDark1"/>
 </timelines>
 </file>
 
@@ -13130,13 +16471,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1649C905-6944-4F98-B4AE-37BE068CDF30}">
-  <dimension ref="A2:M25"/>
+  <dimension ref="A2:M39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -13171,13 +16512,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
-        <v>426530</v>
+        <v>290180</v>
       </c>
       <c r="C6" s="6">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E6" s="6">
-        <v>10663.25</v>
+        <v>9360.645161290322</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>33</v>
@@ -13189,29 +16530,21 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <f>GETPIVOTDATA("Amount",$A$5)</f>
-        <v>426530</v>
+        <v>290180</v>
       </c>
       <c r="C7">
         <f>GETPIVOTDATA("Item",$C$5)</f>
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E7" s="8">
         <f>GETPIVOTDATA("Amount",$E$5)</f>
-        <v>10663.25</v>
+        <v>9360.645161290322</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I7" s="6">
-        <v>136350</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="6">
-        <v>426530</v>
+        <v>290180</v>
       </c>
     </row>
     <row r="20" spans="8:13" x14ac:dyDescent="0.3">
@@ -13227,7 +16560,7 @@
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>38300</v>
+        <v>12000</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>26</v>
@@ -13241,13 +16574,13 @@
         <v>9</v>
       </c>
       <c r="I22" s="6">
-        <v>24270</v>
+        <v>17970</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>19</v>
       </c>
       <c r="M22" s="6">
-        <v>306000</v>
+        <v>195500</v>
       </c>
     </row>
     <row r="23" spans="8:13" x14ac:dyDescent="0.3">
@@ -13255,13 +16588,13 @@
         <v>12</v>
       </c>
       <c r="I23" s="6">
-        <v>155450</v>
+        <v>120750</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="M23" s="6">
-        <v>79800</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="24" spans="8:13" x14ac:dyDescent="0.3">
@@ -13269,13 +16602,13 @@
         <v>20</v>
       </c>
       <c r="I24" s="6">
-        <v>208510</v>
+        <v>139460</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="M24" s="6">
-        <v>12000</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="25" spans="8:13" x14ac:dyDescent="0.3">
@@ -13283,13 +16616,53 @@
         <v>27</v>
       </c>
       <c r="I25" s="6">
-        <v>426530</v>
+        <v>290180</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="M25" s="6">
-        <v>397800</v>
+        <v>269000</v>
+      </c>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="6">
+        <v>58660</v>
+      </c>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="6">
+        <v>94100</v>
+      </c>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="6">
+        <v>48620</v>
+      </c>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="6">
+        <v>201380</v>
       </c>
     </row>
   </sheetData>
@@ -13297,11 +16670,11 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId7"/>
+  <drawing r:id="rId8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
       <x15:timelineRefs>
-        <x15:timelineRef r:id="rId8"/>
+        <x15:timelineRef r:id="rId9"/>
       </x15:timelineRefs>
     </ext>
   </extLst>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EFF462-CF66-4F30-B976-E06B4E1AC1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405FA0EE-B8B4-461D-998E-54322F14677A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="35">
   <si>
     <t>S No</t>
   </si>
@@ -168,6 +168,9 @@
   <si>
     <t>Jan</t>
   </si>
+  <si>
+    <t>Feb</t>
+  </si>
 </sst>
 </file>
 
@@ -240,7 +243,49 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="152">
+  <dxfs count="158">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1590,23 +1635,29 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$6:$H$7</c:f>
+              <c:f>'data analysis'!$H$6:$H$8</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$6:$I$7</c:f>
+              <c:f>'data analysis'!$I$6:$I$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>290180</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>136350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2155,7 +2206,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{B8E61775-6FE6-4DB4-8216-0A143AA8DC32}" type="CELLRANGE">
+                <a:fld id="{A364F027-7915-4FC4-98E9-5FBD4211DA5F}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2166,7 +2217,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{598386B9-0B5A-4026-99FC-91883A7E8F82}" type="PERCENTAGE">
+                <a:fld id="{AE79E41E-D487-47FD-9DB4-58CF4B1E1903}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2261,7 +2312,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{3B880D56-BF59-4B89-B431-00E8A0D4AFDA}" type="CELLRANGE">
+                <a:fld id="{566DE493-B2D2-4D93-979E-2490F3FB57A3}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2272,7 +2323,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{69A2FAC1-F5E8-4A6F-B584-12383D03ECAD}" type="PERCENTAGE">
+                <a:fld id="{700C7C70-6990-44C4-9952-E54C03C0E387}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2367,7 +2418,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{6D6611F4-1C31-48F4-A0AA-1CEAB75005AD}" type="CELLRANGE">
+                <a:fld id="{CE8609EB-FC7D-4956-8D8B-0855137104B7}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2378,7 +2429,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{97C1442A-06FF-4443-81AA-91E167B34498}" type="PERCENTAGE">
+                <a:fld id="{FA007AAC-3BD6-4B03-B254-658DBCFA9BF1}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2473,7 +2524,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{B70DAC1B-E684-40B1-83F3-541BEC3112ED}" type="CELLRANGE">
+                <a:fld id="{E03FDEC3-EC48-4276-A626-DC74294E4C15}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2484,7 +2535,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{10521747-F48A-4BD6-98B1-CF2CB2237851}" type="PERCENTAGE">
+                <a:fld id="{A51CEAFA-865B-474F-ACA8-8658010FFDCC}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2651,7 +2702,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B8E61775-6FE6-4DB4-8216-0A143AA8DC32}" type="CELLRANGE">
+                    <a:fld id="{A364F027-7915-4FC4-98E9-5FBD4211DA5F}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2660,7 +2711,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{598386B9-0B5A-4026-99FC-91883A7E8F82}" type="PERCENTAGE">
+                    <a:fld id="{AE79E41E-D487-47FD-9DB4-58CF4B1E1903}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2698,7 +2749,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3B880D56-BF59-4B89-B431-00E8A0D4AFDA}" type="CELLRANGE">
+                    <a:fld id="{566DE493-B2D2-4D93-979E-2490F3FB57A3}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2707,7 +2758,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{69A2FAC1-F5E8-4A6F-B584-12383D03ECAD}" type="PERCENTAGE">
+                    <a:fld id="{700C7C70-6990-44C4-9952-E54C03C0E387}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2745,7 +2796,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6D6611F4-1C31-48F4-A0AA-1CEAB75005AD}" type="CELLRANGE">
+                    <a:fld id="{CE8609EB-FC7D-4956-8D8B-0855137104B7}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2754,7 +2805,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{97C1442A-06FF-4443-81AA-91E167B34498}" type="PERCENTAGE">
+                    <a:fld id="{FA007AAC-3BD6-4B03-B254-658DBCFA9BF1}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2792,7 +2843,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B70DAC1B-E684-40B1-83F3-541BEC3112ED}" type="CELLRANGE">
+                    <a:fld id="{E03FDEC3-EC48-4276-A626-DC74294E4C15}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2801,7 +2852,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{10521747-F48A-4BD6-98B1-CF2CB2237851}" type="PERCENTAGE">
+                    <a:fld id="{A51CEAFA-865B-474F-ACA8-8658010FFDCC}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2909,16 +2960,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>12000</c:v>
+                  <c:v>38300</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17970</c:v>
+                  <c:v>24270</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>120750</c:v>
+                  <c:v>155450</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>139460</c:v>
+                  <c:v>208510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3380,7 +3431,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scanner</c:v>
+                  <c:v>Monitor</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3392,13 +3443,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>195500</c:v>
+                  <c:v>306000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63000</c:v>
+                  <c:v>79800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10500</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3943,13 +3994,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>58660</c:v>
+                  <c:v>66010</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>94100</c:v>
+                  <c:v>121600</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>48620</c:v>
+                  <c:v>123820</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4244,23 +4295,29 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$6:$H$7</c:f>
+              <c:f>'data analysis'!$H$6:$H$8</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$6:$I$7</c:f>
+              <c:f>'data analysis'!$I$6:$I$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>290180</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>136350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4780,16 +4837,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>12000</c:v>
+                  <c:v>38300</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17970</c:v>
+                  <c:v>24270</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>120750</c:v>
+                  <c:v>155450</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>139460</c:v>
+                  <c:v>208510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5060,7 +5117,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scanner</c:v>
+                  <c:v>Monitor</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5072,13 +5129,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>195500</c:v>
+                  <c:v>306000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63000</c:v>
+                  <c:v>79800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10500</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5469,13 +5526,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>58660</c:v>
+                  <c:v>66010</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>94100</c:v>
+                  <c:v>121600</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>48620</c:v>
+                  <c:v>123820</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10203,7 +10260,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t> $290,180 </a:t>
+              <a:t> $426,530 </a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -10340,7 +10397,7 @@
                 <a:latin typeface="+mj-lt"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>31</a:t>
+              <a:t>40</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="+mj-lt"/>
@@ -10477,7 +10534,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>9361</a:t>
+              <a:t>10663</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -10750,6 +10807,193 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D17C806-2F9C-488C-4058-2B82E123FA7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2476500" y="8343900"/>
+          <a:ext cx="7353300" cy="1234440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="3175">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Graphic 18" descr="Lightbulb and gear with solid fill">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D94E066D-C47F-3015-75A2-57D38C2870DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId12"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2636520" y="8519160"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>54483</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>151257</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{768916E5-0F31-43B1-872B-A649CF3220A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3688080" y="8649843"/>
+          <a:ext cx="3200400" cy="645414"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>top</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0"/>
+            <a:t> sales in jan , top region giza 49% , top product laptop and top salers fathy ali</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -12448,11 +12692,11 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="141">
+    <format dxfId="147">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="6">
+  <chartFormats count="5">
     <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -12489,15 +12733,6 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="7" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
     <chartFormat chart="8" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -12510,12 +12745,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="2">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="478" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -13065,7 +13300,7 @@
       <x v="5"/>
     </i>
     <i>
-      <x v="6"/>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -13078,7 +13313,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="142">
+    <format dxfId="148">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13131,12 +13366,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="2">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="471" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="479" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -13167,7 +13402,7 @@
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="H5:I7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -13663,9 +13898,12 @@
     <field x="8"/>
     <field x="1"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="3">
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -13678,7 +13916,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="147">
+    <format dxfId="153">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13704,12 +13942,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="469" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -14234,18 +14472,18 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="148">
+    <format dxfId="154">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="469" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -14770,18 +15008,18 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="149">
+    <format dxfId="155">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="462" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -15306,18 +15544,18 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="150">
+    <format dxfId="156">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="462" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -15867,7 +16105,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="151">
+    <format dxfId="157">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16046,12 +16284,12 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="469" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
             <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44957"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
           </customFilters>
         </filterColumn>
       </autoFilter>
@@ -16095,10 +16333,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="146"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="145"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="144"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="143"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="152"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="151"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="150"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="149"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -16434,7 +16672,7 @@
     <pivotTable tabId="3" name="PivotTable7"/>
   </pivotTables>
   <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="548194542" filterType="dateBetween">
-    <selection startDate="2023-01-01T00:00:00" endDate="2023-01-31T00:00:00"/>
+    <selection startDate="2023-01-01T00:00:00" endDate="2023-02-28T00:00:00"/>
     <bounds startDate="2023-01-01T00:00:00" endDate="2025-01-01T00:00:00"/>
   </state>
 </timelineCacheDefinition>
@@ -16477,7 +16715,7 @@
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -16512,13 +16750,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
-        <v>290180</v>
+        <v>426530</v>
       </c>
       <c r="C6" s="6">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6">
-        <v>9360.645161290322</v>
+        <v>10663.25</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>33</v>
@@ -16530,21 +16768,29 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <f>GETPIVOTDATA("Amount",$A$5)</f>
-        <v>290180</v>
+        <v>426530</v>
       </c>
       <c r="C7">
         <f>GETPIVOTDATA("Item",$C$5)</f>
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E7" s="8">
         <f>GETPIVOTDATA("Amount",$E$5)</f>
-        <v>9360.645161290322</v>
+        <v>10663.25</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="6">
+        <v>136350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="6">
-        <v>290180</v>
+      <c r="I8" s="6">
+        <v>426530</v>
       </c>
     </row>
     <row r="20" spans="8:13" x14ac:dyDescent="0.3">
@@ -16560,7 +16806,7 @@
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>12000</v>
+        <v>38300</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>26</v>
@@ -16574,13 +16820,13 @@
         <v>9</v>
       </c>
       <c r="I22" s="6">
-        <v>17970</v>
+        <v>24270</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>19</v>
       </c>
       <c r="M22" s="6">
-        <v>195500</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="23" spans="8:13" x14ac:dyDescent="0.3">
@@ -16588,13 +16834,13 @@
         <v>12</v>
       </c>
       <c r="I23" s="6">
-        <v>120750</v>
+        <v>155450</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="M23" s="6">
-        <v>63000</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="24" spans="8:13" x14ac:dyDescent="0.3">
@@ -16602,13 +16848,13 @@
         <v>20</v>
       </c>
       <c r="I24" s="6">
-        <v>139460</v>
+        <v>208510</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="M24" s="6">
-        <v>10500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="25" spans="8:13" x14ac:dyDescent="0.3">
@@ -16616,13 +16862,13 @@
         <v>27</v>
       </c>
       <c r="I25" s="6">
-        <v>290180</v>
+        <v>426530</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="M25" s="6">
-        <v>269000</v>
+        <v>397800</v>
       </c>
     </row>
     <row r="35" spans="8:9" x14ac:dyDescent="0.3">
@@ -16638,7 +16884,7 @@
         <v>11</v>
       </c>
       <c r="I36" s="6">
-        <v>58660</v>
+        <v>66010</v>
       </c>
     </row>
     <row r="37" spans="8:9" x14ac:dyDescent="0.3">
@@ -16646,7 +16892,7 @@
         <v>14</v>
       </c>
       <c r="I37" s="6">
-        <v>94100</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="38" spans="8:9" x14ac:dyDescent="0.3">
@@ -16654,7 +16900,7 @@
         <v>16</v>
       </c>
       <c r="I38" s="6">
-        <v>48620</v>
+        <v>123820</v>
       </c>
     </row>
     <row r="39" spans="8:9" x14ac:dyDescent="0.3">
@@ -16662,7 +16908,7 @@
         <v>27</v>
       </c>
       <c r="I39" s="6">
-        <v>201380</v>
+        <v>311430</v>
       </c>
     </row>
   </sheetData>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405FA0EE-B8B4-461D-998E-54322F14677A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B77C1-6971-443F-972B-25B8E13D4787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -243,13 +243,18 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="158">
+  <dxfs count="11">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
       <fill>
@@ -264,1040 +269,6 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
       <fill>
@@ -2206,7 +1177,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{A364F027-7915-4FC4-98E9-5FBD4211DA5F}" type="CELLRANGE">
+                <a:fld id="{09559A61-2B30-4B4B-B8EF-C331DC274574}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2217,7 +1188,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{AE79E41E-D487-47FD-9DB4-58CF4B1E1903}" type="PERCENTAGE">
+                <a:fld id="{B95AAABA-332F-47AE-B0AD-C327DBE92EA1}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2312,7 +1283,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{566DE493-B2D2-4D93-979E-2490F3FB57A3}" type="CELLRANGE">
+                <a:fld id="{EA8A397C-DB60-406A-B70D-A6F5693C5948}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2323,7 +1294,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{700C7C70-6990-44C4-9952-E54C03C0E387}" type="PERCENTAGE">
+                <a:fld id="{6A406FDA-B452-4E87-859F-E35AC7C42393}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2418,7 +1389,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{CE8609EB-FC7D-4956-8D8B-0855137104B7}" type="CELLRANGE">
+                <a:fld id="{24F68C47-4013-4AEB-8122-C33C6BC7ED93}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2429,7 +1400,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{FA007AAC-3BD6-4B03-B254-658DBCFA9BF1}" type="PERCENTAGE">
+                <a:fld id="{54A3755E-EF1E-4B9D-B2ED-B2FAA6A50EC6}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2524,7 +1495,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{E03FDEC3-EC48-4276-A626-DC74294E4C15}" type="CELLRANGE">
+                <a:fld id="{FB1A7A2F-9D24-4576-A1FE-2A7EF8E597E8}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2535,7 +1506,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{A51CEAFA-865B-474F-ACA8-8658010FFDCC}" type="PERCENTAGE">
+                <a:fld id="{66784A98-C0B6-4564-827B-6BE920F031F6}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -2702,7 +1673,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A364F027-7915-4FC4-98E9-5FBD4211DA5F}" type="CELLRANGE">
+                    <a:fld id="{09559A61-2B30-4B4B-B8EF-C331DC274574}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2711,7 +1682,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{AE79E41E-D487-47FD-9DB4-58CF4B1E1903}" type="PERCENTAGE">
+                    <a:fld id="{B95AAABA-332F-47AE-B0AD-C327DBE92EA1}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2749,7 +1720,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{566DE493-B2D2-4D93-979E-2490F3FB57A3}" type="CELLRANGE">
+                    <a:fld id="{EA8A397C-DB60-406A-B70D-A6F5693C5948}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2758,7 +1729,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{700C7C70-6990-44C4-9952-E54C03C0E387}" type="PERCENTAGE">
+                    <a:fld id="{6A406FDA-B452-4E87-859F-E35AC7C42393}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2796,7 +1767,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CE8609EB-FC7D-4956-8D8B-0855137104B7}" type="CELLRANGE">
+                    <a:fld id="{24F68C47-4013-4AEB-8122-C33C6BC7ED93}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2805,7 +1776,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{FA007AAC-3BD6-4B03-B254-658DBCFA9BF1}" type="PERCENTAGE">
+                    <a:fld id="{54A3755E-EF1E-4B9D-B2ED-B2FAA6A50EC6}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2843,7 +1814,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E03FDEC3-EC48-4276-A626-DC74294E4C15}" type="CELLRANGE">
+                    <a:fld id="{FB1A7A2F-9D24-4576-A1FE-2A7EF8E597E8}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2852,7 +1823,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{A51CEAFA-865B-474F-ACA8-8658010FFDCC}" type="PERCENTAGE">
+                    <a:fld id="{66784A98-C0B6-4564-827B-6BE920F031F6}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -10583,15 +9554,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>160020</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
@@ -10627,7 +9598,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="769620" y="4594860"/>
+              <a:off x="762000" y="1661160"/>
               <a:ext cx="1569720" cy="1371600"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12158,7 +11129,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4624B9DB-16A8-46B5-A956-2588C79515CB}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4624B9DB-16A8-46B5-A956-2588C79515CB}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="H35:I39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -12692,7 +11663,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="147">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12780,7 +11751,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57377406-EF9D-40FA-8C1C-85593D1E9337}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57377406-EF9D-40FA-8C1C-85593D1E9337}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="L21:M25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -13313,7 +12284,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="148">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13401,2184 +12372,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="369">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="3">
-    <field x="9"/>
-    <field x="8"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="153">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="154">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="155">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="156">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="H20:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -16105,7 +12899,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="157">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16311,6 +13105,2183 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="9"/>
+    <field x="8"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="7">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="8">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{45FE5043-C852-44A5-BF97-16E323DBE1F5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9">
@@ -16333,10 +15304,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="152"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="151"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="150"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="149"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B77C1-6971-443F-972B-25B8E13D4787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DFF97F-385F-4626-A516-B8D34988A426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -1177,7 +1177,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{09559A61-2B30-4B4B-B8EF-C331DC274574}" type="CELLRANGE">
+                <a:fld id="{68F1BF92-E371-4ECB-8310-22EE57828004}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1188,7 +1188,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{B95AAABA-332F-47AE-B0AD-C327DBE92EA1}" type="PERCENTAGE">
+                <a:fld id="{FA5C5D86-563A-48F6-9598-ADECEBAB0628}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1283,7 +1283,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{EA8A397C-DB60-406A-B70D-A6F5693C5948}" type="CELLRANGE">
+                <a:fld id="{0DDA7C6F-92A9-43C5-92E9-33669AF34C6F}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1294,7 +1294,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{6A406FDA-B452-4E87-859F-E35AC7C42393}" type="PERCENTAGE">
+                <a:fld id="{3CB0C594-D308-4A5A-88DC-6319B410E956}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1389,7 +1389,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{24F68C47-4013-4AEB-8122-C33C6BC7ED93}" type="CELLRANGE">
+                <a:fld id="{D0850E04-4EFB-4A44-B0C7-E821DCF9CDEE}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1400,7 +1400,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{54A3755E-EF1E-4B9D-B2ED-B2FAA6A50EC6}" type="PERCENTAGE">
+                <a:fld id="{2F66FD2C-BDB9-4DAE-9D70-CC65737D7C87}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1495,7 +1495,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{FB1A7A2F-9D24-4576-A1FE-2A7EF8E597E8}" type="CELLRANGE">
+                <a:fld id="{DF3A122E-0094-440D-8FFB-BB30FCBBCEE4}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1506,7 +1506,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{66784A98-C0B6-4564-827B-6BE920F031F6}" type="PERCENTAGE">
+                <a:fld id="{93EA13B8-115C-40FA-B1A6-4DD5D6393F67}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1673,7 +1673,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{09559A61-2B30-4B4B-B8EF-C331DC274574}" type="CELLRANGE">
+                    <a:fld id="{68F1BF92-E371-4ECB-8310-22EE57828004}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1682,7 +1682,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{B95AAABA-332F-47AE-B0AD-C327DBE92EA1}" type="PERCENTAGE">
+                    <a:fld id="{FA5C5D86-563A-48F6-9598-ADECEBAB0628}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1720,7 +1720,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EA8A397C-DB60-406A-B70D-A6F5693C5948}" type="CELLRANGE">
+                    <a:fld id="{0DDA7C6F-92A9-43C5-92E9-33669AF34C6F}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1729,7 +1729,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{6A406FDA-B452-4E87-859F-E35AC7C42393}" type="PERCENTAGE">
+                    <a:fld id="{3CB0C594-D308-4A5A-88DC-6319B410E956}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1767,7 +1767,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{24F68C47-4013-4AEB-8122-C33C6BC7ED93}" type="CELLRANGE">
+                    <a:fld id="{D0850E04-4EFB-4A44-B0C7-E821DCF9CDEE}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1776,7 +1776,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{54A3755E-EF1E-4B9D-B2ED-B2FAA6A50EC6}" type="PERCENTAGE">
+                    <a:fld id="{2F66FD2C-BDB9-4DAE-9D70-CC65737D7C87}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1814,7 +1814,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FB1A7A2F-9D24-4576-A1FE-2A7EF8E597E8}" type="CELLRANGE">
+                    <a:fld id="{DF3A122E-0094-440D-8FFB-BB30FCBBCEE4}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1823,7 +1823,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{66784A98-C0B6-4564-827B-6BE920F031F6}" type="PERCENTAGE">
+                    <a:fld id="{93EA13B8-115C-40FA-B1A6-4DD5D6393F67}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -9962,6 +9962,139 @@
             <a:t> sales in jan , top region giza 49% , top product laptop and top salers fathy ali</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B560833-67C2-13CC-D04C-E3F448C40528}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2446020" y="571500"/>
+          <a:ext cx="7353300" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="TextBox 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3753C7B1-CF36-F2D1-BB84-10E5E4D605FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3558540" y="792480"/>
+          <a:ext cx="5128260" cy="472440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800" b="1"/>
+            <a:t>DATA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800" b="1" baseline="0"/>
+            <a:t> ANALYSIS PROFIT COMPANY LILA</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1800" b="1"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DFF97F-385F-4626-A516-B8D34988A426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F553045D-E810-473D-B0CB-339C27480249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -1177,7 +1177,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{68F1BF92-E371-4ECB-8310-22EE57828004}" type="CELLRANGE">
+                <a:fld id="{83D42E0B-8A45-4CCB-B02D-A0DFB4F7F7BD}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1188,7 +1188,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{FA5C5D86-563A-48F6-9598-ADECEBAB0628}" type="PERCENTAGE">
+                <a:fld id="{96D0C994-CA52-4852-B82C-391BFBD27A75}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1283,7 +1283,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{0DDA7C6F-92A9-43C5-92E9-33669AF34C6F}" type="CELLRANGE">
+                <a:fld id="{6DADD7C5-84DF-4EC3-8827-2165CCFCA529}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1294,7 +1294,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{3CB0C594-D308-4A5A-88DC-6319B410E956}" type="PERCENTAGE">
+                <a:fld id="{55B8FAB0-B99E-4EF9-8453-8C18423090A6}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1389,7 +1389,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{D0850E04-4EFB-4A44-B0C7-E821DCF9CDEE}" type="CELLRANGE">
+                <a:fld id="{CB2E2026-B939-42EA-9585-A9EEEC2A6433}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1400,7 +1400,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{2F66FD2C-BDB9-4DAE-9D70-CC65737D7C87}" type="PERCENTAGE">
+                <a:fld id="{3A90F22F-0973-4282-89CA-2E0EF2595FEF}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1495,7 +1495,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{DF3A122E-0094-440D-8FFB-BB30FCBBCEE4}" type="CELLRANGE">
+                <a:fld id="{D7879BDB-044E-4EEB-83CE-49F3A38688C3}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1506,7 +1506,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{93EA13B8-115C-40FA-B1A6-4DD5D6393F67}" type="PERCENTAGE">
+                <a:fld id="{A5BE2335-57C0-4106-9977-09BD5705DB33}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1673,7 +1673,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{68F1BF92-E371-4ECB-8310-22EE57828004}" type="CELLRANGE">
+                    <a:fld id="{83D42E0B-8A45-4CCB-B02D-A0DFB4F7F7BD}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1682,7 +1682,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{FA5C5D86-563A-48F6-9598-ADECEBAB0628}" type="PERCENTAGE">
+                    <a:fld id="{96D0C994-CA52-4852-B82C-391BFBD27A75}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1720,7 +1720,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0DDA7C6F-92A9-43C5-92E9-33669AF34C6F}" type="CELLRANGE">
+                    <a:fld id="{6DADD7C5-84DF-4EC3-8827-2165CCFCA529}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1729,7 +1729,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{3CB0C594-D308-4A5A-88DC-6319B410E956}" type="PERCENTAGE">
+                    <a:fld id="{55B8FAB0-B99E-4EF9-8453-8C18423090A6}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1767,7 +1767,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D0850E04-4EFB-4A44-B0C7-E821DCF9CDEE}" type="CELLRANGE">
+                    <a:fld id="{CB2E2026-B939-42EA-9585-A9EEEC2A6433}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1776,7 +1776,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{2F66FD2C-BDB9-4DAE-9D70-CC65737D7C87}" type="PERCENTAGE">
+                    <a:fld id="{3A90F22F-0973-4282-89CA-2E0EF2595FEF}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1814,7 +1814,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DF3A122E-0094-440D-8FFB-BB30FCBBCEE4}" type="CELLRANGE">
+                    <a:fld id="{D7879BDB-044E-4EEB-83CE-49F3A38688C3}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1823,7 +1823,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{93EA13B8-115C-40FA-B1A6-4DD5D6393F67}" type="PERCENTAGE">
+                    <a:fld id="{A5BE2335-57C0-4106-9977-09BD5705DB33}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -10100,6 +10100,133 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>504286</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>443326</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19576</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Isosceles Triangle 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F71B7DE-7CBE-35D6-FAA7-C3713339BD34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1113886" y="826770"/>
+          <a:ext cx="548640" cy="472966"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>393116</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>129017</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="770981" cy="405432"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{180CBCA1-673B-B494-E9B4-9093821B64F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1002716" y="860537"/>
+          <a:ext cx="770981" cy="405432"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="1"/>
+            <a:t>L</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="1" baseline="0"/>
+            <a:t> I L A</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="2000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F553045D-E810-473D-B0CB-339C27480249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EF60AD-47C3-4837-9AB6-675534328044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -21,18 +21,26 @@
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">table!$A$1:$H$41</definedName>
     <definedName name="NativeTimeline_Date">#N/A</definedName>
+    <definedName name="Slicer_Region">#N/A</definedName>
+    <definedName name="Slicer_Salesman">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId6"/>
+        <x14:slicerCache r:id="rId7"/>
+      </x14:slicerCaches>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
       <x15:timelineCacheRefs>
-        <x15:timelineCacheRef r:id="rId6"/>
+        <x15:timelineCacheRef r:id="rId8"/>
       </x15:timelineCacheRefs>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -243,7 +251,3598 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="524">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -625,10 +4224,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>290180</c:v>
+                  <c:v>120750</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>136350</c:v>
+                  <c:v>34700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1157,48 +4756,6 @@
               <c:y val="-9.7222222222222238E-2"/>
             </c:manualLayout>
           </c:layout>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:fld id="{83D42E0B-8A45-4CCB-B02D-A0DFB4F7F7BD}" type="CELLRANGE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr/>
-                  </a:pPr>
-                  <a:t>[CELLRANGE]</a:t>
-                </a:fld>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t>, </a:t>
-                </a:r>
-                <a:fld id="{96D0C994-CA52-4852-B82C-391BFBD27A75}" type="PERCENTAGE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr/>
-                  </a:pPr>
-                  <a:t>[PERCENTAGE]</a:t>
-                </a:fld>
-                <a:endParaRPr lang="en-US" baseline="0"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1263,48 +4820,6 @@
               <c:y val="-7.8703703703703748E-2"/>
             </c:manualLayout>
           </c:layout>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:fld id="{6DADD7C5-84DF-4EC3-8827-2165CCFCA529}" type="CELLRANGE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr/>
-                  </a:pPr>
-                  <a:t>[CELLRANGE]</a:t>
-                </a:fld>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t>, </a:t>
-                </a:r>
-                <a:fld id="{55B8FAB0-B99E-4EF9-8453-8C18423090A6}" type="PERCENTAGE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr/>
-                  </a:pPr>
-                  <a:t>[PERCENTAGE]</a:t>
-                </a:fld>
-                <a:endParaRPr lang="en-US" baseline="0"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1389,7 +4904,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{CB2E2026-B939-42EA-9585-A9EEEC2A6433}" type="CELLRANGE">
+                <a:fld id="{270467B0-0865-477A-955D-09FAA4C07C2F}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1400,7 +4915,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{3A90F22F-0973-4282-89CA-2E0EF2595FEF}" type="PERCENTAGE">
+                <a:fld id="{30A265E1-18EC-46A8-8255-A5ED3DEE8CB4}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1475,48 +4990,6 @@
               <c:y val="9.722222222222214E-2"/>
             </c:manualLayout>
           </c:layout>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:fld id="{D7879BDB-044E-4EEB-83CE-49F3A38688C3}" type="CELLRANGE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr/>
-                  </a:pPr>
-                  <a:t>[CELLRANGE]</a:t>
-                </a:fld>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t>, </a:t>
-                </a:r>
-                <a:fld id="{A5BE2335-57C0-4106-9977-09BD5705DB33}" type="PERCENTAGE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr/>
-                  </a:pPr>
-                  <a:t>[PERCENTAGE]</a:t>
-                </a:fld>
-                <a:endParaRPr lang="en-US" baseline="0"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1664,8 +5137,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="4.0774719673802244E-2"/>
-                  <c:y val="-9.7222222222222238E-2"/>
+                  <c:x val="8.1549439347604488E-2"/>
+                  <c:y val="0.12037037037037028"/>
                 </c:manualLayout>
               </c:layout>
               <c:tx>
@@ -1673,7 +5146,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{83D42E0B-8A45-4CCB-B02D-A0DFB4F7F7BD}" type="CELLRANGE">
+                    <a:fld id="{270467B0-0865-477A-955D-09FAA4C07C2F}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1682,7 +5155,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{96D0C994-CA52-4852-B82C-391BFBD27A75}" type="PERCENTAGE">
+                    <a:fld id="{30A265E1-18EC-46A8-8255-A5ED3DEE8CB4}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1704,147 +5177,6 @@
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000001-176F-40FB-A8D7-950581BCD903}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.12742099898063192"/>
-                  <c:y val="-7.8703703703703748E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{6DADD7C5-84DF-4EC3-8827-2165CCFCA529}" type="CELLRANGE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:r>
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:t>, </a:t>
-                    </a:r>
-                    <a:fld id="{55B8FAB0-B99E-4EF9-8453-8C18423090A6}" type="PERCENTAGE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[PERCENTAGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US" baseline="0"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-176F-40FB-A8D7-950581BCD903}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="8.1549439347604488E-2"/>
-                  <c:y val="0.12037037037037028"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{CB2E2026-B939-42EA-9585-A9EEEC2A6433}" type="CELLRANGE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:r>
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:t>, </a:t>
-                    </a:r>
-                    <a:fld id="{3A90F22F-0973-4282-89CA-2E0EF2595FEF}" type="PERCENTAGE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[PERCENTAGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US" baseline="0"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-176F-40FB-A8D7-950581BCD903}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-9.1743119266055051E-2"/>
-                  <c:y val="9.722222222222214E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{D7879BDB-044E-4EEB-83CE-49F3A38688C3}" type="CELLRANGE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:r>
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:t>, </a:t>
-                    </a:r>
-                    <a:fld id="{A5BE2335-57C0-4106-9977-09BD5705DB33}" type="PERCENTAGE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[PERCENTAGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US" baseline="0"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-176F-40FB-A8D7-950581BCD903}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1908,18 +5240,9 @@
             <c:strRef>
               <c:f>'data analysis'!$H$21:$H$24</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Alexandria</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Cairo</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>Domietta</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Giza</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1929,18 +5252,9 @@
               <c:f>'data analysis'!$H$21:$H$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>38300</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>24270</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>155450</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>208510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1952,16 +5266,10 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="4"/>
                   <c:pt idx="0">
-                    <c:v>Alexandria</c:v>
+                    <c:v>Domietta</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Cairo</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Domietta</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Giza</c:v>
+                    <c:v>Grand Total</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -2402,7 +5710,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Monitor</c:v>
+                  <c:v>Scanner</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2414,13 +5722,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>306000</c:v>
+                  <c:v>102000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79800</c:v>
+                  <c:v>27300</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12000</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2943,35 +6251,53 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$36:$H$39</c:f>
+              <c:f>'data analysis'!$H$36:$H$42</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Ahmed Said</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Ali Ramadan</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Ashraf Zaki</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>Fathy Ali</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Khaled Hassan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Tamer Mohamed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$36:$I$39</c:f>
+              <c:f>'data analysis'!$I$36:$I$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>66010</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>121600</c:v>
+                  <c:v>56860</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123820</c:v>
+                  <c:v>34100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35260</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18490</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3285,10 +6611,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>290180</c:v>
+                  <c:v>120750</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>136350</c:v>
+                  <c:v>34700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3783,41 +7109,23 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$21:$H$25</c:f>
+              <c:f>'data analysis'!$H$21:$H$22</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Alexandria</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Cairo</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>Domietta</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Giza</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$21:$I$25</c:f>
+              <c:f>'data analysis'!$I$21:$I$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>38300</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>24270</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>155450</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>208510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4088,7 +7396,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Monitor</c:v>
+                  <c:v>Scanner</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4100,13 +7408,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>306000</c:v>
+                  <c:v>102000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79800</c:v>
+                  <c:v>27300</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12000</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4475,35 +7783,53 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$36:$H$39</c:f>
+              <c:f>'data analysis'!$H$36:$H$42</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Ahmed Said</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Ali Ramadan</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Ashraf Zaki</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>Fathy Ali</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Khaled Hassan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Tamer Mohamed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$36:$I$39</c:f>
+              <c:f>'data analysis'!$I$36:$I$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>66010</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>121600</c:v>
+                  <c:v>56860</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123820</c:v>
+                  <c:v>34100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35260</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18490</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9231,7 +12557,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t> $426,530 </a:t>
+              <a:t> $155,450 </a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -9368,7 +12694,7 @@
                 <a:latin typeface="+mj-lt"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>40</a:t>
+              <a:t>19</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="+mj-lt"/>
@@ -9505,7 +12831,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>10663</a:t>
+              <a:t>8182</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -9554,13 +12880,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
+      <xdr:colOff>483870</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -9598,7 +12924,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="762000" y="1661160"/>
+              <a:off x="742950" y="1661160"/>
               <a:ext cx="1569720" cy="1371600"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -10227,6 +13553,162 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>99061</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>483870</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>45721</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="22" name="Salesman 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACECFD1F-B8E4-4194-AB2F-AFD30DF1485C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Salesman 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="742950" y="3208021"/>
+              <a:ext cx="1569720" cy="2141220"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>68581</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>475488</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>53341</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="24" name="Region 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AED8E38F-CCF6-4DC3-9AF5-35D935D40922}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="731520" y="5554981"/>
+              <a:ext cx="1572768" cy="2545080"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10419,16 +13901,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>632460</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>350520</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10451,6 +13933,162 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>632460</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>112395</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Salesman">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41548F97-45E9-3AF9-2932-DBB2F04E2BEB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Salesman"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7749540" y="4663440"/>
+              <a:ext cx="1828800" cy="2581275"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="8" name="Region">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC4471B6-4848-1900-A3FB-F956A41E9C4E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3345180" y="4434840"/>
+              <a:ext cx="1828800" cy="2581275"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -11390,7 +15028,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4624B9DB-16A8-46B5-A956-2588C79515CB}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="H35:I39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="H35:I42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -11438,7 +15076,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="ascending">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="7">
         <item x="0"/>
         <item x="1"/>
@@ -11451,10 +15089,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item x="3"/>
-        <item x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
         <item x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -11902,7 +15540,10 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
     <i>
       <x v="1"/>
     </i>
@@ -11911,6 +15552,12 @@
     </i>
     <i>
       <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -11923,7 +15570,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="517">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -11975,7 +15622,7 @@
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="2">
+  <filters count="1">
     <filter fld="1" type="dateBetween" evalOrder="-1" id="478" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
@@ -11990,13 +15637,6 @@
           <x15:pivotFilter useWholeDay="1"/>
         </ext>
       </extLst>
-    </filter>
-    <filter fld="2" type="count" evalOrder="-1" id="318" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="3" filterVal="3"/>
-        </filterColumn>
-      </autoFilter>
     </filter>
   </filters>
   <extLst>
@@ -12060,13 +15700,23 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="5">
-        <item x="3"/>
+      <items count="7">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -12531,7 +16181,7 @@
       <x v="5"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="6"/>
     </i>
     <i t="grand">
       <x/>
@@ -12544,7 +16194,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="5">
+    <format dxfId="518">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12633,7 +16283,7 @@
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="H20:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="H20:I22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -12681,13 +16331,23 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
+    <pivotField showAll="0">
+      <items count="7">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13135,18 +16795,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -13159,7 +16810,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="6">
+    <format dxfId="519">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13415,8 +17066,26 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="9">
         <item x="6"/>
@@ -13881,7 +17550,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="7">
+    <format dxfId="520">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13984,8 +17653,26 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="9">
         <item x="6"/>
@@ -14437,7 +18124,7 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="8">
+    <format dxfId="521">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14520,8 +18207,26 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField dataField="1" showAll="0">
       <items count="9">
         <item x="6"/>
@@ -14973,7 +18678,7 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="9">
+    <format dxfId="522">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15056,8 +18761,26 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="9">
         <item x="6"/>
@@ -15509,7 +19232,7 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="10">
+    <format dxfId="523">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15559,15 +19282,79 @@
 </queryTable>
 </file>
 
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Salesman" xr10:uid="{FB6793B6-24A6-48C3-953A-7042A4319377}" sourceName="Salesman">
+  <pivotTables>
+    <pivotTable tabId="3" name="PivotTable7"/>
+    <pivotTable tabId="3" name="PivotTable1"/>
+    <pivotTable tabId="3" name="PivotTable2"/>
+    <pivotTable tabId="3" name="PivotTable3"/>
+    <pivotTable tabId="3" name="PivotTable4"/>
+    <pivotTable tabId="3" name="PivotTable5"/>
+    <pivotTable tabId="3" name="PivotTable6"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="548194542">
+      <items count="6">
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+        <i x="5" s="1"/>
+        <i x="4" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{AA6E0936-3738-4F54-BFBB-5DF14712AC6D}" sourceName="Region">
+  <pivotTables>
+    <pivotTable tabId="3" name="PivotTable7"/>
+    <pivotTable tabId="3" name="PivotTable1"/>
+    <pivotTable tabId="3" name="PivotTable2"/>
+    <pivotTable tabId="3" name="PivotTable3"/>
+    <pivotTable tabId="3" name="PivotTable4"/>
+    <pivotTable tabId="3" name="PivotTable5"/>
+    <pivotTable tabId="3" name="PivotTable6"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="548194542">
+      <items count="4">
+        <i x="3"/>
+        <i x="0"/>
+        <i x="1" s="1"/>
+        <i x="2"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Salesman 1" xr10:uid="{B0813A65-02C1-49D2-9E9F-65CDFDF1159A}" cache="Slicer_Salesman" caption="Salesman" rowHeight="247650"/>
+  <slicer name="Region 1" xr10:uid="{E3223445-0FF4-4A60-A5DF-67216457E98D}" cache="Slicer_Region" caption="Region" rowHeight="247650"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Salesman" xr10:uid="{161A2E65-A067-4011-B4D5-390799157232}" cache="Slicer_Salesman" caption="Salesman" rowHeight="247650"/>
+  <slicer name="Region" xr10:uid="{242EC33E-2411-4AC9-A475-16141AC49A62}" cache="Slicer_Region" caption="Region" rowHeight="247650"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}" name="sales" displayName="sales" ref="A1:H41" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="516"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="515"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="514"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="513"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -15929,9 +19716,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
       <x15:timelineRefs>
-        <x15:timelineRef r:id="rId2"/>
+        <x15:timelineRef r:id="rId3"/>
       </x15:timelineRefs>
     </ext>
   </extLst>
@@ -15940,13 +19732,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1649C905-6944-4F98-B4AE-37BE068CDF30}">
-  <dimension ref="A2:M39"/>
+  <dimension ref="A2:M42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -15981,39 +19773,39 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
-        <v>426530</v>
+        <v>155450</v>
       </c>
       <c r="C6" s="6">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E6" s="6">
-        <v>10663.25</v>
+        <v>8181.5789473684208</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="6">
-        <v>290180</v>
+        <v>120750</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <f>GETPIVOTDATA("Amount",$A$5)</f>
-        <v>426530</v>
+        <v>155450</v>
       </c>
       <c r="C7">
         <f>GETPIVOTDATA("Item",$C$5)</f>
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E7" s="8">
         <f>GETPIVOTDATA("Amount",$E$5)</f>
-        <v>10663.25</v>
+        <v>8181.5789473684208</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>34</v>
       </c>
       <c r="I7" s="6">
-        <v>136350</v>
+        <v>34700</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -16021,7 +19813,7 @@
         <v>27</v>
       </c>
       <c r="I8" s="6">
-        <v>426530</v>
+        <v>155450</v>
       </c>
     </row>
     <row r="20" spans="8:13" x14ac:dyDescent="0.3">
@@ -16034,10 +19826,10 @@
     </row>
     <row r="21" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H21" s="5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I21" s="6">
-        <v>38300</v>
+        <v>155450</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>26</v>
@@ -16048,58 +19840,40 @@
     </row>
     <row r="22" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H22" s="5" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I22" s="6">
-        <v>24270</v>
+        <v>155450</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>19</v>
       </c>
       <c r="M22" s="6">
-        <v>306000</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="23" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" s="6">
-        <v>155450</v>
-      </c>
       <c r="L23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="M23" s="6">
-        <v>79800</v>
+        <v>27300</v>
       </c>
     </row>
     <row r="24" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="6">
-        <v>208510</v>
-      </c>
       <c r="L24" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="M24" s="6">
-        <v>12000</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="25" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I25" s="6">
-        <v>426530</v>
-      </c>
       <c r="L25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="M25" s="6">
-        <v>397800</v>
+        <v>139800</v>
       </c>
     </row>
     <row r="35" spans="8:9" x14ac:dyDescent="0.3">
@@ -16112,34 +19886,58 @@
     </row>
     <row r="36" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H36" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I36" s="6">
-        <v>66010</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="37" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H37" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I37" s="6">
-        <v>121600</v>
+        <v>56860</v>
       </c>
     </row>
     <row r="38" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H38" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I38" s="6">
-        <v>123820</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="39" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="6">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="6">
+        <v>35260</v>
+      </c>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="6">
+        <v>18490</v>
+      </c>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I39" s="6">
-        <v>311430</v>
+      <c r="I42" s="6">
+        <v>155450</v>
       </c>
     </row>
   </sheetData>
@@ -16149,9 +19947,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId8"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId9"/>
+      </x14:slicerList>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
       <x15:timelineRefs>
-        <x15:timelineRef r:id="rId9"/>
+        <x15:timelineRef r:id="rId10"/>
       </x15:timelineRefs>
     </ext>
   </extLst>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EF60AD-47C3-4837-9AB6-675534328044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50883547-9298-42DA-9A9D-4F3D9EFF7EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -251,1190 +251,7 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="524">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="355">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4904,7 +3721,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{270467B0-0865-477A-955D-09FAA4C07C2F}" type="CELLRANGE">
+                <a:fld id="{502845F5-63E0-4354-9E93-04323B850460}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -4915,7 +3732,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{30A265E1-18EC-46A8-8255-A5ED3DEE8CB4}" type="PERCENTAGE">
+                <a:fld id="{51BA0436-7A9B-4B6C-8F2A-82C3460B240F}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -5146,7 +3963,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{270467B0-0865-477A-955D-09FAA4C07C2F}" type="CELLRANGE">
+                    <a:fld id="{502845F5-63E0-4354-9E93-04323B850460}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5155,7 +3972,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{30A265E1-18EC-46A8-8255-A5ED3DEE8CB4}" type="PERCENTAGE">
+                    <a:fld id="{51BA0436-7A9B-4B6C-8F2A-82C3460B240F}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -12468,6 +11285,95 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Rectangle: Rounded Corners 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D598809-2899-CA04-5365-D4B55ECB3A62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10629900" cy="10294620"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 1531"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:glow rad="381000">
+            <a:schemeClr val="accent2">
+              <a:satMod val="175000"/>
+              <a:alpha val="40000"/>
+            </a:schemeClr>
+          </a:glow>
+          <a:outerShdw blurRad="50800" dist="38100" dir="8100000" algn="tr" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+          <a:softEdge rad="0"/>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="obliqueTopLeft"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d z="158750"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
@@ -15570,7 +14476,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="517">
+    <format dxfId="348">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16194,7 +15100,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="518">
+    <format dxfId="349">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16810,7 +15716,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="519">
+    <format dxfId="350">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -17550,7 +16456,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="520">
+    <format dxfId="351">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -18124,7 +17030,7 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="521">
+    <format dxfId="352">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -18678,7 +17584,7 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="522">
+    <format dxfId="353">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -19232,7 +18138,7 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="523">
+    <format dxfId="354">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -19351,10 +18257,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="516"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="515"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="514"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="513"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="347"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="346"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="345"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="344"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50883547-9298-42DA-9A9D-4F3D9EFF7EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC1819C-370B-4C28-AE89-CA0855A14835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -3721,7 +3721,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{502845F5-63E0-4354-9E93-04323B850460}" type="CELLRANGE">
+                <a:fld id="{FEEC32A3-2FF5-4CFB-8605-4A4C5AD2D8B3}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -3732,7 +3732,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{51BA0436-7A9B-4B6C-8F2A-82C3460B240F}" type="PERCENTAGE">
+                <a:fld id="{66702D19-7F1F-4C38-A0FE-C9DC081F3236}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -3963,7 +3963,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{502845F5-63E0-4354-9E93-04323B850460}" type="CELLRANGE">
+                    <a:fld id="{FEEC32A3-2FF5-4CFB-8605-4A4C5AD2D8B3}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3972,7 +3972,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{51BA0436-7A9B-4B6C-8F2A-82C3460B240F}" type="PERCENTAGE">
+                    <a:fld id="{66702D19-7F1F-4C38-A0FE-C9DC081F3236}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC1819C-370B-4C28-AE89-CA0855A14835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A4B093-34FC-4ED4-A4C5-A3B6E851FECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -251,2415 +251,7 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="355">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -3610,7 +1202,6 @@
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:dlblFieldTable/>
               <c15:showDataLabelsRange val="1"/>
             </c:ext>
           </c:extLst>
@@ -3674,7 +1265,6 @@
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:dlblFieldTable/>
               <c15:showDataLabelsRange val="1"/>
             </c:ext>
           </c:extLst>
@@ -3721,7 +1311,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{FEEC32A3-2FF5-4CFB-8605-4A4C5AD2D8B3}" type="CELLRANGE">
+                <a:fld id="{358BDF7D-75EF-412E-A458-8EDCA1788404}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -3732,7 +1322,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{66702D19-7F1F-4C38-A0FE-C9DC081F3236}" type="PERCENTAGE">
+                <a:fld id="{3777432D-6524-49AA-895C-4B78A5F60EBA}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -3844,7 +1434,6 @@
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:dlblFieldTable/>
               <c15:showDataLabelsRange val="1"/>
             </c:ext>
           </c:extLst>
@@ -3963,7 +1552,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FEEC32A3-2FF5-4CFB-8605-4A4C5AD2D8B3}" type="CELLRANGE">
+                    <a:fld id="{358BDF7D-75EF-412E-A458-8EDCA1788404}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3972,7 +1561,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{66702D19-7F1F-4C38-A0FE-C9DC081F3236}" type="PERCENTAGE">
+                    <a:fld id="{3777432D-6524-49AA-895C-4B78A5F60EBA}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -11796,8 +9385,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+      <mc:Choice Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Date 1">
@@ -11815,12 +9404,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date 1"/>
+              <tsle:timeslicer name="Date 1"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12231,9 +9820,53 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:gradFill flip="none" rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="FFC000">
+                <a:shade val="30000"/>
+                <a:satMod val="115000"/>
+              </a:srgbClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:srgbClr val="FFC000">
+                <a:shade val="67500"/>
+                <a:satMod val="115000"/>
+              </a:srgbClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="FFC000">
+                <a:shade val="100000"/>
+                <a:satMod val="115000"/>
+              </a:srgbClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="100000" b="100000"/>
+          </a:path>
+          <a:tileRect t="-100000" r="-100000"/>
+        </a:gradFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" dist="228600" dir="2700000" algn="ctr">
+            <a:srgbClr val="000000">
+              <a:alpha val="30000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="glow" dir="t">
+            <a:rot lat="0" lon="0" rev="4800000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d prstMaterial="matte">
+          <a:bevelT w="127000" h="63500"/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -12364,6 +9997,9 @@
         <a:prstGeom prst="triangle">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFC000"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -12472,8 +10108,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>45721</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="22" name="Salesman 1">
@@ -12496,7 +10132,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12550,8 +10186,8 @@
       <xdr:row>44</xdr:row>
       <xdr:rowOff>53341</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="24" name="Region 1">
@@ -12574,7 +10210,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12854,8 +10490,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>112395</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Salesman">
@@ -12878,7 +10514,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12932,8 +10568,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Region">
@@ -12956,7 +10592,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13933,6 +11569,1701 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="9"/>
+    <field x="8"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="5">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="6">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4624B9DB-16A8-46B5-A956-2588C79515CB}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="H35:I42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -14476,7 +13807,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="348">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14556,7 +13887,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57377406-EF9D-40FA-8C1C-85593D1E9337}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="L21:M25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -15100,7 +14431,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="349">
+    <format dxfId="8">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15187,7 +14518,561 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="41">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="6"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="29">
+        <item x="17"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="44927"/>
+            <customFilter operator="lessThanOrEqual" val="44985"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="H20:I22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -15716,7 +15601,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="350">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15922,2255 +15807,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="369">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="3">
-    <field x="9"/>
-    <field x="8"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="351">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974FEEDC-EEE3-49C4-A2FB-AE1EFBA9B27E}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:E6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="352">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{345D8BDC-BD52-413E-910B-58A138F0B6C8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="353">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EB74471-1F15-4675-88B3-E79C41D747E2}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="41">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="6"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="29">
-        <item x="17"/>
-        <item x="6"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="4"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="5"/>
-        <item x="16"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="354">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters and="1">
-            <customFilter operator="greaterThanOrEqual" val="44927"/>
-            <customFilter operator="lessThanOrEqual" val="44985"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
-          <x15:pivotFilter useWholeDay="1"/>
-        </ext>
-      </extLst>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{45FE5043-C852-44A5-BF97-16E323DBE1F5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9">
@@ -18257,10 +15893,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="347"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="346"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="345"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="344"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A4B093-34FC-4ED4-A4C5-A3B6E851FECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1FAAF8-3877-4538-9C50-7D78229FE8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -315,6 +315,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFDD71"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1311,7 +1316,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{358BDF7D-75EF-412E-A458-8EDCA1788404}" type="CELLRANGE">
+                <a:fld id="{DA4B05AC-683C-4A27-AD91-C23E5434802F}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1322,7 +1327,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{3777432D-6524-49AA-895C-4B78A5F60EBA}" type="PERCENTAGE">
+                <a:fld id="{D3EA0865-3403-45FA-BC51-85AB7CCD831A}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1552,7 +1557,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{358BDF7D-75EF-412E-A458-8EDCA1788404}" type="CELLRANGE">
+                    <a:fld id="{DA4B05AC-683C-4A27-AD91-C23E5434802F}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1561,7 +1566,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{3777432D-6524-49AA-895C-4B78A5F60EBA}" type="PERCENTAGE">
+                    <a:fld id="{D3EA0865-3403-45FA-BC51-85AB7CCD831A}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -8907,9 +8912,7 @@
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
+          <a:srgbClr val="FFDD71"/>
         </a:solidFill>
         <a:ln>
           <a:noFill/>
@@ -9012,18 +9015,53 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="95000"/>
-            </a:schemeClr>
-          </a:solidFill>
+          <a:gradFill flip="none" rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="30000"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="67500"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="100000"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+            </a:gsLst>
+            <a:path path="circle">
+              <a:fillToRect t="100000" r="100000"/>
+            </a:path>
+            <a:tileRect l="-100000" b="-100000"/>
+          </a:gradFill>
           <a:ln w="9525" cmpd="sng">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:shade val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="190500" dist="228600" dir="2700000" algn="ctr">
+              <a:srgbClr val="000000">
+                <a:alpha val="30000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="glow" dir="t">
+              <a:rot lat="0" lon="0" rev="4800000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d prstMaterial="matte">
+            <a:bevelT w="127000" h="63500"/>
+          </a:sp3d>
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="0">
@@ -9149,18 +9187,53 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="95000"/>
-            </a:schemeClr>
-          </a:solidFill>
+          <a:gradFill flip="none" rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="30000"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="67500"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="100000"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+            </a:gsLst>
+            <a:path path="circle">
+              <a:fillToRect t="100000" r="100000"/>
+            </a:path>
+            <a:tileRect l="-100000" b="-100000"/>
+          </a:gradFill>
           <a:ln w="9525" cmpd="sng">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:shade val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="190500" dist="228600" dir="2700000" algn="ctr">
+              <a:srgbClr val="000000">
+                <a:alpha val="30000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="glow" dir="t">
+              <a:rot lat="0" lon="0" rev="4800000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d prstMaterial="matte">
+            <a:bevelT w="127000" h="63500"/>
+          </a:sp3d>
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="0">

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1FAAF8-3877-4538-9C50-7D78229FE8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F091165-B633-441F-BD63-6F2E227B2CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -251,7 +251,203 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="39">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1316,7 +1512,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{DA4B05AC-683C-4A27-AD91-C23E5434802F}" type="CELLRANGE">
+                <a:fld id="{08592724-D8EE-43FB-880A-8AEF1CB421A1}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1327,7 +1523,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{D3EA0865-3403-45FA-BC51-85AB7CCD831A}" type="PERCENTAGE">
+                <a:fld id="{6993F9A7-906F-4EB4-B3B2-9D8150DC029D}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1557,7 +1753,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DA4B05AC-683C-4A27-AD91-C23E5434802F}" type="CELLRANGE">
+                    <a:fld id="{08592724-D8EE-43FB-880A-8AEF1CB421A1}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1566,7 +1762,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{D3EA0865-3403-45FA-BC51-85AB7CCD831A}" type="PERCENTAGE">
+                    <a:fld id="{6993F9A7-906F-4EB4-B3B2-9D8150DC029D}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -9359,18 +9555,53 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="95000"/>
-            </a:schemeClr>
-          </a:solidFill>
+          <a:gradFill flip="none" rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="30000"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="67500"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:srgbClr val="FFC000">
+                  <a:shade val="100000"/>
+                  <a:satMod val="115000"/>
+                </a:srgbClr>
+              </a:gs>
+            </a:gsLst>
+            <a:path path="circle">
+              <a:fillToRect t="100000" r="100000"/>
+            </a:path>
+            <a:tileRect l="-100000" b="-100000"/>
+          </a:gradFill>
           <a:ln w="9525" cmpd="sng">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:shade val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="190500" dist="228600" dir="2700000" algn="ctr">
+              <a:srgbClr val="000000">
+                <a:alpha val="30000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="glow" dir="t">
+              <a:rot lat="0" lon="0" rev="4800000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d prstMaterial="matte">
+            <a:bevelT w="127000" h="63500"/>
+          </a:sp3d>
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="0">
@@ -12175,7 +12406,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="32">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12201,7 +12432,7 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="509" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -12749,13 +12980,13 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="5">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="509" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -13303,13 +13534,13 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="6">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="502" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -13880,7 +14111,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="7">
+    <format dxfId="35">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13933,7 +14164,7 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="478" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="510" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -14504,7 +14735,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="8">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14557,7 +14788,7 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="2">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="479" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="511" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -15112,13 +15343,13 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="9">
+    <format dxfId="37">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="470" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="502" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -15674,7 +15905,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="10">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15853,7 +16084,7 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="1" type="dateBetween" evalOrder="-1" id="477" name="Date">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="509" name="Date">
       <autoFilter ref="A1">
         <filterColumn colId="0">
           <customFilters and="1">
@@ -15966,10 +16197,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="28"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -16354,7 +16585,7 @@
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5546875" bestFit="1" customWidth="1"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F091165-B633-441F-BD63-6F2E227B2CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA19C59-1229-48E1-BB54-3D4A9DA82CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -554,9 +554,8 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -565,14 +564,32 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="1"/>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t>sales</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t> by months</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" b="1"/>
+            <a:endParaRPr lang="en-US" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -591,9 +608,8 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -730,14 +746,30 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="10000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="dot"/>
+          <c:size val="22"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="10000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -804,14 +836,30 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="10000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="dot"/>
+            <c:size val="22"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:cat>
             <c:strRef>
@@ -857,6 +905,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1216137871"/>
         <c:axId val="1216138351"/>
@@ -874,13 +923,14 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
               </a:schemeClr>
             </a:solidFill>
+            <a:prstDash val="dash"/>
             <a:round/>
           </a:ln>
           <a:effectLst/>
@@ -890,11 +940,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -916,23 +965,10 @@
         <c:axId val="1216138351"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -949,11 +985,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -988,9 +1023,32 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:srgbClr val="FFC000">
+            <a:shade val="30000"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="50000">
+          <a:srgbClr val="FFC000">
+            <a:shade val="67500"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:srgbClr val="FFC000">
+            <a:shade val="100000"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect t="100000" r="100000"/>
+      </a:path>
+      <a:tileRect l="-100000" b="-100000"/>
+    </a:gradFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -1512,7 +1570,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{08592724-D8EE-43FB-880A-8AEF1CB421A1}" type="CELLRANGE">
+                <a:fld id="{B7E78C7C-7642-49BB-A231-FA80D04A8E7A}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1523,7 +1581,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{6993F9A7-906F-4EB4-B3B2-9D8150DC029D}" type="PERCENTAGE">
+                <a:fld id="{8E3BE822-79BF-4A4F-AD9F-01FFAC3F2027}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -1753,7 +1811,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{08592724-D8EE-43FB-880A-8AEF1CB421A1}" type="CELLRANGE">
+                    <a:fld id="{B7E78C7C-7642-49BB-A231-FA80D04A8E7A}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1762,7 +1820,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{6993F9A7-906F-4EB4-B3B2-9D8150DC029D}" type="PERCENTAGE">
+                    <a:fld id="{8E3BE822-79BF-4A4F-AD9F-01FFAC3F2027}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -11873,7 +11931,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1DCBE86-DE74-4357-B405-7E7C9F6C13A1}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="H5:I8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA19C59-1229-48E1-BB54-3D4A9DA82CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6A9D1A-82F0-43E7-B735-F1CA76982CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="35">
   <si>
     <t>S No</t>
   </si>
@@ -251,7 +251,56 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -513,6 +562,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFECAF"/>
+      <color rgb="FFFFDC6D"/>
+      <color rgb="FFEEB500"/>
+      <color rgb="FF8A6900"/>
       <color rgb="FFFFDD71"/>
     </mruColors>
   </colors>
@@ -882,10 +935,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>120750</c:v>
+                  <c:v>290180</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34700</c:v>
+                  <c:v>136350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1059,6 +1112,13 @@
       <a:round/>
     </a:ln>
     <a:effectLst/>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
+    <a:sp3d prstMaterial="matte">
+      <a:bevelT w="127000" h="63500"/>
+    </a:sp3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -1118,9 +1178,8 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1129,14 +1188,32 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="1"/>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t>amount</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t> by region</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" b="1"/>
+            <a:endParaRPr lang="en-US" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1155,9 +1232,8 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1375,11 +1451,10 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="10000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -1407,12 +1482,10 @@
         <c:idx val="7"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="FFDC6D"/>
           </a:solidFill>
           <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1424,132 +1497,6 @@
               <c:y val="-9.7222222222222238E-2"/>
             </c:manualLayout>
           </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:showDataLabelsRange val="1"/>
-            </c:ext>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="8"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="0.12742099898063192"/>
-              <c:y val="-7.8703703703703748E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:showDataLabelsRange val="1"/>
-            </c:ext>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="9"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="8.1549439347604488E-2"/>
-              <c:y val="0.12037037037037028"/>
-            </c:manualLayout>
-          </c:layout>
           <c:tx>
             <c:rich>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -1558,11 +1505,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="10000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -1570,10 +1516,16 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{B7E78C7C-7642-49BB-A231-FA80D04A8E7A}" type="CELLRANGE">
-                  <a:rPr lang="en-US" baseline="0"/>
+                <a:fld id="{2AE37A7E-30B3-4200-A591-4497C611D6FD}" type="CELLRANGE">
+                  <a:rPr lang="en-US"/>
                   <a:pPr>
-                    <a:defRPr/>
+                    <a:defRPr b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
                   </a:pPr>
                   <a:t>[CELLRANGE]</a:t>
                 </a:fld>
@@ -1581,10 +1533,16 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{8E3BE822-79BF-4A4F-AD9F-01FFAC3F2027}" type="PERCENTAGE">
+                <a:fld id="{04E09333-67D9-4F91-81B5-E511B3859BD8}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
-                    <a:defRPr/>
+                    <a:defRPr b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
                   </a:pPr>
                   <a:t>[PERCENTAGE]</a:t>
                 </a:fld>
@@ -1606,11 +1564,238 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="10000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:dlblFieldTable/>
+              <c15:showDataLabelsRange val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="EEB500"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0.12742099898063192"/>
+              <c:y val="-7.8703703703703748E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="10000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:fld id="{739BB34D-32C2-486B-B65D-449C51618E08}" type="CELLRANGE">
+                  <a:rPr lang="en-US"/>
+                  <a:pPr>
+                    <a:defRPr b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:t>[CELLRANGE]</a:t>
+                </a:fld>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>, </a:t>
+                </a:r>
+                <a:fld id="{91BDEF3C-D92A-4623-B70B-8A05DDC81C12}" type="PERCENTAGE">
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:pPr>
+                    <a:defRPr b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:t>[PERCENTAGE]</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" baseline="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="10000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:dlblFieldTable/>
+              <c15:showDataLabelsRange val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="8A6900"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="8.1549439347604488E-2"/>
+              <c:y val="0.12037037037037028"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="10000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:fld id="{E63DAC9B-FDB8-40EC-AB0B-CF2E20C296C5}" type="CELLRANGE">
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:pPr>
+                    <a:defRPr b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:t>[CELLRANGE]</a:t>
+                </a:fld>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>, </a:t>
+                </a:r>
+                <a:fld id="{2B3AA187-31E8-42F9-BD54-8849D9F8F7A2}" type="PERCENTAGE">
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:pPr>
+                    <a:defRPr b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:t>[PERCENTAGE]</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" baseline="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="10000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -1639,12 +1824,10 @@
         <c:idx val="10"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="FFECAF"/>
           </a:solidFill>
           <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1656,6 +1839,59 @@
               <c:y val="9.722222222222214E-2"/>
             </c:manualLayout>
           </c:layout>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="10000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:fld id="{349E3509-FBE0-4FD9-9D9C-E55D02CB0D9A}" type="CELLRANGE">
+                  <a:rPr lang="en-US"/>
+                  <a:pPr>
+                    <a:defRPr b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:t>[CELLRANGE]</a:t>
+                </a:fld>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>, </a:t>
+                </a:r>
+                <a:fld id="{BBD6F1EB-9824-43FE-AB0E-CE9491288FC8}" type="PERCENTAGE">
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:pPr>
+                    <a:defRPr b="1">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:t>[PERCENTAGE]</a:t>
+                </a:fld>
+                <a:endParaRPr lang="en-US" baseline="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1670,11 +1906,10 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="10000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -1693,6 +1928,7 @@
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:dlblFieldTable/>
               <c15:showDataLabelsRange val="1"/>
             </c:ext>
           </c:extLst>
@@ -1722,12 +1958,10 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="FFDC6D"/>
               </a:solidFill>
               <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -1742,12 +1976,10 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="EEB500"/>
               </a:solidFill>
               <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -1762,12 +1994,10 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="8A6900"/>
               </a:solidFill>
               <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -1782,12 +2012,10 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="FFECAF"/>
               </a:solidFill>
               <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -1802,8 +2030,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="8.1549439347604488E-2"/>
-                  <c:y val="0.12037037037037028"/>
+                  <c:x val="4.0774719673802244E-2"/>
+                  <c:y val="-9.7222222222222238E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:tx>
@@ -1811,8 +2039,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B7E78C7C-7642-49BB-A231-FA80D04A8E7A}" type="CELLRANGE">
-                      <a:rPr lang="en-US" baseline="0"/>
+                    <a:fld id="{2AE37A7E-30B3-4200-A591-4497C611D6FD}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -1820,7 +2048,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{8E3BE822-79BF-4A4F-AD9F-01FFAC3F2027}" type="PERCENTAGE">
+                    <a:fld id="{04E09333-67D9-4F91-81B5-E511B3859BD8}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1845,6 +2073,147 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.12742099898063192"/>
+                  <c:y val="-7.8703703703703748E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{739BB34D-32C2-486B-B65D-449C51618E08}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{91BDEF3C-D92A-4623-B70B-8A05DDC81C12}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[PERCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-176F-40FB-A8D7-950581BCD903}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.1549439347604488E-2"/>
+                  <c:y val="0.12037037037037028"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E63DAC9B-FDB8-40EC-AB0B-CF2E20C296C5}" type="CELLRANGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{2B3AA187-31E8-42F9-BD54-8849D9F8F7A2}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[PERCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-176F-40FB-A8D7-950581BCD903}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-9.1743119266055051E-2"/>
+                  <c:y val="9.722222222222214E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{349E3509-FBE0-4FD9-9D9C-E55D02CB0D9A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>, </a:t>
+                    </a:r>
+                    <a:fld id="{BBD6F1EB-9824-43FE-AB0E-CE9491288FC8}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr/>
+                      <a:t>[PERCENTAGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-176F-40FB-A8D7-950581BCD903}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1859,11 +2228,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="10000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -1905,9 +2273,18 @@
             <c:strRef>
               <c:f>'data analysis'!$H$21:$H$24</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>Alexandria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cairo</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Domietta</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Giza</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1917,9 +2294,18 @@
               <c:f>'data analysis'!$H$21:$H$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>38300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24270</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>155450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>208510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1931,10 +2317,16 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="4"/>
                   <c:pt idx="0">
+                    <c:v>Alexandria</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Cairo</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
                     <c:v>Domietta</c:v>
                   </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Grand Total</c:v>
+                  <c:pt idx="3">
+                    <c:v>Giza</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -1976,9 +2368,32 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:srgbClr val="FFC000">
+            <a:shade val="30000"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="50000">
+          <a:srgbClr val="FFC000">
+            <a:shade val="67500"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:srgbClr val="FFC000">
+            <a:shade val="100000"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect t="100000" r="100000"/>
+      </a:path>
+      <a:tileRect l="-100000" b="-100000"/>
+    </a:gradFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -1989,6 +2404,13 @@
       <a:round/>
     </a:ln>
     <a:effectLst/>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
+    <a:sp3d prstMaterial="matte">
+      <a:bevelT w="127000" h="63500"/>
+    </a:sp3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -2375,7 +2797,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scanner</c:v>
+                  <c:v>Monitor</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2387,13 +2809,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>102000</c:v>
+                  <c:v>306000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27300</c:v>
+                  <c:v>79800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10500</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2947,22 +3369,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2040</c:v>
+                  <c:v>44190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56860</c:v>
+                  <c:v>66010</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34100</c:v>
+                  <c:v>121600</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8700</c:v>
+                  <c:v>123820</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35260</c:v>
+                  <c:v>39400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18490</c:v>
+                  <c:v>31510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3276,10 +3698,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>120750</c:v>
+                  <c:v>290180</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34700</c:v>
+                  <c:v>136350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3774,23 +4196,41 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$21:$H$22</c:f>
+              <c:f>'data analysis'!$H$21:$H$25</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>Alexandria</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cairo</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Domietta</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Giza</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$21:$I$22</c:f>
+              <c:f>'data analysis'!$I$21:$I$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>38300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24270</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>155450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>208510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4061,7 +4501,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Scanner</c:v>
+                  <c:v>Monitor</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4073,13 +4513,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>102000</c:v>
+                  <c:v>306000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27300</c:v>
+                  <c:v>79800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10500</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4479,22 +4919,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2040</c:v>
+                  <c:v>44190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56860</c:v>
+                  <c:v>66010</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34100</c:v>
+                  <c:v>121600</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8700</c:v>
+                  <c:v>123820</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35260</c:v>
+                  <c:v>39400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18490</c:v>
+                  <c:v>31510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9344,7 +9784,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t> $155,450 </a:t>
+              <a:t> $426,530 </a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -9516,7 +9956,7 @@
                 <a:latin typeface="+mj-lt"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>19</a:t>
+              <a:t>40</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="+mj-lt"/>
@@ -9688,7 +10128,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>8182</a:t>
+              <a:t>10663</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -10926,7 +11366,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
+      <xdr:colOff>213360</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
@@ -11993,10 +12433,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -12464,7 +12904,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="32">
+    <format dxfId="39">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12580,10 +13020,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13038,7 +13478,7 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="33">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13134,10 +13574,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13592,7 +14032,7 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="34">
+    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13688,10 +14128,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14169,7 +14609,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="35">
+    <format dxfId="42">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14312,10 +14752,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14780,7 +15220,7 @@
       <x v="5"/>
     </i>
     <i>
-      <x v="6"/>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -14793,7 +15233,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="36">
+    <format dxfId="43">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14943,10 +15383,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -15401,7 +15841,7 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="37">
+    <format dxfId="44">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15436,7 +15876,7 @@
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5387BD-8EFF-428C-8AAB-833B9D93326E}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="H20:I22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="H20:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -15497,10 +15937,10 @@
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -15948,9 +16388,18 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -15963,7 +16412,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="38">
+    <format dxfId="45">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16226,10 +16675,10 @@
   <data>
     <tabular pivotCacheId="548194542">
       <items count="4">
-        <i x="3"/>
-        <i x="0"/>
+        <i x="3" s="1"/>
+        <i x="0" s="1"/>
         <i x="1" s="1"/>
-        <i x="2"/>
+        <i x="2" s="1"/>
       </items>
     </tabular>
   </data>
@@ -16255,10 +16704,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="35"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -16642,8 +17091,8 @@
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5546875" bestFit="1" customWidth="1"/>
@@ -16677,39 +17126,39 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
-        <v>155450</v>
+        <v>426530</v>
       </c>
       <c r="C6" s="6">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6">
-        <v>8181.5789473684208</v>
+        <v>10663.25</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="6">
-        <v>120750</v>
+        <v>290180</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <f>GETPIVOTDATA("Amount",$A$5)</f>
-        <v>155450</v>
+        <v>426530</v>
       </c>
       <c r="C7">
         <f>GETPIVOTDATA("Item",$C$5)</f>
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E7" s="8">
         <f>GETPIVOTDATA("Amount",$E$5)</f>
-        <v>8181.5789473684208</v>
+        <v>10663.25</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>34</v>
       </c>
       <c r="I7" s="6">
-        <v>34700</v>
+        <v>136350</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -16717,7 +17166,7 @@
         <v>27</v>
       </c>
       <c r="I8" s="6">
-        <v>155450</v>
+        <v>426530</v>
       </c>
     </row>
     <row r="20" spans="8:13" x14ac:dyDescent="0.3">
@@ -16730,10 +17179,10 @@
     </row>
     <row r="21" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H21" s="5" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>155450</v>
+        <v>38300</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>26</v>
@@ -16744,40 +17193,58 @@
     </row>
     <row r="22" spans="8:13" x14ac:dyDescent="0.3">
       <c r="H22" s="5" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I22" s="6">
-        <v>155450</v>
+        <v>24270</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>19</v>
       </c>
       <c r="M22" s="6">
-        <v>102000</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="23" spans="8:13" x14ac:dyDescent="0.3">
+      <c r="H23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="6">
+        <v>155450</v>
+      </c>
       <c r="L23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="M23" s="6">
-        <v>27300</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="24" spans="8:13" x14ac:dyDescent="0.3">
+      <c r="H24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="6">
+        <v>208510</v>
+      </c>
       <c r="L24" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="M24" s="6">
-        <v>10500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="25" spans="8:13" x14ac:dyDescent="0.3">
+      <c r="H25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="6">
+        <v>426530</v>
+      </c>
       <c r="L25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="M25" s="6">
-        <v>139800</v>
+        <v>397800</v>
       </c>
     </row>
     <row r="35" spans="8:9" x14ac:dyDescent="0.3">
@@ -16793,7 +17260,7 @@
         <v>8</v>
       </c>
       <c r="I36" s="6">
-        <v>2040</v>
+        <v>44190</v>
       </c>
     </row>
     <row r="37" spans="8:9" x14ac:dyDescent="0.3">
@@ -16801,7 +17268,7 @@
         <v>11</v>
       </c>
       <c r="I37" s="6">
-        <v>56860</v>
+        <v>66010</v>
       </c>
     </row>
     <row r="38" spans="8:9" x14ac:dyDescent="0.3">
@@ -16809,7 +17276,7 @@
         <v>14</v>
       </c>
       <c r="I38" s="6">
-        <v>34100</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="39" spans="8:9" x14ac:dyDescent="0.3">
@@ -16817,7 +17284,7 @@
         <v>16</v>
       </c>
       <c r="I39" s="6">
-        <v>8700</v>
+        <v>123820</v>
       </c>
     </row>
     <row r="40" spans="8:9" x14ac:dyDescent="0.3">
@@ -16825,7 +17292,7 @@
         <v>18</v>
       </c>
       <c r="I40" s="6">
-        <v>35260</v>
+        <v>39400</v>
       </c>
     </row>
     <row r="41" spans="8:9" x14ac:dyDescent="0.3">
@@ -16833,7 +17300,7 @@
         <v>17</v>
       </c>
       <c r="I41" s="6">
-        <v>18490</v>
+        <v>31510</v>
       </c>
     </row>
     <row r="42" spans="8:9" x14ac:dyDescent="0.3">
@@ -16841,7 +17308,7 @@
         <v>27</v>
       </c>
       <c r="I42" s="6">
-        <v>155450</v>
+        <v>426530</v>
       </c>
     </row>
   </sheetData>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6A9D1A-82F0-43E7-B735-F1CA76982CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0198854-854B-445A-9856-7D8493B0883C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -562,9 +562,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFEEB500"/>
       <color rgb="FFFFECAF"/>
       <color rgb="FFFFDC6D"/>
-      <color rgb="FFEEB500"/>
       <color rgb="FF8A6900"/>
       <color rgb="FFFFDD71"/>
     </mruColors>
@@ -1516,7 +1516,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{2AE37A7E-30B3-4200-A591-4497C611D6FD}" type="CELLRANGE">
+                <a:fld id="{AC7BA32A-30DE-4CEE-892B-13D35B0EC420}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1533,7 +1533,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{04E09333-67D9-4F91-81B5-E511B3859BD8}" type="PERCENTAGE">
+                <a:fld id="{33C4265D-FCC4-4330-BB59-88D45E9EC5C3}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1630,7 +1630,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{739BB34D-32C2-486B-B65D-449C51618E08}" type="CELLRANGE">
+                <a:fld id="{7A8ED9C6-D552-4986-BC1A-016543CABE9F}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1647,7 +1647,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{91BDEF3C-D92A-4623-B70B-8A05DDC81C12}" type="PERCENTAGE">
+                <a:fld id="{B784940E-EE59-4642-B38C-D4226C247B0B}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1744,7 +1744,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{E63DAC9B-FDB8-40EC-AB0B-CF2E20C296C5}" type="CELLRANGE">
+                <a:fld id="{7A27665E-A6A7-4FF8-8970-B9BEF598411F}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1761,7 +1761,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{2B3AA187-31E8-42F9-BD54-8849D9F8F7A2}" type="PERCENTAGE">
+                <a:fld id="{B810169A-9F7D-4FC3-B706-586B7220A655}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1858,7 +1858,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{349E3509-FBE0-4FD9-9D9C-E55D02CB0D9A}" type="CELLRANGE">
+                <a:fld id="{0C49CBC3-B841-4877-A743-1BFAD4A3976F}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1875,7 +1875,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{BBD6F1EB-9824-43FE-AB0E-CE9491288FC8}" type="PERCENTAGE">
+                <a:fld id="{D304380E-B8A5-4004-84DF-A6419684F0A1}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -2039,7 +2039,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2AE37A7E-30B3-4200-A591-4497C611D6FD}" type="CELLRANGE">
+                    <a:fld id="{AC7BA32A-30DE-4CEE-892B-13D35B0EC420}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2048,7 +2048,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{04E09333-67D9-4F91-81B5-E511B3859BD8}" type="PERCENTAGE">
+                    <a:fld id="{33C4265D-FCC4-4330-BB59-88D45E9EC5C3}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2086,7 +2086,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{739BB34D-32C2-486B-B65D-449C51618E08}" type="CELLRANGE">
+                    <a:fld id="{7A8ED9C6-D552-4986-BC1A-016543CABE9F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2095,7 +2095,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{91BDEF3C-D92A-4623-B70B-8A05DDC81C12}" type="PERCENTAGE">
+                    <a:fld id="{B784940E-EE59-4642-B38C-D4226C247B0B}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2133,7 +2133,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E63DAC9B-FDB8-40EC-AB0B-CF2E20C296C5}" type="CELLRANGE">
+                    <a:fld id="{7A27665E-A6A7-4FF8-8970-B9BEF598411F}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2142,7 +2142,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{2B3AA187-31E8-42F9-BD54-8849D9F8F7A2}" type="PERCENTAGE">
+                    <a:fld id="{B810169A-9F7D-4FC3-B706-586B7220A655}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2180,7 +2180,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{349E3509-FBE0-4FD9-9D9C-E55D02CB0D9A}" type="CELLRANGE">
+                    <a:fld id="{0C49CBC3-B841-4877-A743-1BFAD4A3976F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2189,7 +2189,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{BBD6F1EB-9824-43FE-AB0E-CE9491288FC8}" type="PERCENTAGE">
+                    <a:fld id="{D304380E-B8A5-4004-84DF-A6419684F0A1}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -10435,9 +10435,53 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:gradFill flip="none" rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="EEB500">
+                <a:shade val="30000"/>
+                <a:satMod val="115000"/>
+              </a:srgbClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:srgbClr val="EEB500">
+                <a:shade val="67500"/>
+                <a:satMod val="115000"/>
+              </a:srgbClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="EEB500">
+                <a:shade val="100000"/>
+                <a:satMod val="115000"/>
+              </a:srgbClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect t="100000" r="100000"/>
+          </a:path>
+          <a:tileRect l="-100000" b="-100000"/>
+        </a:gradFill>
         <a:ln w="3175">
           <a:noFill/>
         </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" dist="228600" dir="2700000" algn="ctr">
+            <a:srgbClr val="000000">
+              <a:alpha val="30000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="glow" dir="t">
+            <a:rot lat="0" lon="0" rev="4800000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d prstMaterial="matte">
+          <a:bevelT w="127000" h="63500"/>
+        </a:sp3d>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0198854-854B-445A-9856-7D8493B0883C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D7C777-E6C9-4753-BB22-FC455F0ADDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -251,154 +251,7 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="46">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -562,10 +415,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFDC6D"/>
+      <color rgb="FF8A6900"/>
       <color rgb="FFEEB500"/>
       <color rgb="FFFFECAF"/>
-      <color rgb="FFFFDC6D"/>
-      <color rgb="FF8A6900"/>
       <color rgb="FFFFDD71"/>
     </mruColors>
   </colors>
@@ -1516,7 +1369,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{AC7BA32A-30DE-4CEE-892B-13D35B0EC420}" type="CELLRANGE">
+                <a:fld id="{BCEFE3A1-5279-439B-9D5C-5592E783B872}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1533,7 +1386,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{33C4265D-FCC4-4330-BB59-88D45E9EC5C3}" type="PERCENTAGE">
+                <a:fld id="{BAABADB7-2A00-4493-AEDA-37DF95019FAB}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1630,7 +1483,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{7A8ED9C6-D552-4986-BC1A-016543CABE9F}" type="CELLRANGE">
+                <a:fld id="{2A40DA4D-081C-4A75-AF48-49C192B11051}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1647,7 +1500,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{B784940E-EE59-4642-B38C-D4226C247B0B}" type="PERCENTAGE">
+                <a:fld id="{1A6EE693-C9CB-4490-8154-3CC7F77D7522}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1744,7 +1597,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{7A27665E-A6A7-4FF8-8970-B9BEF598411F}" type="CELLRANGE">
+                <a:fld id="{2EFC26A8-C002-4AAC-BD46-0D9C3C635444}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1761,7 +1614,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{B810169A-9F7D-4FC3-B706-586B7220A655}" type="PERCENTAGE">
+                <a:fld id="{D58548AA-FB53-4E30-BE6C-815DA5FF1F09}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1858,7 +1711,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{0C49CBC3-B841-4877-A743-1BFAD4A3976F}" type="CELLRANGE">
+                <a:fld id="{99CAD3F5-42F6-4700-BDEA-8BA293C1002D}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1875,7 +1728,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{D304380E-B8A5-4004-84DF-A6419684F0A1}" type="PERCENTAGE">
+                <a:fld id="{0E8D410E-0079-4500-BF15-00B60B057867}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -2039,7 +1892,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AC7BA32A-30DE-4CEE-892B-13D35B0EC420}" type="CELLRANGE">
+                    <a:fld id="{BCEFE3A1-5279-439B-9D5C-5592E783B872}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2048,7 +1901,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{33C4265D-FCC4-4330-BB59-88D45E9EC5C3}" type="PERCENTAGE">
+                    <a:fld id="{BAABADB7-2A00-4493-AEDA-37DF95019FAB}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2086,7 +1939,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7A8ED9C6-D552-4986-BC1A-016543CABE9F}" type="CELLRANGE">
+                    <a:fld id="{2A40DA4D-081C-4A75-AF48-49C192B11051}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2095,7 +1948,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{B784940E-EE59-4642-B38C-D4226C247B0B}" type="PERCENTAGE">
+                    <a:fld id="{1A6EE693-C9CB-4490-8154-3CC7F77D7522}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2133,7 +1986,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7A27665E-A6A7-4FF8-8970-B9BEF598411F}" type="CELLRANGE">
+                    <a:fld id="{2EFC26A8-C002-4AAC-BD46-0D9C3C635444}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2142,7 +1995,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{B810169A-9F7D-4FC3-B706-586B7220A655}" type="PERCENTAGE">
+                    <a:fld id="{D58548AA-FB53-4E30-BE6C-815DA5FF1F09}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2180,7 +2033,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0C49CBC3-B841-4877-A743-1BFAD4A3976F}" type="CELLRANGE">
+                    <a:fld id="{99CAD3F5-42F6-4700-BDEA-8BA293C1002D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2189,7 +2042,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{D304380E-B8A5-4004-84DF-A6419684F0A1}" type="PERCENTAGE">
+                    <a:fld id="{0E8D410E-0079-4500-BF15-00B60B057867}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2482,15 +2335,33 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="1"/>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t>top</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
-              <a:t> prouct by amount</a:t>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> product by amount</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" b="1"/>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t> </a:t>
             </a:r>
           </a:p>
@@ -2669,11 +2540,10 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="10000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -2695,6 +2565,42 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="EEB500"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="8A6900"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFDC6D"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -2727,6 +2633,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="EEB500"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-5A75-4B97-9278-D824DAFE0E46}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="8A6900"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5A75-4B97-9278-D824DAFE0E46}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFDC6D"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-5A75-4B97-9278-D824DAFE0E46}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -2742,11 +2705,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="10000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -2853,11 +2815,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -2869,11 +2831,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="10000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -2914,11 +2875,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="95000"/>
+                    <a:lumOff val="5000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -2953,19 +2914,46 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:srgbClr val="EEB500">
+            <a:shade val="30000"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="50000">
+          <a:srgbClr val="EEB500">
+            <a:shade val="67500"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:srgbClr val="EEB500">
+            <a:shade val="100000"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect t="100000" r="100000"/>
+      </a:path>
+      <a:tileRect l="-100000" b="-100000"/>
+    </a:gradFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:srgbClr val="FFC000"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
     <a:effectLst/>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
+    <a:sp3d prstMaterial="matte">
+      <a:bevelT w="127000" h="63500"/>
+    </a:sp3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -12948,7 +12936,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="39">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13522,7 +13510,7 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="40">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14076,7 +14064,7 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="41">
+    <format dxfId="20">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14653,7 +14641,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="42">
+    <format dxfId="21">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14734,7 +14722,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57377406-EF9D-40FA-8C1C-85593D1E9337}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57377406-EF9D-40FA-8C1C-85593D1E9337}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="L21:M25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -15277,11 +15265,11 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="43">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="5">
+  <chartFormats count="8">
     <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -15323,6 +15311,42 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -15885,7 +15909,7 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="44">
+    <format dxfId="23">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16456,7 +16480,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="45">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16748,10 +16772,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="14"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D7C777-E6C9-4753-BB22-FC455F0ADDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8812050A-AFF7-4739-B474-798EB2756D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -251,56 +251,7 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -415,11 +366,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFDC6D"/>
       <color rgb="FF8A6900"/>
-      <color rgb="FFEEB500"/>
       <color rgb="FFFFECAF"/>
       <color rgb="FFFFDD71"/>
+      <color rgb="FFFFDC6D"/>
+      <color rgb="FFEEB500"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1369,7 +1320,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{BCEFE3A1-5279-439B-9D5C-5592E783B872}" type="CELLRANGE">
+                <a:fld id="{118FE687-2819-4DEB-9592-D9C8920A626F}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1386,7 +1337,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{BAABADB7-2A00-4493-AEDA-37DF95019FAB}" type="PERCENTAGE">
+                <a:fld id="{ED12DC64-9EEB-4A45-B501-D90E15867279}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1483,7 +1434,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{2A40DA4D-081C-4A75-AF48-49C192B11051}" type="CELLRANGE">
+                <a:fld id="{5CC88ED6-2779-4F12-9818-188E0200F678}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1500,7 +1451,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{1A6EE693-C9CB-4490-8154-3CC7F77D7522}" type="PERCENTAGE">
+                <a:fld id="{D825C52C-4859-4239-A32D-D07C356C206A}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1597,7 +1548,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{2EFC26A8-C002-4AAC-BD46-0D9C3C635444}" type="CELLRANGE">
+                <a:fld id="{43EEB421-DE47-458C-A076-0842EEDD3B95}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1614,7 +1565,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{D58548AA-FB53-4E30-BE6C-815DA5FF1F09}" type="PERCENTAGE">
+                <a:fld id="{487044D8-0337-4544-BEFF-722A6CA889E4}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1711,7 +1662,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{99CAD3F5-42F6-4700-BDEA-8BA293C1002D}" type="CELLRANGE">
+                <a:fld id="{77C4E1E9-C328-4B52-8D54-C4B8F0C76EC5}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1728,7 +1679,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{0E8D410E-0079-4500-BF15-00B60B057867}" type="PERCENTAGE">
+                <a:fld id="{C8E53578-0B89-4022-BC29-ED43C2A9BEB2}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1892,7 +1843,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BCEFE3A1-5279-439B-9D5C-5592E783B872}" type="CELLRANGE">
+                    <a:fld id="{118FE687-2819-4DEB-9592-D9C8920A626F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1901,7 +1852,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{BAABADB7-2A00-4493-AEDA-37DF95019FAB}" type="PERCENTAGE">
+                    <a:fld id="{ED12DC64-9EEB-4A45-B501-D90E15867279}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1939,7 +1890,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2A40DA4D-081C-4A75-AF48-49C192B11051}" type="CELLRANGE">
+                    <a:fld id="{5CC88ED6-2779-4F12-9818-188E0200F678}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1948,7 +1899,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{1A6EE693-C9CB-4490-8154-3CC7F77D7522}" type="PERCENTAGE">
+                    <a:fld id="{D825C52C-4859-4239-A32D-D07C356C206A}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1986,7 +1937,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2EFC26A8-C002-4AAC-BD46-0D9C3C635444}" type="CELLRANGE">
+                    <a:fld id="{43EEB421-DE47-458C-A076-0842EEDD3B95}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1995,7 +1946,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{D58548AA-FB53-4E30-BE6C-815DA5FF1F09}" type="PERCENTAGE">
+                    <a:fld id="{487044D8-0337-4544-BEFF-722A6CA889E4}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2033,7 +1984,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{99CAD3F5-42F6-4700-BDEA-8BA293C1002D}" type="CELLRANGE">
+                    <a:fld id="{77C4E1E9-C328-4B52-8D54-C4B8F0C76EC5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2042,7 +1993,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{0E8D410E-0079-4500-BF15-00B60B057867}" type="PERCENTAGE">
+                    <a:fld id="{C8E53578-0B89-4022-BC29-ED43C2A9BEB2}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -3013,9 +2964,8 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="10000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -3024,14 +2974,32 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="1"/>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t>top</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="10000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t> salers</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" b="1"/>
+            <a:endParaRPr lang="en-US" b="1">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3050,9 +3018,8 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -3208,11 +3175,11 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
+                      <a:lumMod val="95000"/>
+                      <a:lumOff val="5000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -3234,6 +3201,78 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFDD71"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFDD71"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFECAF"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="FFECAF"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="8A6900"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="8A6900"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -3266,6 +3305,120 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="8A6900"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-42EE-4921-8F4A-7E5156F8A379}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="8A6900"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-42EE-4921-8F4A-7E5156F8A379}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFECAF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-42EE-4921-8F4A-7E5156F8A379}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFECAF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-42EE-4921-8F4A-7E5156F8A379}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFDD71"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-42EE-4921-8F4A-7E5156F8A379}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFDD71"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-42EE-4921-8F4A-7E5156F8A379}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -3281,11 +3434,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
+                        <a:lumMod val="95000"/>
+                        <a:lumOff val="5000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -3409,11 +3562,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -3425,11 +3578,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="95000"/>
+                    <a:lumOff val="5000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -3482,9 +3635,32 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:srgbClr val="FFC000">
+            <a:shade val="30000"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="50000">
+          <a:srgbClr val="FFC000">
+            <a:shade val="67500"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:srgbClr val="FFC000">
+            <a:shade val="100000"/>
+            <a:satMod val="115000"/>
+          </a:srgbClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect t="100000" r="100000"/>
+      </a:path>
+      <a:tileRect l="-100000" b="-100000"/>
+    </a:gradFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -3495,6 +3671,13 @@
       <a:round/>
     </a:ln>
     <a:effectLst/>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
+    <a:sp3d prstMaterial="matte">
+      <a:bevelT w="127000" h="63500"/>
+    </a:sp3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -12936,7 +13119,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="18">
+    <format dxfId="11">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13510,7 +13693,7 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="19">
+    <format dxfId="12">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14064,7 +14247,7 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="20">
+    <format dxfId="13">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14641,11 +14824,11 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="21">
+    <format dxfId="14">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="5">
+  <chartFormats count="11">
     <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -14686,6 +14869,78 @@
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -15265,7 +15520,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="22">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15909,7 +16164,7 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="23">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16480,7 +16735,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="24">
+    <format dxfId="17">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16772,10 +17027,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="7"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>

--- a/0B5F9D00.xlsx
+++ b/0B5F9D00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THINKPAD\Desktop\power bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8812050A-AFF7-4739-B474-798EB2756D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C91195-3D85-4B3A-9B9B-EE19E9DBC096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30BFA6B8-A676-4931-80C6-DA6F72E44419}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="35">
   <si>
     <t>S No</t>
   </si>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -251,7 +251,1084 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="169">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="1" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="1" tint="-0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="1" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -363,7 +1440,16 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="2" xr9:uid="{5E624735-CD9C-46A4-8C97-CEDA2DE3572D}">
+      <tableStyleElement type="wholeTable" dxfId="148"/>
+      <tableStyleElement type="headerRow" dxfId="147"/>
+    </tableStyle>
+    <tableStyle name="Timeline Style 1" pivot="0" table="0" count="8" xr9:uid="{116E182F-425B-4EE9-A158-B6869306FD31}">
+      <tableStyleElement type="wholeTable" dxfId="150"/>
+      <tableStyleElement type="headerRow" dxfId="149"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <mruColors>
       <color rgb="FF8A6900"/>
@@ -375,10 +1461,67 @@
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="Slicer Style 1"/>
+      </x14:slicerStyles>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{A0A4C193-F2C1-4fcb-8827-314CF55A85BB}">
+      <x15:dxfs count="6">
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="9"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <font>
+            <sz val="10"/>
+            <color theme="1" tint="0.499984740745262"/>
+          </font>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0" tint="-0.14999847407452621"/>
+              <bgColor theme="0" tint="-0.14999847407452621"/>
+            </patternFill>
+          </fill>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="0"/>
+              <bgColor theme="0"/>
+            </patternFill>
+          </fill>
+        </dxf>
+      </x15:dxfs>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1">
+        <x15:timelineStyle name="Timeline Style 1">
+          <x15:timelineStyleElements>
+            <x15:timelineStyleElement type="selectionLabel" dxfId="3"/>
+            <x15:timelineStyleElement type="timeLevel" dxfId="2"/>
+            <x15:timelineStyleElement type="periodLabel1" dxfId="1"/>
+            <x15:timelineStyleElement type="periodLabel2" dxfId="0"/>
+            <x15:timelineStyleElement type="selectedTimeBlock" dxfId="5"/>
+            <x15:timelineStyleElement type="unselectedTimeBlock" dxfId="4"/>
+          </x15:timelineStyleElements>
+        </x15:timelineStyle>
+      </x15:timelineStyles>
     </ext>
   </extLst>
 </styleSheet>
@@ -739,10 +1882,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>290180</c:v>
+                  <c:v>18690</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>136350</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1320,7 +2463,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{118FE687-2819-4DEB-9592-D9C8920A626F}" type="CELLRANGE">
+                <a:fld id="{9628A3E8-53CF-42AB-9722-122A49B9AF82}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1337,7 +2480,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{ED12DC64-9EEB-4A45-B501-D90E15867279}" type="PERCENTAGE">
+                <a:fld id="{C77A71F5-51C9-4220-9A55-45AA59BA0657}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1434,7 +2577,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{5CC88ED6-2779-4F12-9818-188E0200F678}" type="CELLRANGE">
+                <a:fld id="{4CDE4E97-384B-422C-9BD2-F010A60A42D3}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1451,7 +2594,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{D825C52C-4859-4239-A32D-D07C356C206A}" type="PERCENTAGE">
+                <a:fld id="{D890404F-66EA-4160-8928-898EFABA1C5D}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1548,7 +2691,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{43EEB421-DE47-458C-A076-0842EEDD3B95}" type="CELLRANGE">
+                <a:fld id="{E8F79B11-EC4F-4699-BA5F-368176DA7F12}" type="CELLRANGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1565,7 +2708,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{487044D8-0337-4544-BEFF-722A6CA889E4}" type="PERCENTAGE">
+                <a:fld id="{C9B23524-FF3C-4AB3-A66C-683C4B4DF07A}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1662,7 +2805,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{77C4E1E9-C328-4B52-8D54-C4B8F0C76EC5}" type="CELLRANGE">
+                <a:fld id="{F1EF6902-B147-4DE9-A470-5D45FFF25785}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1679,7 +2822,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{C8E53578-0B89-4022-BC29-ED43C2A9BEB2}" type="PERCENTAGE">
+                <a:fld id="{561A5D49-C7A6-4F9E-A5DC-7B56F775A238}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr b="1">
@@ -1843,7 +2986,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{118FE687-2819-4DEB-9592-D9C8920A626F}" type="CELLRANGE">
+                    <a:fld id="{9628A3E8-53CF-42AB-9722-122A49B9AF82}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1852,7 +2995,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{ED12DC64-9EEB-4A45-B501-D90E15867279}" type="PERCENTAGE">
+                    <a:fld id="{C77A71F5-51C9-4220-9A55-45AA59BA0657}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1890,7 +3033,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5CC88ED6-2779-4F12-9818-188E0200F678}" type="CELLRANGE">
+                    <a:fld id="{4CDE4E97-384B-422C-9BD2-F010A60A42D3}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1899,7 +3042,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{D825C52C-4859-4239-A32D-D07C356C206A}" type="PERCENTAGE">
+                    <a:fld id="{D890404F-66EA-4160-8928-898EFABA1C5D}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1937,7 +3080,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{43EEB421-DE47-458C-A076-0842EEDD3B95}" type="CELLRANGE">
+                    <a:fld id="{E8F79B11-EC4F-4699-BA5F-368176DA7F12}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1946,7 +3089,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{487044D8-0337-4544-BEFF-722A6CA889E4}" type="PERCENTAGE">
+                    <a:fld id="{C9B23524-FF3C-4AB3-A66C-683C4B4DF07A}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1984,7 +3127,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{77C4E1E9-C328-4B52-8D54-C4B8F0C76EC5}" type="CELLRANGE">
+                    <a:fld id="{F1EF6902-B147-4DE9-A470-5D45FFF25785}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1993,7 +3136,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{C8E53578-0B89-4022-BC29-ED43C2A9BEB2}" type="PERCENTAGE">
+                    <a:fld id="{561A5D49-C7A6-4F9E-A5DC-7B56F775A238}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2100,16 +3243,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>38300</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24270</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>155450</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>208510</c:v>
+                  <c:v>15600</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2622,25 +3765,6 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFDC6D"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-5A75-4B97-9278-D824DAFE0E46}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -2710,7 +3834,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Monitor</c:v>
+                  <c:v>Keyboard</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2722,13 +3846,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>306000</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79800</c:v>
+                  <c:v>14700</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12000</c:v>
+                  <c:v>1140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3324,101 +4448,6 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="8A6900"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-42EE-4921-8F4A-7E5156F8A379}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFECAF"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-42EE-4921-8F4A-7E5156F8A379}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFECAF"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-42EE-4921-8F4A-7E5156F8A379}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFDD71"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-42EE-4921-8F4A-7E5156F8A379}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFDD71"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-42EE-4921-8F4A-7E5156F8A379}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -3479,53 +4508,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$36:$H$42</c:f>
+              <c:f>'data analysis'!$H$36:$H$37</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Ahmed Said</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Ali Ramadan</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Ashraf Zaki</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Fathy Ali</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Khaled Hassan</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Tamer Mohamed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$36:$I$42</c:f>
+              <c:f>'data analysis'!$I$36:$I$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>44190</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>66010</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>121600</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>123820</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>39400</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>31510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3869,10 +4868,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>290180</c:v>
+                  <c:v>18690</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>136350</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4392,16 +5391,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>38300</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24270</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>155450</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>208510</c:v>
+                  <c:v>15600</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4672,7 +5671,7 @@
                   <c:v>Printer</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Monitor</c:v>
+                  <c:v>Keyboard</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4684,13 +5683,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>306000</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>79800</c:v>
+                  <c:v>14700</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12000</c:v>
+                  <c:v>1140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5059,53 +6058,23 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'data analysis'!$H$36:$H$42</c:f>
+              <c:f>'data analysis'!$H$36:$H$37</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Ahmed Said</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Ali Ramadan</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Ashraf Zaki</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Fathy Ali</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Khaled Hassan</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Tamer Mohamed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data analysis'!$I$36:$I$42</c:f>
+              <c:f>'data analysis'!$I$36:$I$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>44190</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>66010</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>121600</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>123820</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>39400</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>31510</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9955,7 +10924,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t> $426,530 </a:t>
+              <a:t> $44,190 </a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -10127,7 +11096,7 @@
                 <a:latin typeface="+mj-lt"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>40</a:t>
+              <a:t>7</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="+mj-lt"/>
@@ -10299,7 +11268,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>10663</a:t>
+              <a:t>6313</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2000" b="1">
               <a:latin typeface="Gotham" panose="02000504020000020004" pitchFamily="2" charset="0"/>
@@ -11581,7 +12550,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
+      <xdr:colOff>83820</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
@@ -12638,11 +13607,11 @@
     <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13119,7 +14088,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="11">
+    <format dxfId="162">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13225,11 +14194,11 @@
     <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13693,7 +14662,7 @@
     <dataField name="AVG SALES" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="12">
+    <format dxfId="163">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13779,11 +14748,11 @@
     <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14247,7 +15216,7 @@
     <dataField name="TOTAL ITEM" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="13">
+    <format dxfId="164">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14282,7 +15251,7 @@
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4624B9DB-16A8-46B5-A956-2588C79515CB}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="H35:I42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="H35:I37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -14333,11 +15302,11 @@
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="7">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14794,24 +15763,9 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="2">
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -14824,7 +15778,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="14">
+    <format dxfId="165">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15029,11 +15983,11 @@
     <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -15507,7 +16461,7 @@
       <x v="5"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -15520,7 +16474,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="15">
+    <format dxfId="166">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15696,11 +16650,11 @@
     <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16164,7 +17118,7 @@
     <dataField name="TOTAL SALES" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="16">
+    <format dxfId="167">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16250,11 +17204,11 @@
     <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16735,7 +17689,7 @@
     <dataField name="Sum of Amount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="17">
+    <format dxfId="168">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16973,11 +17927,11 @@
     <tabular pivotCacheId="548194542">
       <items count="6">
         <i x="0" s="1"/>
-        <i x="1" s="1"/>
-        <i x="2" s="1"/>
-        <i x="3" s="1"/>
-        <i x="5" s="1"/>
-        <i x="4" s="1"/>
+        <i x="1"/>
+        <i x="2"/>
+        <i x="3"/>
+        <i x="5"/>
+        <i x="4"/>
       </items>
     </tabular>
   </data>
@@ -17010,8 +17964,8 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Salesman 1" xr10:uid="{B0813A65-02C1-49D2-9E9F-65CDFDF1159A}" cache="Slicer_Salesman" caption="Salesman" rowHeight="247650"/>
-  <slicer name="Region 1" xr10:uid="{E3223445-0FF4-4A60-A5DF-67216457E98D}" cache="Slicer_Region" caption="Region" rowHeight="247650"/>
+  <slicer name="Salesman 1" xr10:uid="{B0813A65-02C1-49D2-9E9F-65CDFDF1159A}" cache="Slicer_Salesman" caption="Salesman" style="Slicer Style 1" rowHeight="247650"/>
+  <slicer name="Region 1" xr10:uid="{E3223445-0FF4-4A60-A5DF-67216457E98D}" cache="Slicer_Region" caption="Region" style="Slicer Style 1" rowHeight="247650"/>
 </slicers>
 </file>
 
@@ -17027,10 +17981,10 @@
   <autoFilter ref="A1:H41" xr:uid="{DAE5D27C-AE6B-4686-951B-ABFA64A7EEE3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{60EE4400-F973-4F15-948A-9008563AA622}" uniqueName="1" name="S No" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{A8629C8B-F662-4D64-94C6-C7B97196A735}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="161"/>
+    <tableColumn id="3" xr3:uid="{5C50CE82-4D1A-4C79-9D0F-247FE1CDFA5C}" uniqueName="3" name="Salesman" queryTableFieldId="3" dataDxfId="160"/>
+    <tableColumn id="4" xr3:uid="{C594ECD2-D104-43F4-A766-C80694137000}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="159"/>
+    <tableColumn id="5" xr3:uid="{4EBFE9AF-2CF8-4086-910A-E4FE148003F0}" uniqueName="5" name="Item" queryTableFieldId="5" dataDxfId="158"/>
     <tableColumn id="6" xr3:uid="{28BA1440-E926-4945-883F-D0FCD7D3BB97}" uniqueName="6" name="Qty" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{9D812FB1-FCA4-4EB2-8FA6-297FD68B5A88}" uniqueName="7" name="Price" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{076B1DB5-2FB3-4FA7-8121-F2E26FB13E54}" uniqueName="8" name="Amount" queryTableFieldId="8"/>
@@ -17374,7 +18328,7 @@
 
 <file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
 <timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <timeline name="Date 1" xr10:uid="{4BAC2FE9-C0D7-4F7A-AA2C-A32B2D77E7A4}" cache="NativeTimeline_Date" caption="Date" level="2" selectionLevel="2" scrollPosition="2023-01-01T00:00:00" style="TimeSlicerStyleDark1"/>
+  <timeline name="Date 1" xr10:uid="{4BAC2FE9-C0D7-4F7A-AA2C-A32B2D77E7A4}" cache="NativeTimeline_Date" caption="Date" level="2" selectionLevel="2" scrollPosition="2023-01-01T00:00:00" style="Timeline Style 1"/>
 </timelines>
 </file>
 
@@ -17408,13 +18362,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1649C905-6944-4F98-B4AE-37BE068CDF30}">
-  <dimension ref="A2:M42"/>
+  <dimension ref="A2:M37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -17449,39 +18403,39 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
-        <v>426530</v>
+        <v>44190</v>
       </c>
       <c r="C6" s="6">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E6" s="6">
-        <v>10663.25</v>
+        <v>6312.8571428571431</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="6">
-        <v>290180</v>
+        <v>18690</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <f>GETPIVOTDATA("Amount",$A$5)</f>
-        <v>426530</v>
+        <v>44190</v>
       </c>
       <c r="C7">
         <f>GETPIVOTDATA("Item",$C$5)</f>
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E7" s="8">
         <f>GETPIVOTDATA("Amount",$E$5)</f>
-        <v>10663.25</v>
+        <v>6312.8571428571431</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>34</v>
       </c>
       <c r="I7" s="6">
-        <v>136350</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -17489,7 +18443,7 @@
         <v>27</v>
       </c>
       <c r="I8" s="6">
-        <v>426530</v>
+        <v>44190</v>
       </c>
     </row>
     <row r="20" spans="8:13" x14ac:dyDescent="0.3">
@@ -17505,7 +18459,7 @@
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>38300</v>
+        <v>25500</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>26</v>
@@ -17519,13 +18473,13 @@
         <v>9</v>
       </c>
       <c r="I22" s="6">
-        <v>24270</v>
+        <v>1050</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>19</v>
       </c>
       <c r="M22" s="6">
-        <v>306000</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="23" spans="8:13" x14ac:dyDescent="0.3">
@@ -17533,13 +18487,13 @@
         <v>12</v>
       </c>
       <c r="I23" s="6">
-        <v>155450</v>
+        <v>2040</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="M23" s="6">
-        <v>79800</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="24" spans="8:13" x14ac:dyDescent="0.3">
@@ -17547,13 +18501,13 @@
         <v>20</v>
       </c>
       <c r="I24" s="6">
-        <v>208510</v>
+        <v>15600</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M24" s="6">
-        <v>12000</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="25" spans="8:13" x14ac:dyDescent="0.3">
@@ -17561,13 +18515,13 @@
         <v>27</v>
       </c>
       <c r="I25" s="6">
-        <v>426530</v>
+        <v>44190</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="M25" s="6">
-        <v>397800</v>
+        <v>41340</v>
       </c>
     </row>
     <row r="35" spans="8:9" x14ac:dyDescent="0.3">
@@ -17588,50 +18542,10 @@
     </row>
     <row r="37" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H37" s="5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="I37" s="6">
-        <v>66010</v>
-      </c>
-    </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="6">
-        <v>121600</v>
-      </c>
-    </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H39" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="6">
-        <v>123820</v>
-      </c>
-    </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="6">
-        <v>39400</v>
-      </c>
-    </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I41" s="6">
-        <v>31510</v>
-      </c>
-    </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="6">
-        <v>426530</v>
+        <v>44190</v>
       </c>
     </row>
   </sheetData>
